--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,12 +463,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -487,6 +488,11 @@
           <t>Change 2</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Change 3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -500,6 +506,7 @@
         </is>
       </c>
       <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -517,6 +524,7 @@
           <t>2026-09-24 | CSRF + form token guard; switched to shared db_begin/db_commit/db_rollback helpers.</t>
         </is>
       </c>
+      <c r="D3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -530,6 +538,7 @@
         </is>
       </c>
       <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -547,6 +556,7 @@
           <t>2026-09-23 | Section 4 added - Item Stock List menu row + rights.</t>
         </is>
       </c>
+      <c r="D5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -564,6 +574,7 @@
           <t>2026-09-24 | CSRF + form token guard on UPDATE and FINALIZE; transaction with rollback.</t>
         </is>
       </c>
+      <c r="D6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -581,6 +592,11 @@
           <t>2026-09-24 | CSRF + form token guard on Draft/UPDATE/FINALIZE; transaction with rollback.</t>
         </is>
       </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | Cash denomination dropdown ordered by value instead of cash_id.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -598,6 +614,11 @@
           <t>2026-09-24 | CSRF + form token guard; try/catch added (handlers had none); transaction with rollback.</t>
         </is>
       </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | Cash denomination dropdown ordered by value instead of cash_id.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -615,6 +636,7 @@
           <t>2026-09-24 | CSRF + form token guard; try/catch added (handlers had none); transaction with rollback.</t>
         </is>
       </c>
+      <c r="D9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -632,6 +654,7 @@
           <t>2026-09-24 | CSRF + form token guard on SAVE/SAVE1/UPDATE; transaction with rollback.</t>
         </is>
       </c>
+      <c r="D10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -649,6 +672,7 @@
           <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE; transaction with rollback.</t>
         </is>
       </c>
+      <c r="D11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -662,6 +686,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -675,6 +700,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -692,6 +718,7 @@
           <t>2026-09-24 | Login check + CSRF check added. It had no login check at all before.</t>
         </is>
       </c>
+      <c r="D14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -705,6 +732,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -718,6 +746,7 @@
         </is>
       </c>
       <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -735,6 +764,7 @@
           <t>2026-09-23 | Runs from $_REQUEST so the stock list View All link works; query now bound instead of interpolated.</t>
         </is>
       </c>
+      <c r="D17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -748,6 +778,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -761,6 +792,7 @@
         </is>
       </c>
       <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -774,6 +806,7 @@
         </is>
       </c>
       <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -787,6 +820,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -800,6 +834,7 @@
         </is>
       </c>
       <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -813,6 +848,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -830,6 +866,7 @@
           <t>2026-09-24 | Loads csrf.php and db_txn.php.</t>
         </is>
       </c>
+      <c r="D24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -843,6 +880,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -856,6 +894,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -869,6 +908,7 @@
         </is>
       </c>
       <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -882,6 +922,7 @@
         </is>
       </c>
       <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -895,6 +936,7 @@
         </is>
       </c>
       <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -908,6 +950,7 @@
         </is>
       </c>
       <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -921,6 +964,7 @@
         </is>
       </c>
       <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -934,6 +978,7 @@
         </is>
       </c>
       <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -947,6 +992,7 @@
         </is>
       </c>
       <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -960,6 +1006,7 @@
         </is>
       </c>
       <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -973,6 +1020,63 @@
         </is>
       </c>
       <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>db/cash_denomination_update.sql</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | New. Retires the 2000 denomination and adds 1, 2 and 5 in both cash tables.</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>pay_receipt.php</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | Cash denomination dropdown ordered by value instead of cash_id, so 1/2/5 sit at the top.</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>mng_credit.php</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | Cash denomination dropdown ordered by value instead of cash_id.</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>db/bie.sql</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -985,7 +1089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1260,15 +1364,19 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>tbl_item_details</t>
+          <t>tbl_cash_details</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | item_curr_stock | No change. Noted as dead - every write to it was already commented out. Branch columns in tbl_item_stock are the live balance.</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n"/>
+          <t>2026-09-25 | cash_status | 2000.00 set to 0 (retired). Not deleted - old receipts hold cash_id 7 and history screens look the name up without checking status.</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | (rows) | Added cash_id 8 = 1.00, 9 = 2.00, 10 = 5.00, all active. Used by the Sales Receipt screen.</t>
+        </is>
+      </c>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="n"/>
@@ -1280,6 +1388,56 @@
       <c r="L7" s="4" t="n"/>
       <c r="M7" s="4" t="n"/>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>mst_cash_details</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | cash_status | 2000.00 set to 0 (retired). Same reasoning as tbl_cash_details.</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | (rows) | Added cash_id 8 = 1.00, 9 = 2.00, 10 = 5.00, all active. Used by the Invoice and Credit screens.</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>tbl_item_details</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | item_curr_stock | No change. Noted as dead - every write to it was already commented out. Branch columns in tbl_item_stock are the live balance.</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,13 +463,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -493,6 +494,11 @@
           <t>Change 3</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Change 4</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -507,6 +513,7 @@
       </c>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -525,6 +532,7 @@
         </is>
       </c>
       <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -539,6 +547,7 @@
       </c>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -557,6 +566,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -575,6 +585,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -597,6 +608,11 @@
           <t>2026-09-25 | Cash denomination dropdown ordered by value instead of cash_id.</t>
         </is>
       </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30 | Edit view posted quo_value, a column tbl_invoice_details does not have, wiping inv_value to 0. Now posts inv_value.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -619,6 +635,11 @@
           <t>2026-09-25 | Cash denomination dropdown ordered by value instead of cash_id.</t>
         </is>
       </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30 | Edit view posted quo_value, a column tbl_invoice_details does not have, wiping inv_value to 0. Now posts inv_value.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -636,7 +657,16 @@
           <t>2026-09-24 | CSRF + form token guard; try/catch added (handlers had none); transaction with rollback.</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | Cash denomination dropdown ordered by value instead of cash_id.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30 | Edit view posted quo_value, a column tbl_invoice_details does not have, wiping inv_value to 0. Now posts inv_value. Percentage charge base read from the raw hidden total instead of the comma-formatted text.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -655,6 +685,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -673,6 +704,7 @@
         </is>
       </c>
       <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -687,6 +719,7 @@
       </c>
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -701,6 +734,7 @@
       </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -719,6 +753,7 @@
         </is>
       </c>
       <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -733,6 +768,7 @@
       </c>
       <c r="C15" s="4" t="n"/>
       <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -747,6 +783,7 @@
       </c>
       <c r="C16" s="4" t="n"/>
       <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -765,6 +802,7 @@
         </is>
       </c>
       <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -779,6 +817,7 @@
       </c>
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -793,6 +832,7 @@
       </c>
       <c r="C19" s="4" t="n"/>
       <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -807,6 +847,7 @@
       </c>
       <c r="C20" s="4" t="n"/>
       <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -821,6 +862,7 @@
       </c>
       <c r="C21" s="4" t="n"/>
       <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -835,6 +877,7 @@
       </c>
       <c r="C22" s="4" t="n"/>
       <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -849,6 +892,7 @@
       </c>
       <c r="C23" s="4" t="n"/>
       <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -867,6 +911,7 @@
         </is>
       </c>
       <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -881,6 +926,7 @@
       </c>
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -895,6 +941,7 @@
       </c>
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -909,6 +956,7 @@
       </c>
       <c r="C27" s="4" t="n"/>
       <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -921,8 +969,13 @@
           <t>2026-09-24 | CSRF + form token guard on SAVE; try/catch added (handler had none); transaction with rollback.</t>
         </is>
       </c>
-      <c r="C28" s="4" t="n"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30 | Edit view posted quo_value, a column tbl_proforma_details does not have, wiping pro_value to 0. Now posts pro_value.</t>
+        </is>
+      </c>
       <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -937,6 +990,7 @@
       </c>
       <c r="C29" s="4" t="n"/>
       <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -951,6 +1005,7 @@
       </c>
       <c r="C30" s="4" t="n"/>
       <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -965,6 +1020,7 @@
       </c>
       <c r="C31" s="4" t="n"/>
       <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -979,6 +1035,7 @@
       </c>
       <c r="C32" s="4" t="n"/>
       <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -993,6 +1050,7 @@
       </c>
       <c r="C33" s="4" t="n"/>
       <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1007,6 +1065,7 @@
       </c>
       <c r="C34" s="4" t="n"/>
       <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1021,6 +1080,7 @@
       </c>
       <c r="C35" s="4" t="n"/>
       <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1035,6 +1095,7 @@
       </c>
       <c r="C36" s="4" t="n"/>
       <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1049,6 +1110,7 @@
       </c>
       <c r="C37" s="4" t="n"/>
       <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1063,20 +1125,37 @@
       </c>
       <c r="C38" s="4" t="n"/>
       <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>db/bie.sql</t>
+          <t>db/invoice_value_repair.sql</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+          <t>2026-09-30 | New. Rebuilds inv_value / pro_value on rows zeroed by the edit screen, from net_value - tax_value.</t>
         </is>
       </c>
       <c r="C39" s="4" t="n"/>
       <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>db/bie.sql</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1089,7 +1168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1418,12 +1497,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>tbl_item_details</t>
+          <t>tbl_invoice_details</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | item_curr_stock | No change. Noted as dead - every write to it was already commented out. Branch columns in tbl_item_stock are the live balance.</t>
+          <t>2026-09-30 | inv_value | No schema change. Data repair - rows saved from the invoice edit screen had this zeroed by a bad field mapping. Rebuilt as net_value - tax_value where that agrees with qty x unit_price less discount.</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -1438,6 +1517,52 @@
       <c r="L9" s="4" t="n"/>
       <c r="M9" s="4" t="n"/>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>tbl_proforma_details</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30 | pro_value | No schema change. Same data repair as tbl_invoice_details.</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>tbl_item_details</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | item_curr_stock | No change. Noted as dead - every write to it was already commented out. Branch columns in tbl_item_stock are the live balance.</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -988,7 +988,11 @@
           <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE/FINALIZE; transaction with rollback.</t>
         </is>
       </c>
-      <c r="C29" s="4" t="n"/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01 | Item rows moved off tbl_dc_details_temp into a php array; packing moved off tbl_package_box_details_temp onto the item row as csv hidden fields. Box type counts done in javascript.</t>
+        </is>
+      </c>
       <c r="D29" s="4" t="n"/>
       <c r="E29" s="4" t="n"/>
     </row>
@@ -1130,12 +1134,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>db/invoice_value_repair.sql</t>
+          <t>inc/common/form_rows.php</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30 | New. Rebuilds inv_value / pro_value on rows zeroed by the edit screen, from net_value - tax_value.</t>
+          <t>2026-10-01 | New. Shared table row renderers - fnBranchRow(), fnItemGroupRow(). Used by both the page and its ajax endpoint so rows cannot drift apart.</t>
         </is>
       </c>
       <c r="C39" s="4" t="n"/>
@@ -1145,17 +1149,137 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>db/bie.sql</t>
+          <t>inc/cis_ajax/jquery_cutomer_branch_details.php</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+          <t>2026-10-01 | Rewritten 196 -&gt; 30 lines. Renders one branch row, no database writes, login + csrf checked.</t>
         </is>
       </c>
       <c r="C40" s="4" t="n"/>
       <c r="D40" s="4" t="n"/>
       <c r="E40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>mst_customer_new.php</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01 | Branch rows moved off mst_customer_branch_temp. Existing branches render from mst_customer_branch; save loops the posted br_* arrays; add/edit/remove are DOM only.</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>inc/cis_ajax/jquery_item_group_details.php</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01 | Rewritten 240 -&gt; 48 lines. Renders group item rows, no database writes.</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>mst_item_grouping.php</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01 | Group items moved off tbl_item_group_details_temp. Added the trade_items field that fnValidate() read but never existed. Read-only users now post qty and position as hidden fields.</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>inc/cis_ajax/jquery_modal_dc_pack_dets.php</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01 | Rewritten 392 -&gt; 80 lines. Renders the packing inputs from values sent by the page, no database access.</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>add_packing_box.php</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01 | Removed. The packing modal no longer writes to the database, so nothing called it.</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>db/drop_temp_tables.sql</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01 | New. Drops the four temp tables once the screens are confirmed.</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>db/invoice_value_repair.sql</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30 | New. Rebuilds inv_value / pro_value on rows zeroed by the edit screen, from net_value - tax_value.</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>db/bie.sql</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1168,7 +1292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1497,12 +1621,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>tbl_invoice_details</t>
+          <t>mst_customer_branch_temp</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30 | inv_value | No schema change. Data repair - rows saved from the invoice edit screen had this zeroed by a bad field mapping. Rebuilt as net_value - tax_value where that agrees with qty x unit_price less discount.</t>
+          <t>2026-10-01 | (whole table) | No longer used. Branch rows live in the page and post back as arrays. Drop with db/drop_temp_tables.sql.</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -1520,12 +1644,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>tbl_proforma_details</t>
+          <t>tbl_item_group_details_temp</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30 | pro_value | No schema change. Same data repair as tbl_invoice_details.</t>
+          <t>2026-10-01 | (whole table) | No longer used. Group items live in the page. Drop with db/drop_temp_tables.sql.</t>
         </is>
       </c>
       <c r="C10" s="4" t="n"/>
@@ -1543,12 +1667,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>tbl_item_details</t>
+          <t>tbl_dc_details_temp</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | item_curr_stock | No change. Noted as dead - every write to it was already commented out. Branch columns in tbl_item_stock are the live balance.</t>
+          <t>2026-10-01 | (whole table) | No longer used. DC item rows are built in php and posted back as arrays. Drop with db/drop_temp_tables.sql.</t>
         </is>
       </c>
       <c r="C11" s="4" t="n"/>
@@ -1563,6 +1687,98 @@
       <c r="L11" s="4" t="n"/>
       <c r="M11" s="4" t="n"/>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>tbl_package_box_details_temp</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01 | (whole table) | No longer used. Packing rides on the DC item row as csv hidden fields. Drop with db/drop_temp_tables.sql.</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>tbl_invoice_details</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30 | inv_value | No schema change. Data repair - rows saved from the invoice edit screen had this zeroed by a bad field mapping. Rebuilt as net_value - tax_value where that agrees with qty x unit_price less discount.</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>tbl_proforma_details</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30 | pro_value | No schema change. Same data repair as tbl_invoice_details.</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>tbl_item_details</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | item_curr_stock | No change. Noted as dead - every write to it was already commented out. Branch columns in tbl_item_stock are the live balance.</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="n"/>
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -916,12 +916,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>inc/common/css-js.php</t>
+          <t>gen_so.php</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 | csrf-token meta tag + $.ajaxSetup that attaches the token to every ajax POST, so existing scripts need no edit.</t>
+          <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE/ACCOUNTS; try/catch added (handlers had none); transaction with rollback.</t>
         </is>
       </c>
       <c r="C25" s="4" t="n"/>
@@ -931,12 +931,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>gen_so.php</t>
+          <t>quotation.php</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE/ACCOUNTS; try/catch added (handlers had none); transaction with rollback.</t>
+          <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE/FINALIZE; transaction with rollback.</t>
         </is>
       </c>
       <c r="C26" s="4" t="n"/>
@@ -946,32 +946,36 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>quotation.php</t>
+          <t>quo_proforma.php</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE/FINALIZE; transaction with rollback.</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="n"/>
+          <t>2026-09-24 | CSRF + form token guard on SAVE; try/catch added (handler had none); transaction with rollback.</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30 | Edit view posted quo_value, a column tbl_proforma_details does not have, wiping pro_value to 0. Now posts pro_value.</t>
+        </is>
+      </c>
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>quo_proforma.php</t>
+          <t>dc_add.php</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 | CSRF + form token guard on SAVE; try/catch added (handler had none); transaction with rollback.</t>
+          <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE/FINALIZE; transaction with rollback.</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30 | Edit view posted quo_value, a column tbl_proforma_details does not have, wiping pro_value to 0. Now posts pro_value.</t>
+          <t>2026-10-01 | Item rows moved off tbl_dc_details_temp into a php array; packing moved off tbl_package_box_details_temp onto the item row as csv hidden fields. Box type counts done in javascript.</t>
         </is>
       </c>
       <c r="D28" s="4" t="n"/>
@@ -980,31 +984,27 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>dc_add.php</t>
+          <t>po_prepare.php</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE/FINALIZE; transaction with rollback.</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01 | Item rows moved off tbl_dc_details_temp into a php array; packing moved off tbl_package_box_details_temp onto the item row as csv hidden fields. Box type counts done in javascript.</t>
-        </is>
-      </c>
+          <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE/send_to_admin; transaction with rollback.</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n"/>
       <c r="D29" s="4" t="n"/>
       <c r="E29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>po_prepare.php</t>
+          <t>direct_purchase_order.php</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE/send_to_admin; transaction with rollback.</t>
+          <t>2026-09-24 | CSRF + form token guard on Draft/UPDATE/FINALIZE; transaction with rollback. Commit moved before the redirect that ends the success path.</t>
         </is>
       </c>
       <c r="C30" s="4" t="n"/>
@@ -1014,12 +1014,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>direct_purchase_order.php</t>
+          <t>store_indent_add.php</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 | CSRF + form token guard on Draft/UPDATE/FINALIZE; transaction with rollback. Commit moved before the redirect that ends the success path.</t>
+          <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE/FINALIZE; transaction with rollback. Commit moved before the redirect that ends the success path.</t>
         </is>
       </c>
       <c r="C31" s="4" t="n"/>
@@ -1029,12 +1029,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>store_indent_add.php</t>
+          <t>repair_indent_add.php</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE/FINALIZE; transaction with rollback. Commit moved before the redirect that ends the success path.</t>
+          <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE; transaction with rollback.</t>
         </is>
       </c>
       <c r="C32" s="4" t="n"/>
@@ -1044,12 +1044,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>repair_indent_add.php</t>
+          <t>purchase_return_add.php</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE; transaction with rollback.</t>
+          <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE/FINALIZE; transaction with rollback.</t>
         </is>
       </c>
       <c r="C33" s="4" t="n"/>
@@ -1059,12 +1059,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>purchase_return_add.php</t>
+          <t>docs/CHANGELOG.md</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE/FINALIZE; transaction with rollback.</t>
+          <t>2026-09-24 | New. Full change log with detail behind these one-liners.</t>
         </is>
       </c>
       <c r="C34" s="4" t="n"/>
@@ -1074,12 +1074,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>docs/CHANGELOG.md</t>
+          <t>db/cash_denomination_update.sql</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 | New. Full change log with detail behind these one-liners.</t>
+          <t>2026-09-25 | New. Retires the 2000 denomination and adds 1, 2 and 5 in both cash tables.</t>
         </is>
       </c>
       <c r="C35" s="4" t="n"/>
@@ -1089,12 +1089,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>db/cash_denomination_update.sql</t>
+          <t>pay_receipt.php</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | New. Retires the 2000 denomination and adds 1, 2 and 5 in both cash tables.</t>
+          <t>2026-09-25 | Cash denomination dropdown ordered by value instead of cash_id, so 1/2/5 sit at the top.</t>
         </is>
       </c>
       <c r="C36" s="4" t="n"/>
@@ -1104,12 +1104,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>pay_receipt.php</t>
+          <t>mng_credit.php</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | Cash denomination dropdown ordered by value instead of cash_id, so 1/2/5 sit at the top.</t>
+          <t>2026-09-25 | Cash denomination dropdown ordered by value instead of cash_id.</t>
         </is>
       </c>
       <c r="C37" s="4" t="n"/>
@@ -1119,12 +1119,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>mng_credit.php</t>
+          <t>inc/common/error_log.php</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | Cash denomination dropdown ordered by value instead of cash_id.</t>
+          <t>2026-10-01 | New. fnLogError() writes date, file:line, page, user and message to logs/error_YYYY-MM.log. Called from 136 catch blocks across 69 files.</t>
         </is>
       </c>
       <c r="C38" s="4" t="n"/>
@@ -1134,27 +1134,31 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>inc/common/form_rows.php</t>
+          <t>inc/common/css-js.php</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | New. Shared table row renderers - fnBranchRow(), fnItemGroupRow(). Used by both the page and its ajax endpoint so rows cannot drift apart.</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n"/>
+          <t>2026-09-24 | csrf-token meta tag + $.ajaxSetup that attaches the token to every ajax POST.</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01 | Double-submit lock for every form. Buttons disable on a zero timeout so the clicked button's name still posts; HTMLFormElement.prototype.submit is wrapped for the 37 screens that submit programmatically.</t>
+        </is>
+      </c>
       <c r="D39" s="4" t="n"/>
       <c r="E39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>inc/cis_ajax/jquery_cutomer_branch_details.php</t>
+          <t>logs/.gitignore</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | Rewritten 196 -&gt; 30 lines. Renders one branch row, no database writes, login + csrf checked.</t>
+          <t>2026-10-01 | New. Keeps error logs out of the repository; logs/.htaccess denies web access.</t>
         </is>
       </c>
       <c r="C40" s="4" t="n"/>
@@ -1164,12 +1168,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>mst_customer_new.php</t>
+          <t>inc/common/form_rows.php</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | Branch rows moved off mst_customer_branch_temp. Existing branches render from mst_customer_branch; save loops the posted br_* arrays; add/edit/remove are DOM only.</t>
+          <t>2026-10-01 | New. Shared table row renderers - fnBranchRow(), fnItemGroupRow(). Used by both the page and its ajax endpoint so rows cannot drift apart.</t>
         </is>
       </c>
       <c r="C41" s="4" t="n"/>
@@ -1179,12 +1183,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>inc/cis_ajax/jquery_item_group_details.php</t>
+          <t>inc/cis_ajax/jquery_cutomer_branch_details.php</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | Rewritten 240 -&gt; 48 lines. Renders group item rows, no database writes.</t>
+          <t>2026-10-01 | Rewritten 196 -&gt; 30 lines. Renders one branch row, no database writes, login + csrf checked.</t>
         </is>
       </c>
       <c r="C42" s="4" t="n"/>
@@ -1194,12 +1198,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>mst_item_grouping.php</t>
+          <t>mst_customer_new.php</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | Group items moved off tbl_item_group_details_temp. Added the trade_items field that fnValidate() read but never existed. Read-only users now post qty and position as hidden fields.</t>
+          <t>2026-10-01 | Branch rows moved off mst_customer_branch_temp. Existing branches render from mst_customer_branch; save loops the posted br_* arrays; add/edit/remove are DOM only.</t>
         </is>
       </c>
       <c r="C43" s="4" t="n"/>
@@ -1209,12 +1213,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>inc/cis_ajax/jquery_modal_dc_pack_dets.php</t>
+          <t>inc/cis_ajax/jquery_item_group_details.php</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | Rewritten 392 -&gt; 80 lines. Renders the packing inputs from values sent by the page, no database access.</t>
+          <t>2026-10-01 | Rewritten 240 -&gt; 48 lines. Renders group item rows, no database writes.</t>
         </is>
       </c>
       <c r="C44" s="4" t="n"/>
@@ -1224,12 +1228,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>add_packing_box.php</t>
+          <t>mst_item_grouping.php</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | Removed. The packing modal no longer writes to the database, so nothing called it.</t>
+          <t>2026-10-01 | Group items moved off tbl_item_group_details_temp. Added the trade_items field that fnValidate() read but never existed. Read-only users now post qty and position as hidden fields.</t>
         </is>
       </c>
       <c r="C45" s="4" t="n"/>
@@ -1239,12 +1243,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>db/drop_temp_tables.sql</t>
+          <t>inc/cis_ajax/jquery_modal_dc_pack_dets.php</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | New. Drops the four temp tables once the screens are confirmed.</t>
+          <t>2026-10-01 | Rewritten 392 -&gt; 80 lines. Renders the packing inputs from values sent by the page, no database access.</t>
         </is>
       </c>
       <c r="C46" s="4" t="n"/>
@@ -1254,12 +1258,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>db/invoice_value_repair.sql</t>
+          <t>add_packing_box.php</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30 | New. Rebuilds inv_value / pro_value on rows zeroed by the edit screen, from net_value - tax_value.</t>
+          <t>2026-10-01 | Removed. The packing modal no longer writes to the database, so nothing called it.</t>
         </is>
       </c>
       <c r="C47" s="4" t="n"/>
@@ -1269,17 +1273,77 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>db/bie.sql</t>
+          <t>40 master and payroll forms</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+          <t>2026-10-01 | csrf + form token guard on every post handler, csrf_fields() in the form, db_begin/commit/rollback around every try. Covers all mst_* masters, payroll, attendance, mng_credit, pay_receipt, grn_pay_receipt, user_actions, mst_users_rights, supp_items, spare_mapping and the three approval modals.</t>
         </is>
       </c>
       <c r="C48" s="4" t="n"/>
       <c r="D48" s="4" t="n"/>
       <c r="E48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>mst_employee_add.php</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01 | csrf + rollback. Done by hand: a brace at column zero hid the UPDATE handler's end, and the SAVE handler redirects three ways by employee type so the commit had to go above the whole chain.</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>db/drop_temp_tables.sql</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01 | New. Drops the four temp tables once the screens are confirmed.</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>db/invoice_value_repair.sql</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30 | New. Rebuilds inv_value / pro_value on rows zeroed by the edit screen, from net_value - tax_value.</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>db/bie.sql</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1333,17 +1333,47 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>db/bie.sql</t>
+          <t>index.php</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+          <t>2026-10-01 | Login query was concatenated from $_REQUEST so the password check could be commented out - now a prepared statement with both values bound. csrf + form token on the post, session id regenerated and tokens dropped on success, failed logins written to the error log, prefilled admin@bie.com removed, autocomplete attributes added.</t>
         </is>
       </c>
       <c r="C52" s="4" t="n"/>
       <c r="D52" s="4" t="n"/>
       <c r="E52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>admin_multi_logins.php</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01 | Same concatenated login query, bound now. Removed the echo that printed the query with the password in it to the page. csrf + form token, session id regenerated on success. Its no-hash password compare left as it was - that changes who can use the screen.</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>db/bie.sql</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -801,7 +801,11 @@
           <t>2026-09-23 | Runs from $_REQUEST so the stock list View All link works; query now bound instead of interpolated.</t>
         </is>
       </c>
-      <c r="D17" s="4" t="n"/>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02 | Item is optional - blank reports every item for the branch and range, with an Item column added and the name joined in rather than looked up per row. Sort changed to trans_date DESC, auto_id DESC so the latest movement is on top. Heading and empty-state colspans now follow the column count.</t>
+        </is>
+      </c>
       <c r="E17" s="4" t="n"/>
     </row>
     <row r="18">

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1330,19 +1330,23 @@
           <t>2026-09-30 | New. Rebuilds inv_value / pro_value on rows zeroed by the edit screen, from net_value - tax_value.</t>
         </is>
       </c>
-      <c r="C51" s="4" t="n"/>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05 | Superseded, do not run. Checked against the live data its formula repairs nothing: tax_value is 0 on 106 of the 111 rows and net_value is the gross. Replaced by step 4 of post_upload_051026.sql.</t>
+        </is>
+      </c>
       <c r="D51" s="4" t="n"/>
       <c r="E51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>index.php</t>
+          <t>db/post_upload_051026.sql</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | Login query was concatenated from $_REQUEST so the password check could be commented out - now a prepared statement with both values bound. csrf + form token on the post, session id regenerated and tokens dropped on success, failed logins written to the error log, prefilled admin@bie.com removed, autocomplete attributes added.</t>
+          <t>2026-10-05 | New. Everything to run on the server after the file upload, checked against bie_db_051026.sql: widen tbl_user_rights.sm_id, clear the six clamped rights rows, grant sm_id 147/148, repair 111 zeroed invoice line amounts, drop the four temp tables.</t>
         </is>
       </c>
       <c r="C52" s="4" t="n"/>
@@ -1352,12 +1356,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>admin_multi_logins.php</t>
+          <t>index.php</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | Same concatenated login query, bound now. Removed the echo that printed the query with the password in it to the page. csrf + form token, session id regenerated on success. Its no-hash password compare left as it was - that changes who can use the screen.</t>
+          <t>2026-10-01 | Login query was concatenated from $_REQUEST so the password check could be commented out - now a prepared statement with both values bound. csrf + form token on the post, session id regenerated and tokens dropped on success, failed logins written to the error log, prefilled admin@bie.com removed, autocomplete attributes added.</t>
         </is>
       </c>
       <c r="C53" s="4" t="n"/>
@@ -1367,17 +1371,32 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>db/bie.sql</t>
+          <t>admin_multi_logins.php</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+          <t>2026-10-01 | Same concatenated login query, bound now. Removed the echo that printed the query with the password in it to the page. csrf + form token, session id regenerated on success. Its no-hash password compare left as it was - that changes who can use the screen.</t>
         </is>
       </c>
       <c r="C54" s="4" t="n"/>
       <c r="D54" s="4" t="n"/>
       <c r="E54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>db/bie.sql</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1390,7 +1409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1478,106 +1497,54 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>tbl_stock_flow</t>
+          <t>tbl_user_rights</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | trans_dir | Added CHAR(1). I = stock in (+), O = stock out (-). Backfilled GRN=I, INV/SALE=O.</t>
+          <t>2026-10-05 | sm_id | Signed TINYINT widened to SMALLINT. It stopped at 127, so the rights rows for the new menus (147, 148) were silently clamped to 127 and the menus never showed.</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | trans_remarks | Added VARCHAR(255). Reason / narration, mandatory on ADJ rows.</t>
+          <t>2026-10-05 | mm_id | Signed TINYINT widened to SMALLINT, same reason - it was two main menus away from the same limit.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | stock_field | Added VARCHAR(30). Which tbl_item_stock column was changed. Backfilled from mst_branch.</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | before_qty | INT to DECIMAL(12,3). Was truncating decimal stock.</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | trans_qty | INT to DECIMAL(12,3). Always a positive magnitude, direction is in trans_dir.</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | rcvd_qty | INT to DECIMAL(12,3).</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | after_qty | INT to DECIMAL(12,3).</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | reje_qty | INT to DECIMAL(12,3).</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | pend_qty | INT to DECIMAL(12,3).</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | trans_type | VARCHAR(8) to VARCHAR(10). Values GRN, INV, ADJ, OPEN, RET.</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | idx_sf_item_branch_date | Index added on (item_id, branch_id, trans_date) - what the reports filter on.</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | idx_sf_trans | Index added on (trans_type, trans_id).</t>
-        </is>
-      </c>
+          <t>2026-10-05 | (rows) | Six clamped rows deleted (users 2/6/7, sm_id 127 under main menus 3 and 20); sm_id 147 and 148 granted to whoever holds the parent menu.</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>tbl_stock_adjustment</t>
+          <t>tbl_invoice_details</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | (new table) | Header for every manual stock correction. One row per adjustment.</t>
+          <t>2026-10-05 | inv_value, tax_value | 111 rows across 35 invoices rebuilt as net_value / (1 + vat/100); tax_value rebuilt with them. Backup taken as tbl_invoice_details_bkp_051026.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | adj_id, adj_refno, adj_slno, adj_finyr | Key and reference number ADJ/nnnn/BIE/&lt;branch&gt;/&lt;finyr&gt;.</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | adj_date, branch_id, stock_field, item_id | What was adjusted, where, and which stock column.</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | adj_type, adj_qty, before_qty, after_qty | I = increase, D = decrease. adj_qty is always positive.</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | item_price, adj_reason, adj_status | Reason is mandatory. adj_status 1 = active, 0 = deleted.</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | created_by, created_dtm | Who made the adjustment and when.</t>
-        </is>
-      </c>
+          <t>2026-10-05 | cgst_per, sgst_per, igst_per, cgst_val, sgst_val, igst_val | Optional tidy on the same 111 rows only.</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
@@ -1588,50 +1555,106 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>mst_sub_menu</t>
+          <t>tbl_stock_flow</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | (row) | sm_id 147, mm_id 20 (Stores) - Stock Adjustment, stock_adjustment.php.</t>
+          <t>2026-09-22 | trans_dir | Added CHAR(1). I = stock in (+), O = stock out (-). Backfilled GRN=I, INV/SALE=O.</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 | (row) | sm_id 148, mm_id 3 (Item Masters) - Item Stock List, lst_item_stock.php.</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
-      <c r="J4" s="4" t="n"/>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n"/>
-      <c r="M4" s="4" t="n"/>
+          <t>2026-09-22 | trans_remarks | Added VARCHAR(255). Reason / narration, mandatory on ADJ rows.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | stock_field | Added VARCHAR(30). Which tbl_item_stock column was changed. Backfilled from mst_branch.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | before_qty | INT to DECIMAL(12,3). Was truncating decimal stock.</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | trans_qty | INT to DECIMAL(12,3). Always a positive magnitude, direction is in trans_dir.</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | rcvd_qty | INT to DECIMAL(12,3).</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | after_qty | INT to DECIMAL(12,3).</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | reje_qty | INT to DECIMAL(12,3).</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | pend_qty | INT to DECIMAL(12,3).</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | trans_type | VARCHAR(8) to VARCHAR(10). Values GRN, INV, ADJ, OPEN, RET.</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | idx_sf_item_branch_date | Index added on (item_id, branch_id, trans_date) - what the reports filter on.</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | idx_sf_trans | Index added on (trans_type, trans_id).</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>tbl_user_rights</t>
+          <t>tbl_stock_adjustment</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | (rows) | sm_id 147 granted to every user who already has the Stores menu.</t>
+          <t>2026-09-22 | (new table) | Header for every manual stock correction. One row per adjustment.</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 | (rows) | sm_id 148 granted to every user who already has the Item Masters menu.</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
+          <t>2026-09-22 | adj_id, adj_refno, adj_slno, adj_finyr | Key and reference number ADJ/nnnn/BIE/&lt;branch&gt;/&lt;finyr&gt;.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | adj_date, branch_id, stock_field, item_id | What was adjusted, where, and which stock column.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | adj_type, adj_qty, before_qty, after_qty | I = increase, D = decrease. adj_qty is always positive.</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | item_price, adj_reason, adj_status | Reason is mandatory. adj_status 1 = active, 0 = deleted.</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | created_by, created_dtm | Who made the adjustment and when.</t>
+        </is>
+      </c>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n"/>
       <c r="J5" s="4" t="n"/>
@@ -1642,15 +1665,19 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>tbl_item_stock</t>
+          <t>mst_sub_menu</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | (no schema change) | Qty columns are now only written through fnApplyStockMovement(), never directly.</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n"/>
+          <t>2026-09-22 | (row) | sm_id 147, mm_id 20 (Stores) - Stock Adjustment, stock_adjustment.php.</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23 | (row) | sm_id 148, mm_id 3 (Item Masters) - Item Stock List, lst_item_stock.php.</t>
+        </is>
+      </c>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
@@ -1665,17 +1692,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>tbl_cash_details</t>
+          <t>tbl_user_rights</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | cash_status | 2000.00 set to 0 (retired). Not deleted - old receipts hold cash_id 7 and history screens look the name up without checking status.</t>
+          <t>2026-09-22 | (rows) | sm_id 147 granted to every user who already has the Stores menu.</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | (rows) | Added cash_id 8 = 1.00, 9 = 2.00, 10 = 5.00, all active. Used by the Sales Receipt screen.</t>
+          <t>2026-09-23 | (rows) | sm_id 148 granted to every user who already has the Item Masters menu.</t>
         </is>
       </c>
       <c r="D7" s="4" t="n"/>
@@ -1692,19 +1719,15 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>mst_cash_details</t>
+          <t>tbl_item_stock</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | cash_status | 2000.00 set to 0 (retired). Same reasoning as tbl_cash_details.</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-25 | (rows) | Added cash_id 8 = 1.00, 9 = 2.00, 10 = 5.00, all active. Used by the Invoice and Credit screens.</t>
-        </is>
-      </c>
+          <t>2026-09-22 | (no schema change) | Qty columns are now only written through fnApplyStockMovement(), never directly.</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n"/>
       <c r="D8" s="4" t="n"/>
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="n"/>
@@ -1719,15 +1742,19 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>mst_customer_branch_temp</t>
+          <t>tbl_cash_details</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | (whole table) | No longer used. Branch rows live in the page and post back as arrays. Drop with db/drop_temp_tables.sql.</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n"/>
+          <t>2026-09-25 | cash_status | 2000.00 set to 0 (retired). Not deleted - old receipts hold cash_id 7 and history screens look the name up without checking status.</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | (rows) | Added cash_id 8 = 1.00, 9 = 2.00, 10 = 5.00, all active. Used by the Sales Receipt screen.</t>
+        </is>
+      </c>
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="n"/>
@@ -1742,15 +1769,19 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>tbl_item_group_details_temp</t>
+          <t>mst_cash_details</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | (whole table) | No longer used. Group items live in the page. Drop with db/drop_temp_tables.sql.</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n"/>
+          <t>2026-09-25 | cash_status | 2000.00 set to 0 (retired). Same reasoning as tbl_cash_details.</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | (rows) | Added cash_id 8 = 1.00, 9 = 2.00, 10 = 5.00, all active. Used by the Invoice and Credit screens.</t>
+        </is>
+      </c>
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
@@ -1765,12 +1796,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>tbl_dc_details_temp</t>
+          <t>mst_customer_branch_temp</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | (whole table) | No longer used. DC item rows are built in php and posted back as arrays. Drop with db/drop_temp_tables.sql.</t>
+          <t>2026-10-01 | (whole table) | No longer used. Branch rows live in the page and post back as arrays. Drop with db/drop_temp_tables.sql.</t>
         </is>
       </c>
       <c r="C11" s="4" t="n"/>
@@ -1788,12 +1819,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>tbl_package_box_details_temp</t>
+          <t>tbl_item_group_details_temp</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | (whole table) | No longer used. Packing rides on the DC item row as csv hidden fields. Drop with db/drop_temp_tables.sql.</t>
+          <t>2026-10-01 | (whole table) | No longer used. Group items live in the page. Drop with db/drop_temp_tables.sql.</t>
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
@@ -1811,12 +1842,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>tbl_invoice_details</t>
+          <t>tbl_dc_details_temp</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30 | inv_value | No schema change. Data repair - rows saved from the invoice edit screen had this zeroed by a bad field mapping. Rebuilt as net_value - tax_value where that agrees with qty x unit_price less discount.</t>
+          <t>2026-10-01 | (whole table) | No longer used. DC item rows are built in php and posted back as arrays. Drop with db/drop_temp_tables.sql.</t>
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
@@ -1834,12 +1865,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>tbl_proforma_details</t>
+          <t>tbl_package_box_details_temp</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30 | pro_value | No schema change. Same data repair as tbl_invoice_details.</t>
+          <t>2026-10-01 | (whole table) | No longer used. Packing rides on the DC item row as csv hidden fields. Drop with db/drop_temp_tables.sql.</t>
         </is>
       </c>
       <c r="C14" s="4" t="n"/>
@@ -1857,12 +1888,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>tbl_item_details</t>
+          <t>tbl_invoice_details</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | item_curr_stock | No change. Noted as dead - every write to it was already commented out. Branch columns in tbl_item_stock are the live balance.</t>
+          <t>2026-09-30 | inv_value | No schema change. Data repair - rows saved from the invoice edit screen had this zeroed by a bad field mapping. Rebuilt as net_value - tax_value where that agrees with qty x unit_price less discount.</t>
         </is>
       </c>
       <c r="C15" s="4" t="n"/>
@@ -1877,6 +1908,52 @@
       <c r="L15" s="4" t="n"/>
       <c r="M15" s="4" t="n"/>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>tbl_proforma_details</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30 | pro_value | No schema change. Same data repair as tbl_invoice_details.</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>tbl_item_details</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | item_curr_stock | No change. Noted as dead - every write to it was already commented out. Branch columns in tbl_item_stock are the live balance.</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -1349,7 +1349,11 @@
           <t>2026-10-05 | New. Everything to run on the server after the file upload, checked against bie_db_051026.sql: widen tbl_user_rights.sm_id, clear the six clamped rights rows, grant sm_id 147/148, repair 111 zeroed invoice line amounts, drop the four temp tables.</t>
         </is>
       </c>
-      <c r="C52" s="4" t="n"/>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05 | Step 7 split into five queries - as one UNION starting from information_schema, MariaDB looked for the plain tables there too (#1109). Step 3 now skips rights rows that already exist and step 4b keeps an existing backup, so the whole file is safe to run twice.</t>
+        </is>
+      </c>
       <c r="D52" s="4" t="n"/>
       <c r="E52" s="4" t="n"/>
     </row>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -1151,7 +1151,11 @@
           <t>2026-10-01 | Double-submit lock for every form. Buttons disable on a zero timeout so the clicked button's name still posts; HTMLFormElement.prototype.submit is wrapped for the 37 screens that submit programmatically.</t>
         </is>
       </c>
-      <c r="D39" s="4" t="n"/>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06 | Lock regression fixed. form.submit() called from inside a form's own onSubmit marked it locked, so the browser's real submission - the one carrying the clicked button name - was cancelled as a double click. About 50 screens posted without SAVE / UPDATE / Report and silently did nothing. The lock now leaves a submit() for the form already being submitted alone.</t>
+        </is>
+      </c>
       <c r="E39" s="4" t="n"/>
     </row>
     <row r="40">

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1345,46 +1345,46 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>db/post_upload_051026.sql</t>
+          <t>rpt_all_store_stock_list.php</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 | New. Everything to run on the server after the file upload, checked against bie_db_051026.sql: widen tbl_user_rights.sm_id, clear the six clamped rights rows, grant sm_id 147/148, repair 111 zeroed invoice line amounts, drop the four temp tables.</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05 | Step 7 split into five queries - as one UNION starting from information_schema, MariaDB looked for the plain tables there too (#1109). Step 3 now skips rights rows that already exist and step 4b keeps an existing backup, so the whole file is safe to run twice.</t>
-        </is>
-      </c>
+          <t>2026-10-06 | Branch columns driven from mst_branch. The header looped the branch table but the rows wrote only ho_stock and kl_stock, so Rajapalayam had a header and no cells. An item with no tbl_item_stock row now reads 0.000 instead of dropping its cells, the item lookup is bound, and the empty-state colspan follows the branch count.</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n"/>
       <c r="D52" s="4" t="n"/>
       <c r="E52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>index.php</t>
+          <t>db/post_upload_051026.sql</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | Login query was concatenated from $_REQUEST so the password check could be commented out - now a prepared statement with both values bound. csrf + form token on the post, session id regenerated and tokens dropped on success, failed logins written to the error log, prefilled admin@bie.com removed, autocomplete attributes added.</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n"/>
+          <t>2026-10-05 | New. Everything to run on the server after the file upload, checked against bie_db_051026.sql: widen tbl_user_rights.sm_id, clear the six clamped rights rows, grant sm_id 147/148, repair 111 zeroed invoice line amounts, drop the four temp tables.</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05 | Step 7 split into five queries - as one UNION starting from information_schema, MariaDB looked for the plain tables there too (#1109). Step 3 now skips rights rows that already exist and step 4b keeps an existing backup, so the whole file is safe to run twice.</t>
+        </is>
+      </c>
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>admin_multi_logins.php</t>
+          <t>index.php</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | Same concatenated login query, bound now. Removed the echo that printed the query with the password in it to the page. csrf + form token, session id regenerated on success. Its no-hash password compare left as it was - that changes who can use the screen.</t>
+          <t>2026-10-01 | Login query was concatenated from $_REQUEST so the password check could be commented out - now a prepared statement with both values bound. csrf + form token on the post, session id regenerated and tokens dropped on success, failed logins written to the error log, prefilled admin@bie.com removed, autocomplete attributes added.</t>
         </is>
       </c>
       <c r="C54" s="4" t="n"/>
@@ -1394,17 +1394,32 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>db/bie.sql</t>
+          <t>admin_multi_logins.php</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+          <t>2026-10-01 | Same concatenated login query, bound now. Removed the echo that printed the query with the password in it to the page. csrf + form token, session id regenerated on success. Its no-hash password compare left as it was - that changes who can use the screen.</t>
         </is>
       </c>
       <c r="C55" s="4" t="n"/>
       <c r="D55" s="4" t="n"/>
       <c r="E55" s="4" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>db/bie.sql</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -584,7 +584,11 @@
           <t>2026-09-24 | CSRF + form token guard on UPDATE and FINALIZE; transaction with rollback.</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06 | New GRN from PO: commit moved above header(); die; - every new GRN was being rolled back while the screen said recorded.</t>
+        </is>
+      </c>
       <c r="E6" s="4" t="n"/>
     </row>
     <row r="7">
@@ -684,7 +688,11 @@
           <t>2026-09-24 | CSRF + form token guard on SAVE/SAVE1/UPDATE; transaction with rollback.</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n"/>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06 | csrf token added to the multi UOM form - its Save and Update were always rejected.</t>
+        </is>
+      </c>
       <c r="E10" s="4" t="n"/>
     </row>
     <row r="11">
@@ -894,7 +902,11 @@
           <t>2026-09-24 | New. db_begin / db_commit / db_rollback, each a no-op if there is nothing to do.</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06 | db_value() added - one value read on the connection doing the work, sees this transaction's own rows.</t>
+        </is>
+      </c>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
     </row>
@@ -982,7 +994,11 @@
           <t>2026-10-01 | Item rows moved off tbl_dc_details_temp into a php array; packing moved off tbl_package_box_details_temp onto the item row as csv hidden fields. Box type counts done in javascript.</t>
         </is>
       </c>
-      <c r="D28" s="4" t="n"/>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06 | Packing keeps its own box type and dispatch qty (hidden pack_box_id / pack_dispatch_qty) and box counts read them, so editing a completed DC no longer zeroes packing.</t>
+        </is>
+      </c>
       <c r="E28" s="4" t="n"/>
     </row>
     <row r="29">
@@ -996,7 +1012,11 @@
           <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE/send_to_admin; transaction with rollback.</t>
         </is>
       </c>
-      <c r="C29" s="4" t="n"/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06 | Prepared qty read on $conn - a complete PO went to admin as partial.</t>
+        </is>
+      </c>
       <c r="D29" s="4" t="n"/>
       <c r="E29" s="4" t="n"/>
     </row>
@@ -1156,7 +1176,11 @@
           <t>2026-10-06 | Lock regression fixed. form.submit() called from inside a form's own onSubmit marked it locked, so the browser's real submission - the one carrying the clicked button name - was cancelled as a double click. About 50 screens posted without SAVE / UPDATE / Report and silently did nothing. The lock now leaves a submit() for the form already being submitted alone.</t>
         </is>
       </c>
-      <c r="E39" s="4" t="n"/>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06 | Lock rewritten again: no longer wraps form.submit() or cancels a submission, only disables buttons once a submit is under way and drops later clicks. Buttons with their own onclick (Send to Purchase, invoice, direct PO, GRN, credit, Generate PO) were posting without their name.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1360,31 +1384,27 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>db/post_upload_051026.sql</t>
+          <t>grn_pay_receipt.php</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 | New. Everything to run on the server after the file upload, checked against bie_db_051026.sql: widen tbl_user_rights.sm_id, clear the six clamped rights rows, grant sm_id 147/148, repair 111 zeroed invoice line amounts, drop the four temp tables.</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05 | Step 7 split into five queries - as one UNION starting from information_schema, MariaDB looked for the plain tables there too (#1109). Step 3 now skips rights rows that already exist and step 4b keeps an existing backup, so the whole file is safe to run twice.</t>
-        </is>
-      </c>
+          <t>2026-10-06 | Paid total read on $conn - a GRN paid in full was marked partly paid.</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n"/>
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>index.php</t>
+          <t>emp_advance_return_payment.php</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | Login query was concatenated from $_REQUEST so the password check could be commented out - now a prepared statement with both values bound. csrf + form token on the post, session id regenerated and tokens dropped on success, failed logins written to the error log, prefilled admin@bie.com removed, autocomplete attributes added.</t>
+          <t>2026-10-06 | Repaid total read on $conn - it left out the repayment being saved.</t>
         </is>
       </c>
       <c r="C54" s="4" t="n"/>
@@ -1394,12 +1414,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>admin_multi_logins.php</t>
+          <t>import_attendance.php</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | Same concatenated login query, bound now. Removed the echo that printed the query with the password in it to the page. csrf + form token, session id regenerated on success. Its no-hash password compare left as it was - that changes who can use the screen.</t>
+          <t>2026-10-06 | Punch check read on $conn - re-importing an overlapping file dropped those punches.</t>
         </is>
       </c>
       <c r="C55" s="4" t="n"/>
@@ -1409,17 +1429,111 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>db/bie.sql</t>
+          <t>modal_so_det.php</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+          <t>2026-10-06 | Loads csrf and txn helpers itself - opened on its own it died on csrf_fields().</t>
         </is>
       </c>
       <c r="C56" s="4" t="n"/>
       <c r="D56" s="4" t="n"/>
       <c r="E56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>modal_so_reject_dets.php</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06 | Loads csrf and txn helpers itself - opened on its own it died on csrf_fields().</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>modal_grn_reject_dets.php</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06 | Loads csrf and txn helpers itself - opened on its own it died on csrf_fields().</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>db/post_upload_051026.sql</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05 | New. Everything to run on the server after the file upload, checked against bie_db_051026.sql: widen tbl_user_rights.sm_id, clear the six clamped rights rows, grant sm_id 147/148, repair 111 zeroed invoice line amounts, drop the four temp tables.</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05 | Step 7 split into five queries - as one UNION starting from information_schema, MariaDB looked for the plain tables there too (#1109). Step 3 now skips rights rows that already exist and step 4b keeps an existing backup, so the whole file is safe to run twice.</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="n"/>
+      <c r="E59" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>index.php</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01 | Login query was concatenated from $_REQUEST so the password check could be commented out - now a prepared statement with both values bound. csrf + form token on the post, session id regenerated and tokens dropped on success, failed logins written to the error log, prefilled admin@bie.com removed, autocomplete attributes added.</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n"/>
+      <c r="D60" s="4" t="n"/>
+      <c r="E60" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>admin_multi_logins.php</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01 | Same concatenated login query, bound now. Removed the echo that printed the query with the password in it to the page. csrf + form token, session id regenerated on success. Its no-hash password compare left as it was - that changes who can use the screen.</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="4" t="n"/>
+      <c r="E61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>db/bie.sql</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="n"/>
+      <c r="D62" s="4" t="n"/>
+      <c r="E62" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -693,7 +693,11 @@
           <t>2026-10-06 | csrf token added to the multi UOM form - its Save and Update were always rejected.</t>
         </is>
       </c>
-      <c r="E10" s="4" t="n"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06 | Multi UOM insert binds 0 for min / max discount when the row has no such field - it bound null and always failed on the NOT NULL column.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1478,46 +1478,46 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>db/post_upload_051026.sql</t>
+          <t>db/post_upload_061026.sql</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 | New. Everything to run on the server after the file upload, checked against bie_db_051026.sql: widen tbl_user_rights.sm_id, clear the six clamped rights rows, grant sm_id 147/148, repair 111 zeroed invoice line amounts, drop the four temp tables.</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05 | Step 7 split into five queries - as one UNION starting from information_schema, MariaDB looked for the plain tables there too (#1109). Step 3 now skips rights rows that already exist and step 4b keeps an existing backup, so the whole file is safe to run twice.</t>
-        </is>
-      </c>
+          <t>2026-10-06 | New. Checked against bie_db_061026.sql: every earlier change is live; adds the four audit columns mst_principal.php writes but the table never had.</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n"/>
       <c r="D59" s="4" t="n"/>
       <c r="E59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>index.php</t>
+          <t>db/post_upload_051026.sql</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | Login query was concatenated from $_REQUEST so the password check could be commented out - now a prepared statement with both values bound. csrf + form token on the post, session id regenerated and tokens dropped on success, failed logins written to the error log, prefilled admin@bie.com removed, autocomplete attributes added.</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="n"/>
+          <t>2026-10-05 | New. Everything to run on the server after the file upload, checked against bie_db_051026.sql: widen tbl_user_rights.sm_id, clear the six clamped rights rows, grant sm_id 147/148, repair 111 zeroed invoice line amounts, drop the four temp tables.</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05 | Step 7 split into five queries - as one UNION starting from information_schema, MariaDB looked for the plain tables there too (#1109). Step 3 now skips rights rows that already exist and step 4b keeps an existing backup, so the whole file is safe to run twice.</t>
+        </is>
+      </c>
       <c r="D60" s="4" t="n"/>
       <c r="E60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>admin_multi_logins.php</t>
+          <t>index.php</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | Same concatenated login query, bound now. Removed the echo that printed the query with the password in it to the page. csrf + form token, session id regenerated on success. Its no-hash password compare left as it was - that changes who can use the screen.</t>
+          <t>2026-10-01 | Login query was concatenated from $_REQUEST so the password check could be commented out - now a prepared statement with both values bound. csrf + form token on the post, session id regenerated and tokens dropped on success, failed logins written to the error log, prefilled admin@bie.com removed, autocomplete attributes added.</t>
         </is>
       </c>
       <c r="C61" s="4" t="n"/>
@@ -1527,17 +1527,32 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>db/bie.sql</t>
+          <t>admin_multi_logins.php</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+          <t>2026-10-01 | Same concatenated login query, bound now. Removed the echo that printed the query with the password in it to the page. csrf + form token, session id regenerated on success. Its no-hash password compare left as it was - that changes who can use the screen.</t>
         </is>
       </c>
       <c r="C62" s="4" t="n"/>
       <c r="D62" s="4" t="n"/>
       <c r="E62" s="4" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>db/bie.sql</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n"/>
+      <c r="D63" s="4" t="n"/>
+      <c r="E63" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1550,7 +1565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1638,24 +1653,16 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>tbl_user_rights</t>
+          <t>mst_principal</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 | sm_id | Signed TINYINT widened to SMALLINT. It stopped at 127, so the rights rows for the new menus (147, 148) were silently clamped to 127 and the menus never showed.</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05 | mm_id | Signed TINYINT widened to SMALLINT, same reason - it was two main menus away from the same limit.</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05 | (rows) | Six clamped rows deleted (users 2/6/7, sm_id 127 under main menus 3 and 20); sm_id 147 and 148 granted to whoever holds the parent menu.</t>
-        </is>
-      </c>
+          <t>2026-10-06 | created_by, created_dtm, modify_by, modify_dtm | Added - mst_principal.php writes them on save and update, so both always failed with Unknown column. Existing rows get 0 / NULL.</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
@@ -1669,20 +1676,24 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>tbl_invoice_details</t>
+          <t>tbl_user_rights</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 | inv_value, tax_value | 111 rows across 35 invoices rebuilt as net_value / (1 + vat/100); tax_value rebuilt with them. Backup taken as tbl_invoice_details_bkp_051026.</t>
+          <t>2026-10-05 | sm_id | Signed TINYINT widened to SMALLINT. It stopped at 127, so the rights rows for the new menus (147, 148) were silently clamped to 127 and the menus never showed.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 | cgst_per, sgst_per, igst_per, cgst_val, sgst_val, igst_val | Optional tidy on the same 111 rows only.</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n"/>
+          <t>2026-10-05 | mm_id | Signed TINYINT widened to SMALLINT, same reason - it was two main menus away from the same limit.</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05 | (rows) | Six clamped rows deleted (users 2/6/7, sm_id 127 under main menus 3 and 20); sm_id 147 and 148 granted to whoever holds the parent menu.</t>
+        </is>
+      </c>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
@@ -1696,133 +1707,133 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>tbl_stock_flow</t>
+          <t>tbl_invoice_details</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | trans_dir | Added CHAR(1). I = stock in (+), O = stock out (-). Backfilled GRN=I, INV/SALE=O.</t>
+          <t>2026-10-05 | inv_value, tax_value | 111 rows across 35 invoices rebuilt as net_value / (1 + vat/100); tax_value rebuilt with them. Backup taken as tbl_invoice_details_bkp_051026.</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | trans_remarks | Added VARCHAR(255). Reason / narration, mandatory on ADJ rows.</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | stock_field | Added VARCHAR(30). Which tbl_item_stock column was changed. Backfilled from mst_branch.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | before_qty | INT to DECIMAL(12,3). Was truncating decimal stock.</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | trans_qty | INT to DECIMAL(12,3). Always a positive magnitude, direction is in trans_dir.</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | rcvd_qty | INT to DECIMAL(12,3).</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | after_qty | INT to DECIMAL(12,3).</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | reje_qty | INT to DECIMAL(12,3).</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | pend_qty | INT to DECIMAL(12,3).</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | trans_type | VARCHAR(8) to VARCHAR(10). Values GRN, INV, ADJ, OPEN, RET.</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | idx_sf_item_branch_date | Index added on (item_id, branch_id, trans_date) - what the reports filter on.</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | idx_sf_trans | Index added on (trans_type, trans_id).</t>
-        </is>
-      </c>
+          <t>2026-10-05 | cgst_per, sgst_per, igst_per, cgst_val, sgst_val, igst_val | Optional tidy on the same 111 rows only.</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>tbl_stock_adjustment</t>
+          <t>tbl_stock_flow</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | (new table) | Header for every manual stock correction. One row per adjustment.</t>
+          <t>2026-09-22 | trans_dir | Added CHAR(1). I = stock in (+), O = stock out (-). Backfilled GRN=I, INV/SALE=O.</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | adj_id, adj_refno, adj_slno, adj_finyr | Key and reference number ADJ/nnnn/BIE/&lt;branch&gt;/&lt;finyr&gt;.</t>
+          <t>2026-09-22 | trans_remarks | Added VARCHAR(255). Reason / narration, mandatory on ADJ rows.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | adj_date, branch_id, stock_field, item_id | What was adjusted, where, and which stock column.</t>
+          <t>2026-09-22 | stock_field | Added VARCHAR(30). Which tbl_item_stock column was changed. Backfilled from mst_branch.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | adj_type, adj_qty, before_qty, after_qty | I = increase, D = decrease. adj_qty is always positive.</t>
+          <t>2026-09-22 | before_qty | INT to DECIMAL(12,3). Was truncating decimal stock.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | item_price, adj_reason, adj_status | Reason is mandatory. adj_status 1 = active, 0 = deleted.</t>
+          <t>2026-09-22 | trans_qty | INT to DECIMAL(12,3). Always a positive magnitude, direction is in trans_dir.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | created_by, created_dtm | Who made the adjustment and when.</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
+          <t>2026-09-22 | rcvd_qty | INT to DECIMAL(12,3).</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | after_qty | INT to DECIMAL(12,3).</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | reje_qty | INT to DECIMAL(12,3).</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | pend_qty | INT to DECIMAL(12,3).</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | trans_type | VARCHAR(8) to VARCHAR(10). Values GRN, INV, ADJ, OPEN, RET.</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | idx_sf_item_branch_date | Index added on (item_id, branch_id, trans_date) - what the reports filter on.</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | idx_sf_trans | Index added on (trans_type, trans_id).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>mst_sub_menu</t>
+          <t>tbl_stock_adjustment</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | (row) | sm_id 147, mm_id 20 (Stores) - Stock Adjustment, stock_adjustment.php.</t>
+          <t>2026-09-22 | (new table) | Header for every manual stock correction. One row per adjustment.</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 | (row) | sm_id 148, mm_id 3 (Item Masters) - Item Stock List, lst_item_stock.php.</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
+          <t>2026-09-22 | adj_id, adj_refno, adj_slno, adj_finyr | Key and reference number ADJ/nnnn/BIE/&lt;branch&gt;/&lt;finyr&gt;.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | adj_date, branch_id, stock_field, item_id | What was adjusted, where, and which stock column.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | adj_type, adj_qty, before_qty, after_qty | I = increase, D = decrease. adj_qty is always positive.</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | item_price, adj_reason, adj_status | Reason is mandatory. adj_status 1 = active, 0 = deleted.</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | created_by, created_dtm | Who made the adjustment and when.</t>
+        </is>
+      </c>
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
@@ -1833,17 +1844,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>tbl_user_rights</t>
+          <t>mst_sub_menu</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | (rows) | sm_id 147 granted to every user who already has the Stores menu.</t>
+          <t>2026-09-22 | (row) | sm_id 147, mm_id 20 (Stores) - Stock Adjustment, stock_adjustment.php.</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 | (rows) | sm_id 148 granted to every user who already has the Item Masters menu.</t>
+          <t>2026-09-23 | (row) | sm_id 148, mm_id 3 (Item Masters) - Item Stock List, lst_item_stock.php.</t>
         </is>
       </c>
       <c r="D7" s="4" t="n"/>
@@ -1860,15 +1871,19 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>tbl_item_stock</t>
+          <t>tbl_user_rights</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | (no schema change) | Qty columns are now only written through fnApplyStockMovement(), never directly.</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n"/>
+          <t>2026-09-22 | (rows) | sm_id 147 granted to every user who already has the Stores menu.</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23 | (rows) | sm_id 148 granted to every user who already has the Item Masters menu.</t>
+        </is>
+      </c>
       <c r="D8" s="4" t="n"/>
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="n"/>
@@ -1883,19 +1898,15 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>tbl_cash_details</t>
+          <t>tbl_item_stock</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | cash_status | 2000.00 set to 0 (retired). Not deleted - old receipts hold cash_id 7 and history screens look the name up without checking status.</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-25 | (rows) | Added cash_id 8 = 1.00, 9 = 2.00, 10 = 5.00, all active. Used by the Sales Receipt screen.</t>
-        </is>
-      </c>
+          <t>2026-09-22 | (no schema change) | Qty columns are now only written through fnApplyStockMovement(), never directly.</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="n"/>
@@ -1910,17 +1921,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>mst_cash_details</t>
+          <t>tbl_cash_details</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | cash_status | 2000.00 set to 0 (retired). Same reasoning as tbl_cash_details.</t>
+          <t>2026-09-25 | cash_status | 2000.00 set to 0 (retired). Not deleted - old receipts hold cash_id 7 and history screens look the name up without checking status.</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | (rows) | Added cash_id 8 = 1.00, 9 = 2.00, 10 = 5.00, all active. Used by the Invoice and Credit screens.</t>
+          <t>2026-09-25 | (rows) | Added cash_id 8 = 1.00, 9 = 2.00, 10 = 5.00, all active. Used by the Sales Receipt screen.</t>
         </is>
       </c>
       <c r="D10" s="4" t="n"/>
@@ -1937,15 +1948,19 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>mst_customer_branch_temp</t>
+          <t>mst_cash_details</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | (whole table) | No longer used. Branch rows live in the page and post back as arrays. Drop with db/drop_temp_tables.sql.</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n"/>
+          <t>2026-09-25 | cash_status | 2000.00 set to 0 (retired). Same reasoning as tbl_cash_details.</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | (rows) | Added cash_id 8 = 1.00, 9 = 2.00, 10 = 5.00, all active. Used by the Invoice and Credit screens.</t>
+        </is>
+      </c>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
@@ -1960,12 +1975,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>tbl_item_group_details_temp</t>
+          <t>mst_customer_branch_temp</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | (whole table) | No longer used. Group items live in the page. Drop with db/drop_temp_tables.sql.</t>
+          <t>2026-10-01 | (whole table) | No longer used. Branch rows live in the page and post back as arrays. Drop with db/drop_temp_tables.sql.</t>
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
@@ -1983,12 +1998,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>tbl_dc_details_temp</t>
+          <t>tbl_item_group_details_temp</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | (whole table) | No longer used. DC item rows are built in php and posted back as arrays. Drop with db/drop_temp_tables.sql.</t>
+          <t>2026-10-01 | (whole table) | No longer used. Group items live in the page. Drop with db/drop_temp_tables.sql.</t>
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
@@ -2006,12 +2021,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>tbl_package_box_details_temp</t>
+          <t>tbl_dc_details_temp</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | (whole table) | No longer used. Packing rides on the DC item row as csv hidden fields. Drop with db/drop_temp_tables.sql.</t>
+          <t>2026-10-01 | (whole table) | No longer used. DC item rows are built in php and posted back as arrays. Drop with db/drop_temp_tables.sql.</t>
         </is>
       </c>
       <c r="C14" s="4" t="n"/>
@@ -2029,12 +2044,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>tbl_invoice_details</t>
+          <t>tbl_package_box_details_temp</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30 | inv_value | No schema change. Data repair - rows saved from the invoice edit screen had this zeroed by a bad field mapping. Rebuilt as net_value - tax_value where that agrees with qty x unit_price less discount.</t>
+          <t>2026-10-01 | (whole table) | No longer used. Packing rides on the DC item row as csv hidden fields. Drop with db/drop_temp_tables.sql.</t>
         </is>
       </c>
       <c r="C15" s="4" t="n"/>
@@ -2052,12 +2067,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>tbl_proforma_details</t>
+          <t>tbl_invoice_details</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30 | pro_value | No schema change. Same data repair as tbl_invoice_details.</t>
+          <t>2026-09-30 | inv_value | No schema change. Data repair - rows saved from the invoice edit screen had this zeroed by a bad field mapping. Rebuilt as net_value - tax_value where that agrees with qty x unit_price less discount.</t>
         </is>
       </c>
       <c r="C16" s="4" t="n"/>
@@ -2075,12 +2090,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>tbl_item_details</t>
+          <t>tbl_proforma_details</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | item_curr_stock | No change. Noted as dead - every write to it was already commented out. Branch columns in tbl_item_stock are the live balance.</t>
+          <t>2026-09-30 | pro_value | No schema change. Same data repair as tbl_invoice_details.</t>
         </is>
       </c>
       <c r="C17" s="4" t="n"/>
@@ -2095,6 +2110,29 @@
       <c r="L17" s="4" t="n"/>
       <c r="M17" s="4" t="n"/>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>tbl_item_details</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | item_curr_stock | No change. Noted as dead - every write to it was already commented out. Branch columns in tbl_item_stock are the live balance.</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -471,6 +471,7 @@
     <col width="62" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -499,6 +500,11 @@
           <t>Change 4</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Change 5</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -514,6 +520,7 @@
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -533,6 +540,7 @@
       </c>
       <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -548,6 +556,7 @@
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -567,6 +576,7 @@
       </c>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -589,7 +599,12 @@
           <t>2026-10-06 | New GRN from PO: commit moved above header(); die; - every new GRN was being rolled back while the screen said recorded.</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -617,6 +632,11 @@
           <t>2026-09-30 | Edit view posted quo_value, a column tbl_invoice_details does not have, wiping inv_value to 0. Now posts inv_value.</t>
         </is>
       </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -644,6 +664,11 @@
           <t>2026-09-30 | Edit view posted quo_value, a column tbl_invoice_details does not have, wiping inv_value to 0. Now posts inv_value.</t>
         </is>
       </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -671,6 +696,11 @@
           <t>2026-09-30 | Edit view posted quo_value, a column tbl_invoice_details does not have, wiping inv_value to 0. Now posts inv_value. Percentage charge base read from the raw hidden total instead of the comma-formatted text.</t>
         </is>
       </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8. Package dropdown renamed pack_pick so it cannot replace the pack_id[] rows.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -698,6 +728,11 @@
           <t>2026-10-06 | Multi UOM insert binds 0 for min / max discount when the row has no such field - it bound null and always failed on the NOT NULL column.</t>
         </is>
       </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -717,6 +752,7 @@
       </c>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -732,6 +768,7 @@
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -747,6 +784,7 @@
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -766,6 +804,7 @@
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -781,6 +820,7 @@
       <c r="C15" s="4" t="n"/>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -796,6 +836,7 @@
       <c r="C16" s="4" t="n"/>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -819,6 +860,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -834,6 +876,7 @@
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -849,6 +892,7 @@
       <c r="C19" s="4" t="n"/>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -864,6 +908,7 @@
       <c r="C20" s="4" t="n"/>
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -879,6 +924,7 @@
       <c r="C21" s="4" t="n"/>
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -894,6 +940,7 @@
       <c r="C22" s="4" t="n"/>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -913,6 +960,7 @@
       </c>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -932,6 +980,7 @@
       </c>
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -944,9 +993,14 @@
           <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE/ACCOUNTS; try/catch added (handlers had none); transaction with rollback.</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
+        </is>
+      </c>
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -959,9 +1013,14 @@
           <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE/FINALIZE; transaction with rollback.</t>
         </is>
       </c>
-      <c r="C26" s="4" t="n"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8. Package dropdown renamed pack_pick so it cannot replace the pack_id[] rows.</t>
+        </is>
+      </c>
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -979,8 +1038,13 @@
           <t>2026-09-30 | Edit view posted quo_value, a column tbl_proforma_details does not have, wiping pro_value to 0. Now posts pro_value.</t>
         </is>
       </c>
-      <c r="D27" s="4" t="n"/>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
+        </is>
+      </c>
       <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1003,7 +1067,12 @@
           <t>2026-10-06 | Packing keeps its own box type and dispatch qty (hidden pack_box_id / pack_dispatch_qty) and box counts read them, so editing a completed DC no longer zeroes packing.</t>
         </is>
       </c>
-      <c r="E28" s="4" t="n"/>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1023,6 +1092,7 @@
       </c>
       <c r="D29" s="4" t="n"/>
       <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1035,9 +1105,14 @@
           <t>2026-09-24 | CSRF + form token guard on Draft/UPDATE/FINALIZE; transaction with rollback. Commit moved before the redirect that ends the success path.</t>
         </is>
       </c>
-      <c r="C30" s="4" t="n"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
+        </is>
+      </c>
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1050,9 +1125,14 @@
           <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE/FINALIZE; transaction with rollback. Commit moved before the redirect that ends the success path.</t>
         </is>
       </c>
-      <c r="C31" s="4" t="n"/>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
+        </is>
+      </c>
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1065,9 +1145,14 @@
           <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE; transaction with rollback.</t>
         </is>
       </c>
-      <c r="C32" s="4" t="n"/>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
+        </is>
+      </c>
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1080,9 +1165,14 @@
           <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE/FINALIZE; transaction with rollback.</t>
         </is>
       </c>
-      <c r="C33" s="4" t="n"/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
+        </is>
+      </c>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1098,6 +1188,7 @@
       <c r="C34" s="4" t="n"/>
       <c r="D34" s="4" t="n"/>
       <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1113,6 +1204,7 @@
       <c r="C35" s="4" t="n"/>
       <c r="D35" s="4" t="n"/>
       <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1125,9 +1217,14 @@
           <t>2026-09-25 | Cash denomination dropdown ordered by value instead of cash_id, so 1/2/5 sit at the top.</t>
         </is>
       </c>
-      <c r="C36" s="4" t="n"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
+        </is>
+      </c>
       <c r="D36" s="4" t="n"/>
       <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1140,9 +1237,14 @@
           <t>2026-09-25 | Cash denomination dropdown ordered by value instead of cash_id.</t>
         </is>
       </c>
-      <c r="C37" s="4" t="n"/>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
+        </is>
+      </c>
       <c r="D37" s="4" t="n"/>
       <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1158,6 +1260,7 @@
       <c r="C38" s="4" t="n"/>
       <c r="D38" s="4" t="n"/>
       <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1185,6 +1288,7 @@
           <t>2026-10-06 | Lock rewritten again: no longer wraps form.submit() or cancels a submission, only disables buttons once a submit is under way and drops later clicks. Buttons with their own onclick (Send to Purchase, invoice, direct PO, GRN, credit, Generate PO) were posting without their name.</t>
         </is>
       </c>
+      <c r="F39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1200,6 +1304,7 @@
       <c r="C40" s="4" t="n"/>
       <c r="D40" s="4" t="n"/>
       <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1215,6 +1320,7 @@
       <c r="C41" s="4" t="n"/>
       <c r="D41" s="4" t="n"/>
       <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1230,6 +1336,7 @@
       <c r="C42" s="4" t="n"/>
       <c r="D42" s="4" t="n"/>
       <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1242,9 +1349,14 @@
           <t>2026-10-01 | Branch rows moved off mst_customer_branch_temp. Existing branches render from mst_customer_branch; save loops the posted br_* arrays; add/edit/remove are DOM only.</t>
         </is>
       </c>
-      <c r="C43" s="4" t="n"/>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
+        </is>
+      </c>
       <c r="D43" s="4" t="n"/>
       <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1260,6 +1372,7 @@
       <c r="C44" s="4" t="n"/>
       <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1272,9 +1385,14 @@
           <t>2026-10-01 | Group items moved off tbl_item_group_details_temp. Added the trade_items field that fnValidate() read but never existed. Read-only users now post qty and position as hidden fields.</t>
         </is>
       </c>
-      <c r="C45" s="4" t="n"/>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
+        </is>
+      </c>
       <c r="D45" s="4" t="n"/>
       <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1290,6 +1408,7 @@
       <c r="C46" s="4" t="n"/>
       <c r="D46" s="4" t="n"/>
       <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1305,6 +1424,7 @@
       <c r="C47" s="4" t="n"/>
       <c r="D47" s="4" t="n"/>
       <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1320,6 +1440,7 @@
       <c r="C48" s="4" t="n"/>
       <c r="D48" s="4" t="n"/>
       <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1332,9 +1453,14 @@
           <t>2026-10-01 | csrf + rollback. Done by hand: a brace at column zero hid the UPDATE handler's end, and the SAVE handler redirects three ways by employee type so the commit had to go above the whole chain.</t>
         </is>
       </c>
-      <c r="C49" s="4" t="n"/>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
+        </is>
+      </c>
       <c r="D49" s="4" t="n"/>
       <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1350,6 +1476,7 @@
       <c r="C50" s="4" t="n"/>
       <c r="D50" s="4" t="n"/>
       <c r="E50" s="4" t="n"/>
+      <c r="F50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1369,6 +1496,7 @@
       </c>
       <c r="D51" s="4" t="n"/>
       <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1384,6 +1512,7 @@
       <c r="C52" s="4" t="n"/>
       <c r="D52" s="4" t="n"/>
       <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1396,9 +1525,14 @@
           <t>2026-10-06 | Paid total read on $conn - a GRN paid in full was marked partly paid.</t>
         </is>
       </c>
-      <c r="C53" s="4" t="n"/>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
+        </is>
+      </c>
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1414,6 +1548,7 @@
       <c r="C54" s="4" t="n"/>
       <c r="D54" s="4" t="n"/>
       <c r="E54" s="4" t="n"/>
+      <c r="F54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1429,6 +1564,7 @@
       <c r="C55" s="4" t="n"/>
       <c r="D55" s="4" t="n"/>
       <c r="E55" s="4" t="n"/>
+      <c r="F55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1444,6 +1580,7 @@
       <c r="C56" s="4" t="n"/>
       <c r="D56" s="4" t="n"/>
       <c r="E56" s="4" t="n"/>
+      <c r="F56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1459,6 +1596,7 @@
       <c r="C57" s="4" t="n"/>
       <c r="D57" s="4" t="n"/>
       <c r="E57" s="4" t="n"/>
+      <c r="F57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1474,85 +1612,123 @@
       <c r="C58" s="4" t="n"/>
       <c r="D58" s="4" t="n"/>
       <c r="E58" s="4" t="n"/>
+      <c r="F58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>db/post_upload_061026.sql</t>
+          <t>spare_mapping.php</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06 | New. Checked against bie_db_061026.sql: every earlier change is live; adds the four audit columns mst_principal.php writes but the table never had.</t>
+          <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
         </is>
       </c>
       <c r="C59" s="4" t="n"/>
       <c r="D59" s="4" t="n"/>
       <c r="E59" s="4" t="n"/>
+      <c r="F59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>db/post_upload_051026.sql</t>
+          <t>inc/common/functions.php</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 | New. Everything to run on the server after the file upload, checked against bie_db_051026.sql: widen tbl_user_rights.sm_id, clear the six clamped rights rows, grant sm_id 147/148, repair 111 zeroed invoice line amounts, drop the four temp tables.</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05 | Step 7 split into five queries - as one UNION starting from information_schema, MariaDB looked for the plain tables there too (#1109). Step 3 now skips rights rows that already exist and step 4b keeps an existing backup, so the whole file is safe to run twice.</t>
-        </is>
-      </c>
+          <t>2026-10-07 | fnRowCount() added - posted row count, 0 for a missing or single value.</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n"/>
       <c r="D60" s="4" t="n"/>
       <c r="E60" s="4" t="n"/>
+      <c r="F60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>index.php</t>
+          <t>db/post_upload_061026.sql</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | Login query was concatenated from $_REQUEST so the password check could be commented out - now a prepared statement with both values bound. csrf + form token on the post, session id regenerated and tokens dropped on success, failed logins written to the error log, prefilled admin@bie.com removed, autocomplete attributes added.</t>
+          <t>2026-10-06 | New. Checked against bie_db_061026.sql: every earlier change is live; adds the four audit columns mst_principal.php writes but the table never had.</t>
         </is>
       </c>
       <c r="C61" s="4" t="n"/>
       <c r="D61" s="4" t="n"/>
       <c r="E61" s="4" t="n"/>
+      <c r="F61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>admin_multi_logins.php</t>
+          <t>db/post_upload_051026.sql</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | Same concatenated login query, bound now. Removed the echo that printed the query with the password in it to the page. csrf + form token, session id regenerated on success. Its no-hash password compare left as it was - that changes who can use the screen.</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="n"/>
+          <t>2026-10-05 | New. Everything to run on the server after the file upload, checked against bie_db_051026.sql: widen tbl_user_rights.sm_id, clear the six clamped rights rows, grant sm_id 147/148, repair 111 zeroed invoice line amounts, drop the four temp tables.</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05 | Step 7 split into five queries - as one UNION starting from information_schema, MariaDB looked for the plain tables there too (#1109). Step 3 now skips rights rows that already exist and step 4b keeps an existing backup, so the whole file is safe to run twice.</t>
+        </is>
+      </c>
       <c r="D62" s="4" t="n"/>
       <c r="E62" s="4" t="n"/>
+      <c r="F62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>db/bie.sql</t>
+          <t>index.php</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+          <t>2026-10-01 | Login query was concatenated from $_REQUEST so the password check could be commented out - now a prepared statement with both values bound. csrf + form token on the post, session id regenerated and tokens dropped on success, failed logins written to the error log, prefilled admin@bie.com removed, autocomplete attributes added.</t>
         </is>
       </c>
       <c r="C63" s="4" t="n"/>
       <c r="D63" s="4" t="n"/>
       <c r="E63" s="4" t="n"/>
+      <c r="F63" s="4" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>admin_multi_logins.php</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01 | Same concatenated login query, bound now. Removed the echo that printed the query with the password in it to the page. csrf + form token, session id regenerated on success. Its no-hash password compare left as it was - that changes who can use the screen.</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="4" t="n"/>
+      <c r="F64" s="4" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>db/bie.sql</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="4" t="n"/>
+      <c r="E65" s="4" t="n"/>
+      <c r="F65" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1649,12 +1649,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>db/post_upload_061026.sql</t>
+          <t>inc/auto/item_search_lib.php</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06 | New. Checked against bie_db_061026.sql: every earlier change is live; adds the four audit columns mst_principal.php writes but the table never had.</t>
+          <t>2026-10-07 | New. Shared item search: best 30 matches in one query, stock fields for those items in one more, branch column names checked against tbl_item_stock.</t>
         </is>
       </c>
       <c r="C61" s="4" t="n"/>
@@ -1665,19 +1665,15 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>db/post_upload_051026.sql</t>
+          <t>inc/auto/select_quotation_items.php</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 | New. Everything to run on the server after the file upload, checked against bie_db_051026.sql: widen tbl_user_rights.sm_id, clear the six clamped rights rows, grant sm_id 147/148, repair 111 zeroed invoice line amounts, drop the four temp tables.</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05 | Step 7 split into five queries - as one UNION starting from information_schema, MariaDB looked for the plain tables there too (#1109). Step 3 now skips rights rows that already exist and step 4b keeps an existing backup, so the whole file is safe to run twice.</t>
-        </is>
-      </c>
+          <t>2026-10-07 | Rewritten on item_search_lib - one letter went from 8.6 s and 2,865 items to 9 ms and the best 30; session released early, text bound.</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="n"/>
       <c r="D62" s="4" t="n"/>
       <c r="E62" s="4" t="n"/>
       <c r="F62" s="4" t="n"/>
@@ -1685,12 +1681,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>index.php</t>
+          <t>inc/auto/select_store_indent_items.php</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | Login query was concatenated from $_REQUEST so the password check could be commented out - now a prepared statement with both values bound. csrf + form token on the post, session id regenerated and tokens dropped on success, failed logins written to the error log, prefilled admin@bie.com removed, autocomplete attributes added.</t>
+          <t>2026-10-07 | Rewritten on item_search_lib - one letter went from 5 s to 8 ms; session released early, text bound.</t>
         </is>
       </c>
       <c r="C63" s="4" t="n"/>
@@ -1701,12 +1697,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>admin_multi_logins.php</t>
+          <t>inc/auto/select_repair_indent_items.php</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | Same concatenated login query, bound now. Removed the echo that printed the query with the password in it to the page. csrf + form token, session id regenerated on success. Its no-hash password compare left as it was - that changes who can use the screen.</t>
+          <t>2026-10-07 | Session released straight away so keystrokes are not queued.</t>
         </is>
       </c>
       <c r="C64" s="4" t="n"/>
@@ -1717,18 +1713,102 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>db/bie.sql</t>
+          <t>inc/cis_ajax/select_spare_mapping_items.php</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+          <t>2026-10-07 | Session released straight away; typed text bound.</t>
         </is>
       </c>
       <c r="C65" s="4" t="n"/>
       <c r="D65" s="4" t="n"/>
       <c r="E65" s="4" t="n"/>
       <c r="F65" s="4" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>db/post_upload_061026.sql</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06 | New. Checked against bie_db_061026.sql: every earlier change is live; adds the four audit columns mst_principal.php writes but the table never had.</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>db/post_upload_051026.sql</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05 | New. Everything to run on the server after the file upload, checked against bie_db_051026.sql: widen tbl_user_rights.sm_id, clear the six clamped rights rows, grant sm_id 147/148, repair 111 zeroed invoice line amounts, drop the four temp tables.</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05 | Step 7 split into five queries - as one UNION starting from information_schema, MariaDB looked for the plain tables there too (#1109). Step 3 now skips rights rows that already exist and step 4b keeps an existing backup, so the whole file is safe to run twice.</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="n"/>
+      <c r="F67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>index.php</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01 | Login query was concatenated from $_REQUEST so the password check could be commented out - now a prepared statement with both values bound. csrf + form token on the post, session id regenerated and tokens dropped on success, failed logins written to the error log, prefilled admin@bie.com removed, autocomplete attributes added.</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="4" t="n"/>
+      <c r="F68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>admin_multi_logins.php</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01 | Same concatenated login query, bound now. Removed the echo that printed the query with the password in it to the page. csrf + form token, session id regenerated on success. Its no-hash password compare left as it was - that changes who can use the screen.</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="n"/>
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>db/bie.sql</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n"/>
+      <c r="D70" s="4" t="n"/>
+      <c r="E70" s="4" t="n"/>
+      <c r="F70" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -750,7 +750,11 @@
           <t>2026-09-24 | CSRF + form token guard on SAVE/UPDATE; transaction with rollback.</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n"/>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12 | Branch dropdown gets All and is saved on a new item (All = every active branch, e.g. 1,2,3); it was ignored before and every item saved as branch 1. Principal shows Name - Code. Min / Max Discount on new item only, saved to each branch's min/max discount column in tbl_item_stock; min above max is refused.</t>
+        </is>
+      </c>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
     </row>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1653,12 +1653,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>inc/auto/item_search_lib.php</t>
+          <t>db/import_spac_price_list_121026.sql</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07 | New. Shared item search: best 30 matches in one query, stock fields for those items in one more, branch column names checked against tbl_item_stock.</t>
+          <t>2026-10-12 | New. One-time import of the SPAC price list (4,702 items) - adds missing categories and HSN codes, items for all branches, stock rows with price, discount and min/max discount. Safe to run twice.</t>
         </is>
       </c>
       <c r="C61" s="4" t="n"/>
@@ -1669,12 +1669,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>inc/auto/select_quotation_items.php</t>
+          <t>inc/auto/item_search_lib.php</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07 | Rewritten on item_search_lib - one letter went from 8.6 s and 2,865 items to 9 ms and the best 30; session released early, text bound.</t>
+          <t>2026-10-07 | New. Shared item search: best 30 matches in one query, stock fields for those items in one more, branch column names checked against tbl_item_stock.</t>
         </is>
       </c>
       <c r="C62" s="4" t="n"/>
@@ -1685,12 +1685,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>inc/auto/select_store_indent_items.php</t>
+          <t>inc/auto/select_quotation_items.php</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07 | Rewritten on item_search_lib - one letter went from 5 s to 8 ms; session released early, text bound.</t>
+          <t>2026-10-07 | Rewritten on item_search_lib - one letter went from 8.6 s and 2,865 items to 9 ms and the best 30; session released early, text bound.</t>
         </is>
       </c>
       <c r="C63" s="4" t="n"/>
@@ -1701,12 +1701,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>inc/auto/select_repair_indent_items.php</t>
+          <t>inc/auto/select_store_indent_items.php</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07 | Session released straight away so keystrokes are not queued.</t>
+          <t>2026-10-07 | Rewritten on item_search_lib - one letter went from 5 s to 8 ms; session released early, text bound.</t>
         </is>
       </c>
       <c r="C64" s="4" t="n"/>
@@ -1717,12 +1717,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>inc/cis_ajax/select_spare_mapping_items.php</t>
+          <t>inc/auto/select_repair_indent_items.php</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07 | Session released straight away; typed text bound.</t>
+          <t>2026-10-07 | Session released straight away so keystrokes are not queued.</t>
         </is>
       </c>
       <c r="C65" s="4" t="n"/>
@@ -1733,12 +1733,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>db/post_upload_061026.sql</t>
+          <t>inc/cis_ajax/select_spare_mapping_items.php</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06 | New. Checked against bie_db_061026.sql: every earlier change is live; adds the four audit columns mst_principal.php writes but the table never had.</t>
+          <t>2026-10-07 | Session released straight away; typed text bound.</t>
         </is>
       </c>
       <c r="C66" s="4" t="n"/>
@@ -1749,19 +1749,15 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>db/post_upload_051026.sql</t>
+          <t>db/post_upload_061026.sql</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 | New. Everything to run on the server after the file upload, checked against bie_db_051026.sql: widen tbl_user_rights.sm_id, clear the six clamped rights rows, grant sm_id 147/148, repair 111 zeroed invoice line amounts, drop the four temp tables.</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05 | Step 7 split into five queries - as one UNION starting from information_schema, MariaDB looked for the plain tables there too (#1109). Step 3 now skips rights rows that already exist and step 4b keeps an existing backup, so the whole file is safe to run twice.</t>
-        </is>
-      </c>
+          <t>2026-10-06 | New. Checked against bie_db_061026.sql: every earlier change is live; adds the four audit columns mst_principal.php writes but the table never had.</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n"/>
       <c r="D67" s="4" t="n"/>
       <c r="E67" s="4" t="n"/>
       <c r="F67" s="4" t="n"/>
@@ -1769,15 +1765,19 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>index.php</t>
+          <t>db/post_upload_051026.sql</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | Login query was concatenated from $_REQUEST so the password check could be commented out - now a prepared statement with both values bound. csrf + form token on the post, session id regenerated and tokens dropped on success, failed logins written to the error log, prefilled admin@bie.com removed, autocomplete attributes added.</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="n"/>
+          <t>2026-10-05 | New. Everything to run on the server after the file upload, checked against bie_db_051026.sql: widen tbl_user_rights.sm_id, clear the six clamped rights rows, grant sm_id 147/148, repair 111 zeroed invoice line amounts, drop the four temp tables.</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05 | Step 7 split into five queries - as one UNION starting from information_schema, MariaDB looked for the plain tables there too (#1109). Step 3 now skips rights rows that already exist and step 4b keeps an existing backup, so the whole file is safe to run twice.</t>
+        </is>
+      </c>
       <c r="D68" s="4" t="n"/>
       <c r="E68" s="4" t="n"/>
       <c r="F68" s="4" t="n"/>
@@ -1785,12 +1785,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>admin_multi_logins.php</t>
+          <t>index.php</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | Same concatenated login query, bound now. Removed the echo that printed the query with the password in it to the page. csrf + form token, session id regenerated on success. Its no-hash password compare left as it was - that changes who can use the screen.</t>
+          <t>2026-10-01 | Login query was concatenated from $_REQUEST so the password check could be commented out - now a prepared statement with both values bound. csrf + form token on the post, session id regenerated and tokens dropped on success, failed logins written to the error log, prefilled admin@bie.com removed, autocomplete attributes added.</t>
         </is>
       </c>
       <c r="C69" s="4" t="n"/>
@@ -1801,18 +1801,34 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>db/bie.sql</t>
+          <t>admin_multi_logins.php</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+          <t>2026-10-01 | Same concatenated login query, bound now. Removed the echo that printed the query with the password in it to the page. csrf + form token, session id regenerated on success. Its no-hash password compare left as it was - that changes who can use the screen.</t>
         </is>
       </c>
       <c r="C70" s="4" t="n"/>
       <c r="D70" s="4" t="n"/>
       <c r="E70" s="4" t="n"/>
       <c r="F70" s="4" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>db/bie.sql</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | Base dump updated - 2000 inactive, 1/2/5 added to tbl_cash_details and mst_cash_details.</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="n"/>
+      <c r="D71" s="4" t="n"/>
+      <c r="E71" s="4" t="n"/>
+      <c r="F71" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1825,7 +1841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1913,12 +1929,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>mst_principal</t>
+          <t>mst_category</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06 | created_by, created_dtm, modify_by, modify_dtm | Added - mst_principal.php writes them on save and update, so both always failed with Unknown column. Existing rows get 0 / NULL.</t>
+          <t>2026-10-12 | (rows) | SPAC import adds AIR GUN, FRL, TUBING. Sheet FITTING mapped to the existing FITTINGS.</t>
         </is>
       </c>
       <c r="C2" s="4" t="n"/>
@@ -1936,24 +1952,16 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>tbl_user_rights</t>
+          <t>mst_hsn</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 | sm_id | Signed TINYINT widened to SMALLINT. It stopped at 127, so the rights rows for the new menus (147, 148) were silently clamped to 127 and the menus never showed.</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05 | mm_id | Signed TINYINT widened to SMALLINT, same reason - it was two main menus away from the same limit.</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05 | (rows) | Six clamped rows deleted (users 2/6/7, sm_id 127 under main menus 3 and 20); sm_id 147 and 148 granted to whoever holds the parent menu.</t>
-        </is>
-      </c>
+          <t>2026-10-12 | (rows) | SPAC import adds 39173290, 39174000, 40169390, 84678910, 84812000, 85045090, 85365090, 85444999 at 18% (9 + 9).</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
@@ -1967,19 +1975,15 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>tbl_invoice_details</t>
+          <t>tbl_item_details / tbl_item_stock</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 | inv_value, tax_value | 111 rows across 35 invoices rebuilt as net_value / (1 + vat/100); tax_value rebuilt with them. Backup taken as tbl_invoice_details_bkp_051026.</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05 | cgst_per, sgst_per, igst_per, cgst_val, sgst_val, igst_val | Optional tidy on the same 111 rows only.</t>
-        </is>
-      </c>
+          <t>2026-10-12 | (rows) | SPAC import adds 4,702 items (principal SPAC, Pneumatic, Trading, branches 1,2,3) and one stock row each.</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n"/>
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
@@ -1994,106 +1998,50 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>tbl_stock_flow</t>
+          <t>mst_principal</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | trans_dir | Added CHAR(1). I = stock in (+), O = stock out (-). Backfilled GRN=I, INV/SALE=O.</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | trans_remarks | Added VARCHAR(255). Reason / narration, mandatory on ADJ rows.</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | stock_field | Added VARCHAR(30). Which tbl_item_stock column was changed. Backfilled from mst_branch.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | before_qty | INT to DECIMAL(12,3). Was truncating decimal stock.</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | trans_qty | INT to DECIMAL(12,3). Always a positive magnitude, direction is in trans_dir.</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | rcvd_qty | INT to DECIMAL(12,3).</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | after_qty | INT to DECIMAL(12,3).</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | reje_qty | INT to DECIMAL(12,3).</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | pend_qty | INT to DECIMAL(12,3).</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | trans_type | VARCHAR(8) to VARCHAR(10). Values GRN, INV, ADJ, OPEN, RET.</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | idx_sf_item_branch_date | Index added on (item_id, branch_id, trans_date) - what the reports filter on.</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | idx_sf_trans | Index added on (trans_type, trans_id).</t>
-        </is>
-      </c>
+          <t>2026-10-06 | created_by, created_dtm, modify_by, modify_dtm | Added - mst_principal.php writes them on save and update, so both always failed with Unknown column. Existing rows get 0 / NULL.</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>tbl_stock_adjustment</t>
+          <t>tbl_user_rights</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | (new table) | Header for every manual stock correction. One row per adjustment.</t>
+          <t>2026-10-05 | sm_id | Signed TINYINT widened to SMALLINT. It stopped at 127, so the rights rows for the new menus (147, 148) were silently clamped to 127 and the menus never showed.</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | adj_id, adj_refno, adj_slno, adj_finyr | Key and reference number ADJ/nnnn/BIE/&lt;branch&gt;/&lt;finyr&gt;.</t>
+          <t>2026-10-05 | mm_id | Signed TINYINT widened to SMALLINT, same reason - it was two main menus away from the same limit.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | adj_date, branch_id, stock_field, item_id | What was adjusted, where, and which stock column.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | adj_type, adj_qty, before_qty, after_qty | I = increase, D = decrease. adj_qty is always positive.</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | item_price, adj_reason, adj_status | Reason is mandatory. adj_status 1 = active, 0 = deleted.</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | created_by, created_dtm | Who made the adjustment and when.</t>
-        </is>
-      </c>
+          <t>2026-10-05 | (rows) | Six clamped rows deleted (users 2/6/7, sm_id 127 under main menus 3 and 20); sm_id 147 and 148 granted to whoever holds the parent menu.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
@@ -2104,17 +2052,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>mst_sub_menu</t>
+          <t>tbl_invoice_details</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | (row) | sm_id 147, mm_id 20 (Stores) - Stock Adjustment, stock_adjustment.php.</t>
+          <t>2026-10-05 | inv_value, tax_value | 111 rows across 35 invoices rebuilt as net_value / (1 + vat/100); tax_value rebuilt with them. Backup taken as tbl_invoice_details_bkp_051026.</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 | (row) | sm_id 148, mm_id 3 (Item Masters) - Item Stock List, lst_item_stock.php.</t>
+          <t>2026-10-05 | cgst_per, sgst_per, igst_per, cgst_val, sgst_val, igst_val | Optional tidy on the same 111 rows only.</t>
         </is>
       </c>
       <c r="D7" s="4" t="n"/>
@@ -2131,46 +2079,106 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>tbl_user_rights</t>
+          <t>tbl_stock_flow</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | (rows) | sm_id 147 granted to every user who already has the Stores menu.</t>
+          <t>2026-09-22 | trans_dir | Added CHAR(1). I = stock in (+), O = stock out (-). Backfilled GRN=I, INV/SALE=O.</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 | (rows) | sm_id 148 granted to every user who already has the Item Masters menu.</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n"/>
+          <t>2026-09-22 | trans_remarks | Added VARCHAR(255). Reason / narration, mandatory on ADJ rows.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | stock_field | Added VARCHAR(30). Which tbl_item_stock column was changed. Backfilled from mst_branch.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | before_qty | INT to DECIMAL(12,3). Was truncating decimal stock.</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | trans_qty | INT to DECIMAL(12,3). Always a positive magnitude, direction is in trans_dir.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | rcvd_qty | INT to DECIMAL(12,3).</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | after_qty | INT to DECIMAL(12,3).</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | reje_qty | INT to DECIMAL(12,3).</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | pend_qty | INT to DECIMAL(12,3).</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | trans_type | VARCHAR(8) to VARCHAR(10). Values GRN, INV, ADJ, OPEN, RET.</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | idx_sf_item_branch_date | Index added on (item_id, branch_id, trans_date) - what the reports filter on.</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | idx_sf_trans | Index added on (trans_type, trans_id).</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>tbl_item_stock</t>
+          <t>tbl_stock_adjustment</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | (no schema change) | Qty columns are now only written through fnApplyStockMovement(), never directly.</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
+          <t>2026-09-22 | (new table) | Header for every manual stock correction. One row per adjustment.</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | adj_id, adj_refno, adj_slno, adj_finyr | Key and reference number ADJ/nnnn/BIE/&lt;branch&gt;/&lt;finyr&gt;.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | adj_date, branch_id, stock_field, item_id | What was adjusted, where, and which stock column.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | adj_type, adj_qty, before_qty, after_qty | I = increase, D = decrease. adj_qty is always positive.</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | item_price, adj_reason, adj_status | Reason is mandatory. adj_status 1 = active, 0 = deleted.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | created_by, created_dtm | Who made the adjustment and when.</t>
+        </is>
+      </c>
       <c r="H9" s="4" t="n"/>
       <c r="I9" s="4" t="n"/>
       <c r="J9" s="4" t="n"/>
@@ -2181,17 +2189,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>tbl_cash_details</t>
+          <t>mst_sub_menu</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | cash_status | 2000.00 set to 0 (retired). Not deleted - old receipts hold cash_id 7 and history screens look the name up without checking status.</t>
+          <t>2026-09-22 | (row) | sm_id 147, mm_id 20 (Stores) - Stock Adjustment, stock_adjustment.php.</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | (rows) | Added cash_id 8 = 1.00, 9 = 2.00, 10 = 5.00, all active. Used by the Sales Receipt screen.</t>
+          <t>2026-09-23 | (row) | sm_id 148, mm_id 3 (Item Masters) - Item Stock List, lst_item_stock.php.</t>
         </is>
       </c>
       <c r="D10" s="4" t="n"/>
@@ -2208,17 +2216,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>mst_cash_details</t>
+          <t>tbl_user_rights</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | cash_status | 2000.00 set to 0 (retired). Same reasoning as tbl_cash_details.</t>
+          <t>2026-09-22 | (rows) | sm_id 147 granted to every user who already has the Stores menu.</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | (rows) | Added cash_id 8 = 1.00, 9 = 2.00, 10 = 5.00, all active. Used by the Invoice and Credit screens.</t>
+          <t>2026-09-23 | (rows) | sm_id 148 granted to every user who already has the Item Masters menu.</t>
         </is>
       </c>
       <c r="D11" s="4" t="n"/>
@@ -2235,12 +2243,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>mst_customer_branch_temp</t>
+          <t>tbl_item_stock</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | (whole table) | No longer used. Branch rows live in the page and post back as arrays. Drop with db/drop_temp_tables.sql.</t>
+          <t>2026-09-22 | (no schema change) | Qty columns are now only written through fnApplyStockMovement(), never directly.</t>
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
@@ -2258,15 +2266,19 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>tbl_item_group_details_temp</t>
+          <t>tbl_cash_details</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | (whole table) | No longer used. Group items live in the page. Drop with db/drop_temp_tables.sql.</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n"/>
+          <t>2026-09-25 | cash_status | 2000.00 set to 0 (retired). Not deleted - old receipts hold cash_id 7 and history screens look the name up without checking status.</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | (rows) | Added cash_id 8 = 1.00, 9 = 2.00, 10 = 5.00, all active. Used by the Sales Receipt screen.</t>
+        </is>
+      </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
@@ -2281,15 +2293,19 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>tbl_dc_details_temp</t>
+          <t>mst_cash_details</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | (whole table) | No longer used. DC item rows are built in php and posted back as arrays. Drop with db/drop_temp_tables.sql.</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n"/>
+          <t>2026-09-25 | cash_status | 2000.00 set to 0 (retired). Same reasoning as tbl_cash_details.</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | (rows) | Added cash_id 8 = 1.00, 9 = 2.00, 10 = 5.00, all active. Used by the Invoice and Credit screens.</t>
+        </is>
+      </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
@@ -2304,12 +2320,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>tbl_package_box_details_temp</t>
+          <t>mst_customer_branch_temp</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | (whole table) | No longer used. Packing rides on the DC item row as csv hidden fields. Drop with db/drop_temp_tables.sql.</t>
+          <t>2026-10-01 | (whole table) | No longer used. Branch rows live in the page and post back as arrays. Drop with db/drop_temp_tables.sql.</t>
         </is>
       </c>
       <c r="C15" s="4" t="n"/>
@@ -2327,12 +2343,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>tbl_invoice_details</t>
+          <t>tbl_item_group_details_temp</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30 | inv_value | No schema change. Data repair - rows saved from the invoice edit screen had this zeroed by a bad field mapping. Rebuilt as net_value - tax_value where that agrees with qty x unit_price less discount.</t>
+          <t>2026-10-01 | (whole table) | No longer used. Group items live in the page. Drop with db/drop_temp_tables.sql.</t>
         </is>
       </c>
       <c r="C16" s="4" t="n"/>
@@ -2350,12 +2366,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>tbl_proforma_details</t>
+          <t>tbl_dc_details_temp</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30 | pro_value | No schema change. Same data repair as tbl_invoice_details.</t>
+          <t>2026-10-01 | (whole table) | No longer used. DC item rows are built in php and posted back as arrays. Drop with db/drop_temp_tables.sql.</t>
         </is>
       </c>
       <c r="C17" s="4" t="n"/>
@@ -2373,12 +2389,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>tbl_item_details</t>
+          <t>tbl_package_box_details_temp</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | item_curr_stock | No change. Noted as dead - every write to it was already commented out. Branch columns in tbl_item_stock are the live balance.</t>
+          <t>2026-10-01 | (whole table) | No longer used. Packing rides on the DC item row as csv hidden fields. Drop with db/drop_temp_tables.sql.</t>
         </is>
       </c>
       <c r="C18" s="4" t="n"/>
@@ -2393,6 +2409,75 @@
       <c r="L18" s="4" t="n"/>
       <c r="M18" s="4" t="n"/>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>tbl_invoice_details</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30 | inv_value | No schema change. Data repair - rows saved from the invoice edit screen had this zeroed by a bad field mapping. Rebuilt as net_value - tax_value where that agrees with qty x unit_price less discount.</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>tbl_proforma_details</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30 | pro_value | No schema change. Same data repair as tbl_invoice_details.</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>tbl_item_details</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | item_curr_stock | No change. Noted as dead - every write to it was already commented out. Branch columns in tbl_item_stock are the live balance.</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -472,6 +472,7 @@
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="62" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -505,6 +506,11 @@
           <t>Change 5</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Change 6</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -521,6 +527,7 @@
       <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -541,6 +548,7 @@
       <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -557,6 +565,7 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -577,6 +586,7 @@
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -605,6 +615,7 @@
         </is>
       </c>
       <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -637,6 +648,7 @@
           <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
         </is>
       </c>
+      <c r="G7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -669,6 +681,7 @@
           <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
         </is>
       </c>
+      <c r="G8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -701,6 +714,7 @@
           <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8. Package dropdown renamed pack_pick so it cannot replace the pack_id[] rows.</t>
         </is>
       </c>
+      <c r="G9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -733,6 +747,11 @@
           <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
         </is>
       </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | updated_by from _user_id (was empty).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -755,8 +774,13 @@
           <t>2026-10-12 | Branch dropdown gets All and is saved on a new item (All = every active branch, e.g. 1,2,3); it was ignored before and every item saved as branch 1. Principal shows Name - Code. Min / Max Discount on new item only, saved to each branch's min/max discount column in tbl_item_stock; min above max is refused.</t>
         </is>
       </c>
-      <c r="E11" s="4" t="n"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | _userid replaced by _user_id - the admin price-required check never ran.</t>
+        </is>
+      </c>
       <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -773,6 +797,7 @@
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -789,6 +814,7 @@
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -809,6 +835,7 @@
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -825,6 +852,7 @@
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -841,6 +869,7 @@
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -865,6 +894,7 @@
       </c>
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -881,6 +911,7 @@
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -897,6 +928,7 @@
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -913,6 +945,7 @@
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -929,6 +962,7 @@
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -945,6 +979,7 @@
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -965,6 +1000,7 @@
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -982,9 +1018,14 @@
           <t>2026-09-24 | Loads csrf.php and db_txn.php.</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n"/>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Loads access.php.</t>
+        </is>
+      </c>
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1005,6 +1046,7 @@
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1025,6 +1067,7 @@
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1049,6 +1092,7 @@
       </c>
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1076,7 +1120,12 @@
           <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
         </is>
       </c>
-      <c r="F28" s="4" t="n"/>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | dc_verify_by from _user_id - _userid is never set at login, so it was always empty.</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1094,9 +1143,14 @@
           <t>2026-10-06 | Prepared qty read on $conn - a complete PO went to admin as partial.</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n"/>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | modify_by from _user_id (was empty).</t>
+        </is>
+      </c>
       <c r="E29" s="4" t="n"/>
       <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1117,6 +1171,7 @@
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1137,6 +1192,7 @@
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1157,6 +1213,7 @@
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1177,6 +1234,7 @@
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1193,6 +1251,7 @@
       <c r="D34" s="4" t="n"/>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1209,6 +1268,7 @@
       <c r="D35" s="4" t="n"/>
       <c r="E35" s="4" t="n"/>
       <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1229,6 +1289,7 @@
       <c r="D36" s="4" t="n"/>
       <c r="E36" s="4" t="n"/>
       <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1249,6 +1310,7 @@
       <c r="D37" s="4" t="n"/>
       <c r="E37" s="4" t="n"/>
       <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1265,6 +1327,7 @@
       <c r="D38" s="4" t="n"/>
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1292,7 +1355,12 @@
           <t>2026-10-06 | Lock rewritten again: no longer wraps form.submit() or cancels a submission, only disables buttons once a submit is under way and drops later clicks. Buttons with their own onclick (Send to Purchase, invoice, direct PO, GRN, credit, Generate PO) were posting without their name.</t>
         </is>
       </c>
-      <c r="F39" s="4" t="n"/>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Csrf token attached in $.ajaxPrefilter - pages passing their own beforeSend dropped the ajaxSetup hook, so their posts had no token.</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1309,6 +1377,7 @@
       <c r="D40" s="4" t="n"/>
       <c r="E40" s="4" t="n"/>
       <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1325,6 +1394,7 @@
       <c r="D41" s="4" t="n"/>
       <c r="E41" s="4" t="n"/>
       <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1341,6 +1411,7 @@
       <c r="D42" s="4" t="n"/>
       <c r="E42" s="4" t="n"/>
       <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1361,6 +1432,7 @@
       <c r="D43" s="4" t="n"/>
       <c r="E43" s="4" t="n"/>
       <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1377,6 +1449,7 @@
       <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1397,6 +1470,7 @@
       <c r="D45" s="4" t="n"/>
       <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1413,6 +1487,7 @@
       <c r="D46" s="4" t="n"/>
       <c r="E46" s="4" t="n"/>
       <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1429,6 +1504,7 @@
       <c r="D47" s="4" t="n"/>
       <c r="E47" s="4" t="n"/>
       <c r="F47" s="4" t="n"/>
+      <c r="G47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1445,6 +1521,7 @@
       <c r="D48" s="4" t="n"/>
       <c r="E48" s="4" t="n"/>
       <c r="F48" s="4" t="n"/>
+      <c r="G48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1465,6 +1542,7 @@
       <c r="D49" s="4" t="n"/>
       <c r="E49" s="4" t="n"/>
       <c r="F49" s="4" t="n"/>
+      <c r="G49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1481,6 +1559,7 @@
       <c r="D50" s="4" t="n"/>
       <c r="E50" s="4" t="n"/>
       <c r="F50" s="4" t="n"/>
+      <c r="G50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1501,6 +1580,7 @@
       <c r="D51" s="4" t="n"/>
       <c r="E51" s="4" t="n"/>
       <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1517,6 +1597,7 @@
       <c r="D52" s="4" t="n"/>
       <c r="E52" s="4" t="n"/>
       <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1534,9 +1615,14 @@
           <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
         </is>
       </c>
-      <c r="D53" s="4" t="n"/>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | _userid replaced by _user_id - the admin Edit amount button never showed for anyone.</t>
+        </is>
+      </c>
       <c r="E53" s="4" t="n"/>
       <c r="F53" s="4" t="n"/>
+      <c r="G53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1553,6 +1639,7 @@
       <c r="D54" s="4" t="n"/>
       <c r="E54" s="4" t="n"/>
       <c r="F54" s="4" t="n"/>
+      <c r="G54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1569,6 +1656,7 @@
       <c r="D55" s="4" t="n"/>
       <c r="E55" s="4" t="n"/>
       <c r="F55" s="4" t="n"/>
+      <c r="G55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1581,10 +1669,15 @@
           <t>2026-10-06 | Loads csrf and txn helpers itself - opened on its own it died on csrf_fields().</t>
         </is>
       </c>
-      <c r="C56" s="4" t="n"/>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Starts its own session when posted directly - credit approval failed since 2026-10-01. Allowed for the credit-approval tile users; approver saved as the user, was always 1.</t>
+        </is>
+      </c>
       <c r="D56" s="4" t="n"/>
       <c r="E56" s="4" t="n"/>
       <c r="F56" s="4" t="n"/>
+      <c r="G56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1597,10 +1690,15 @@
           <t>2026-10-06 | Loads csrf and txn helpers itself - opened on its own it died on csrf_fields().</t>
         </is>
       </c>
-      <c r="C57" s="4" t="n"/>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Starts its own session when posted directly - every cancel failed the csrf check since 2026-10-01. Cancel allowed for admin only (the link); cancelled-by is the user, was always 1.</t>
+        </is>
+      </c>
       <c r="D57" s="4" t="n"/>
       <c r="E57" s="4" t="n"/>
       <c r="F57" s="4" t="n"/>
+      <c r="G57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1613,10 +1711,15 @@
           <t>2026-10-06 | Loads csrf and txn helpers itself - opened on its own it died on csrf_fields().</t>
         </is>
       </c>
-      <c r="C58" s="4" t="n"/>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Starts its own session when posted directly - every cancel failed since 2026-10-01. Allowed for admin or head office (the link); cancelled-by is the user, was always 1.</t>
+        </is>
+      </c>
       <c r="D58" s="4" t="n"/>
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="n"/>
+      <c r="G58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -1633,6 +1736,7 @@
       <c r="D59" s="4" t="n"/>
       <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="n"/>
+      <c r="G59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1649,6 +1753,7 @@
       <c r="D60" s="4" t="n"/>
       <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="n"/>
+      <c r="G60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -1665,6 +1770,7 @@
       <c r="D61" s="4" t="n"/>
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="n"/>
+      <c r="G61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -1681,6 +1787,7 @@
       <c r="D62" s="4" t="n"/>
       <c r="E62" s="4" t="n"/>
       <c r="F62" s="4" t="n"/>
+      <c r="G62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -1697,6 +1804,7 @@
       <c r="D63" s="4" t="n"/>
       <c r="E63" s="4" t="n"/>
       <c r="F63" s="4" t="n"/>
+      <c r="G63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -1713,6 +1821,7 @@
       <c r="D64" s="4" t="n"/>
       <c r="E64" s="4" t="n"/>
       <c r="F64" s="4" t="n"/>
+      <c r="G64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -1729,6 +1838,7 @@
       <c r="D65" s="4" t="n"/>
       <c r="E65" s="4" t="n"/>
       <c r="F65" s="4" t="n"/>
+      <c r="G65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -1745,6 +1855,7 @@
       <c r="D66" s="4" t="n"/>
       <c r="E66" s="4" t="n"/>
       <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -1761,6 +1872,7 @@
       <c r="D67" s="4" t="n"/>
       <c r="E67" s="4" t="n"/>
       <c r="F67" s="4" t="n"/>
+      <c r="G67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -1781,6 +1893,7 @@
       <c r="D68" s="4" t="n"/>
       <c r="E68" s="4" t="n"/>
       <c r="F68" s="4" t="n"/>
+      <c r="G68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -1797,6 +1910,7 @@
       <c r="D69" s="4" t="n"/>
       <c r="E69" s="4" t="n"/>
       <c r="F69" s="4" t="n"/>
+      <c r="G69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -1813,6 +1927,7 @@
       <c r="D70" s="4" t="n"/>
       <c r="E70" s="4" t="n"/>
       <c r="F70" s="4" t="n"/>
+      <c r="G70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -1829,6 +1944,211 @@
       <c r="D71" s="4" t="n"/>
       <c r="E71" s="4" t="n"/>
       <c r="F71" s="4" t="n"/>
+      <c r="G71" s="4" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>inc/common/access.php</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | New. fnAccessDenied, fnAjaxGuard (login + csrf), fnUserHasMenu, fnTaskUserListed - server-side checks for approve / verify / reject.</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="n"/>
+      <c r="D72" s="4" t="n"/>
+      <c r="E72" s="4" t="n"/>
+      <c r="F72" s="4" t="n"/>
+      <c r="G72" s="4" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>inc/cis_ajax/jquery_po_approval.php</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Login + csrf + approver check (admin, as the button); remarks and id bound instead of pasted into the sql.</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n"/>
+      <c r="D73" s="4" t="n"/>
+      <c r="E73" s="4" t="n"/>
+      <c r="F73" s="4" t="n"/>
+      <c r="G73" s="4" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>inc/cis_ajax/jquery_purchase_return_approval.php</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Login + csrf + approver check (admin - the list is an admin-only menu); remarks and id bound.</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="n"/>
+      <c r="D74" s="4" t="n"/>
+      <c r="E74" s="4" t="n"/>
+      <c r="F74" s="4" t="n"/>
+      <c r="G74" s="4" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>inc/cis_ajax/jquery_quo_approval.php</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Login + csrf + approver check: admin or the quotation's branch, as the button.</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="n"/>
+      <c r="D75" s="4" t="n"/>
+      <c r="E75" s="4" t="n"/>
+      <c r="F75" s="4" t="n"/>
+      <c r="G75" s="4" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>inc/cis_ajax/jquery_so_approval.php</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Login + csrf + approver check (admin, as the button).</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="n"/>
+      <c r="D76" s="4" t="n"/>
+      <c r="E76" s="4" t="n"/>
+      <c r="F76" s="4" t="n"/>
+      <c r="G76" s="4" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>inc/cis_ajax/jquery_dc_approval.php</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Login + csrf + approver check: admin or the DC's branch, as the button.</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="n"/>
+      <c r="D77" s="4" t="n"/>
+      <c r="E77" s="4" t="n"/>
+      <c r="F77" s="4" t="n"/>
+      <c r="G77" s="4" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>inc/cis_ajax/jquery_sales_repair_status.php</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Login + csrf + check (admin, as the buttons).</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="n"/>
+      <c r="D78" s="4" t="n"/>
+      <c r="E78" s="4" t="n"/>
+      <c r="F78" s="4" t="n"/>
+      <c r="G78" s="4" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>inc/cis_ajax/jquery_so_pay_status.php</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Login + csrf + check: holders of the Sales Order in Accounts menu. Verifier saved from _user_id - it was always empty.</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="n"/>
+      <c r="D79" s="4" t="n"/>
+      <c r="E79" s="4" t="n"/>
+      <c r="F79" s="4" t="n"/>
+      <c r="G79" s="4" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>so_verify.php</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Csrf + check: holders of the Sales Order in Accounts menu; so_id bound.</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="n"/>
+      <c r="D80" s="4" t="n"/>
+      <c r="E80" s="4" t="n"/>
+      <c r="F80" s="4" t="n"/>
+      <c r="G80" s="4" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>mst_supplier_approve.php</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Csrf token on the form + approver check (admin, the only user shown the link).</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="n"/>
+      <c r="D81" s="4" t="n"/>
+      <c r="E81" s="4" t="n"/>
+      <c r="F81" s="4" t="n"/>
+      <c r="G81" s="4" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>branch_wise_item_update.php</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Update allowed for admin at head office or the item-approval users; updated_by from _user_id (was empty).</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="n"/>
+      <c r="D82" s="4" t="n"/>
+      <c r="E82" s="4" t="n"/>
+      <c r="F82" s="4" t="n"/>
+      <c r="G82" s="4" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>po_prepare_print.php</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | modify_by from _user_id (was empty).</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="n"/>
+      <c r="D83" s="4" t="n"/>
+      <c r="E83" s="4" t="n"/>
+      <c r="F83" s="4" t="n"/>
+      <c r="G83" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -779,7 +779,11 @@
           <t>2026-10-13 | _userid replaced by _user_id - the admin price-required check never ran.</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n"/>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Price block check uses Task Settings (ITEM C) - was user 1; both branches show it.</t>
+        </is>
+      </c>
       <c r="G11" s="4" t="n"/>
     </row>
     <row r="12">
@@ -1064,7 +1068,11 @@
           <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8. Package dropdown renamed pack_pick so it cannot replace the pack_id[] rows.</t>
         </is>
       </c>
-      <c r="D26" s="4" t="n"/>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Named approver from Task Settings (QUOTATION A, else admin) - was tbl_task_user 1.</t>
+        </is>
+      </c>
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
@@ -1168,7 +1176,11 @@
           <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
         </is>
       </c>
-      <c r="D30" s="4" t="n"/>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Named approver from Task Settings (PURCHASE_ORDER A, else admin) - was tbl_task_user 1.</t>
+        </is>
+      </c>
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="n"/>
       <c r="G30" s="4" t="n"/>
@@ -1189,7 +1201,11 @@
           <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
         </is>
       </c>
-      <c r="D31" s="4" t="n"/>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Named approver from Task Settings (STORE_INDENT A, else admin) - was tbl_task_user 1.</t>
+        </is>
+      </c>
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="4" t="n"/>
       <c r="G31" s="4" t="n"/>
@@ -1620,7 +1636,11 @@
           <t>2026-10-13 | _userid replaced by _user_id - the admin Edit amount button never showed for anyone.</t>
         </is>
       </c>
-      <c r="E53" s="4" t="n"/>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Edit paid amount for approvers in Task Settings (GRN_PAYMENT A) - was admin.</t>
+        </is>
+      </c>
       <c r="F53" s="4" t="n"/>
       <c r="G53" s="4" t="n"/>
     </row>
@@ -1674,7 +1694,11 @@
           <t>2026-10-13 | Starts its own session when posted directly - credit approval failed since 2026-10-01. Allowed for the credit-approval tile users; approver saved as the user, was always 1.</t>
         </is>
       </c>
-      <c r="D56" s="4" t="n"/>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Credit approval for approvers in Task Settings (CREDIT_SALES A).</t>
+        </is>
+      </c>
       <c r="E56" s="4" t="n"/>
       <c r="F56" s="4" t="n"/>
       <c r="G56" s="4" t="n"/>
@@ -1695,7 +1719,11 @@
           <t>2026-10-13 | Starts its own session when posted directly - every cancel failed the csrf check since 2026-10-01. Cancel allowed for admin only (the link); cancelled-by is the user, was always 1.</t>
         </is>
       </c>
-      <c r="D57" s="4" t="n"/>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Cancel for approvers in Task Settings (SALES_ORDER A).</t>
+        </is>
+      </c>
       <c r="E57" s="4" t="n"/>
       <c r="F57" s="4" t="n"/>
       <c r="G57" s="4" t="n"/>
@@ -1716,7 +1744,11 @@
           <t>2026-10-13 | Starts its own session when posted directly - every cancel failed since 2026-10-01. Allowed for admin or head office (the link); cancelled-by is the user, was always 1.</t>
         </is>
       </c>
-      <c r="D58" s="4" t="n"/>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Cancel for approvers in Task Settings (GRN A).</t>
+        </is>
+      </c>
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="n"/>
       <c r="G58" s="4" t="n"/>
@@ -1957,7 +1989,11 @@
           <t>2026-10-13 | New. fnAccessDenied, fnAjaxGuard (login + csrf), fnUserHasMenu, fnTaskUserListed - server-side checks for approve / verify / reject.</t>
         </is>
       </c>
-      <c r="C72" s="4" t="n"/>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | fnTaskCan(code, role, branch), fnTaskIsAdmin, fnTaskDefaultUser; rows read once per request. fnUserHasMenu / fnTaskUserListed removed.</t>
+        </is>
+      </c>
       <c r="D72" s="4" t="n"/>
       <c r="E72" s="4" t="n"/>
       <c r="F72" s="4" t="n"/>
@@ -1974,7 +2010,11 @@
           <t>2026-10-13 | Login + csrf + approver check (admin, as the button); remarks and id bound instead of pasted into the sql.</t>
         </is>
       </c>
-      <c r="C73" s="4" t="n"/>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Approver from Task Settings (PURCHASE_ORDER A).</t>
+        </is>
+      </c>
       <c r="D73" s="4" t="n"/>
       <c r="E73" s="4" t="n"/>
       <c r="F73" s="4" t="n"/>
@@ -1991,7 +2031,11 @@
           <t>2026-10-13 | Login + csrf + approver check (admin - the list is an admin-only menu); remarks and id bound.</t>
         </is>
       </c>
-      <c r="C74" s="4" t="n"/>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Approver from Task Settings (PURCHASE_RETURN A).</t>
+        </is>
+      </c>
       <c r="D74" s="4" t="n"/>
       <c r="E74" s="4" t="n"/>
       <c r="F74" s="4" t="n"/>
@@ -2008,7 +2052,11 @@
           <t>2026-10-13 | Login + csrf + approver check: admin or the quotation's branch, as the button.</t>
         </is>
       </c>
-      <c r="C75" s="4" t="n"/>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Approver from Task Settings (QUOTATION A, per branch).</t>
+        </is>
+      </c>
       <c r="D75" s="4" t="n"/>
       <c r="E75" s="4" t="n"/>
       <c r="F75" s="4" t="n"/>
@@ -2025,7 +2073,11 @@
           <t>2026-10-13 | Login + csrf + approver check (admin, as the button).</t>
         </is>
       </c>
-      <c r="C76" s="4" t="n"/>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Approver from Task Settings (SALES_ORDER A).</t>
+        </is>
+      </c>
       <c r="D76" s="4" t="n"/>
       <c r="E76" s="4" t="n"/>
       <c r="F76" s="4" t="n"/>
@@ -2042,7 +2094,11 @@
           <t>2026-10-13 | Login + csrf + approver check: admin or the DC's branch, as the button.</t>
         </is>
       </c>
-      <c r="C77" s="4" t="n"/>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Approver from Task Settings (DC A, per branch).</t>
+        </is>
+      </c>
       <c r="D77" s="4" t="n"/>
       <c r="E77" s="4" t="n"/>
       <c r="F77" s="4" t="n"/>
@@ -2059,7 +2115,11 @@
           <t>2026-10-13 | Login + csrf + check (admin, as the buttons).</t>
         </is>
       </c>
-      <c r="C78" s="4" t="n"/>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Send for approval / approve from Task Settings (SALES_REPAIR V / A).</t>
+        </is>
+      </c>
       <c r="D78" s="4" t="n"/>
       <c r="E78" s="4" t="n"/>
       <c r="F78" s="4" t="n"/>
@@ -2076,7 +2136,11 @@
           <t>2026-10-13 | Login + csrf + check: holders of the Sales Order in Accounts menu. Verifier saved from _user_id - it was always empty.</t>
         </is>
       </c>
-      <c r="C79" s="4" t="n"/>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Verifier from Task Settings (SALES_RECEIPT V) - was the Sales Order in Accounts menu.</t>
+        </is>
+      </c>
       <c r="D79" s="4" t="n"/>
       <c r="E79" s="4" t="n"/>
       <c r="F79" s="4" t="n"/>
@@ -2093,7 +2157,11 @@
           <t>2026-10-13 | Csrf + check: holders of the Sales Order in Accounts menu; so_id bound.</t>
         </is>
       </c>
-      <c r="C80" s="4" t="n"/>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Verifier from Task Settings (SALES_RECEIPT V) - was the Sales Order in Accounts menu.</t>
+        </is>
+      </c>
       <c r="D80" s="4" t="n"/>
       <c r="E80" s="4" t="n"/>
       <c r="F80" s="4" t="n"/>
@@ -2110,7 +2178,11 @@
           <t>2026-10-13 | Csrf token on the form + approver check (admin, the only user shown the link).</t>
         </is>
       </c>
-      <c r="C81" s="4" t="n"/>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Approver from Task Settings (SUPPLIER A).</t>
+        </is>
+      </c>
       <c r="D81" s="4" t="n"/>
       <c r="E81" s="4" t="n"/>
       <c r="F81" s="4" t="n"/>
@@ -2127,7 +2199,11 @@
           <t>2026-10-13 | Update allowed for admin at head office or the item-approval users; updated_by from _user_id (was empty).</t>
         </is>
       </c>
-      <c r="C82" s="4" t="n"/>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Item creators and approvers from Task Settings (ITEM C / A).</t>
+        </is>
+      </c>
       <c r="D82" s="4" t="n"/>
       <c r="E82" s="4" t="n"/>
       <c r="F82" s="4" t="n"/>
@@ -2149,6 +2225,873 @@
       <c r="E83" s="4" t="n"/>
       <c r="F83" s="4" t="n"/>
       <c r="G83" s="4" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>attendance_report_ot.php</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Salary issue button for approvers in Task Settings (SALARY A) - was admin.</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="n"/>
+      <c r="D84" s="4" t="n"/>
+      <c r="E84" s="4" t="n"/>
+      <c r="F84" s="4" t="n"/>
+      <c r="G84" s="4" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>attendance_report_pf.php</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Salary issue button for approvers in Task Settings (SALARY A) - was admin.</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="n"/>
+      <c r="D85" s="4" t="n"/>
+      <c r="E85" s="4" t="n"/>
+      <c r="F85" s="4" t="n"/>
+      <c r="G85" s="4" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>attendance_report_withoutpf.php</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Salary issue button for approvers in Task Settings (SALARY A) - was admin.</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="n"/>
+      <c r="D86" s="4" t="n"/>
+      <c r="E86" s="4" t="n"/>
+      <c r="F86" s="4" t="n"/>
+      <c r="G86" s="4" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>dc_list.php</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Branch filter for viewers in Task Settings (DC W) - was head office.</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="n"/>
+      <c r="D87" s="4" t="n"/>
+      <c r="E87" s="4" t="n"/>
+      <c r="F87" s="4" t="n"/>
+      <c r="G87" s="4" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>dc_print.php</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Approve / reject for approvers in Task Settings (DC A) - was admin or the DC's branch.</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="n"/>
+      <c r="D88" s="4" t="n"/>
+      <c r="E88" s="4" t="n"/>
+      <c r="F88" s="4" t="n"/>
+      <c r="G88" s="4" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>employee_advance.php</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Branch filter for viewers in Task Settings (EMPLOYEE W) - was head office.</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="n"/>
+      <c r="D89" s="4" t="n"/>
+      <c r="E89" s="4" t="n"/>
+      <c r="F89" s="4" t="n"/>
+      <c r="G89" s="4" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>employee_debit_note.php</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Branch filter for viewers in Task Settings (EMPLOYEE W) - was head office.</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="n"/>
+      <c r="D90" s="4" t="n"/>
+      <c r="E90" s="4" t="n"/>
+      <c r="F90" s="4" t="n"/>
+      <c r="G90" s="4" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>employee_salary.php</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Branch filter for viewers in Task Settings (EMPLOYEE W) - was head office.</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="n"/>
+      <c r="D91" s="4" t="n"/>
+      <c r="E91" s="4" t="n"/>
+      <c r="F91" s="4" t="n"/>
+      <c r="G91" s="4" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>grn_list.php</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Branch filter for viewers in Task Settings (GRN W) - was head office.</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="n"/>
+      <c r="D92" s="4" t="n"/>
+      <c r="E92" s="4" t="n"/>
+      <c r="F92" s="4" t="n"/>
+      <c r="G92" s="4" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>grn_payment_details.php</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Branch filter for viewers in Task Settings (GRN_PAYMENT W) - was head office.</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="n"/>
+      <c r="D93" s="4" t="n"/>
+      <c r="E93" s="4" t="n"/>
+      <c r="F93" s="4" t="n"/>
+      <c r="G93" s="4" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>home.php</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Dashboard tiles shown to all-branch approvers of each task (PO, supplier, quotation, credit sales, new item, GRN payment) - were the tbl_task_user ids.</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="n"/>
+      <c r="D94" s="4" t="n"/>
+      <c r="E94" s="4" t="n"/>
+      <c r="F94" s="4" t="n"/>
+      <c r="G94" s="4" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxDclist.php</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | All branches for viewers in Task Settings (DC W) - was admin or head office.</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="n"/>
+      <c r="D95" s="4" t="n"/>
+      <c r="E95" s="4" t="n"/>
+      <c r="F95" s="4" t="n"/>
+      <c r="G95" s="4" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxEmployeeAdvance.php</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | All branches for viewers in Task Settings (EMPLOYEE W) - was admin or head office.</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="n"/>
+      <c r="D96" s="4" t="n"/>
+      <c r="E96" s="4" t="n"/>
+      <c r="F96" s="4" t="n"/>
+      <c r="G96" s="4" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxEmployeeDebit.php</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | All branches for viewers in Task Settings (EMPLOYEE W) - was admin or head office.</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="n"/>
+      <c r="D97" s="4" t="n"/>
+      <c r="E97" s="4" t="n"/>
+      <c r="F97" s="4" t="n"/>
+      <c r="G97" s="4" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxEmployeeSalarySet.php</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | All branches for viewers in Task Settings (EMPLOYEE W) - was admin or head office.</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="n"/>
+      <c r="D98" s="4" t="n"/>
+      <c r="E98" s="4" t="n"/>
+      <c r="F98" s="4" t="n"/>
+      <c r="G98" s="4" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxEmployeeWorkDetsList.php</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | All branches for viewers in Task Settings (EMPLOYEE W) - was admin or head office.</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="n"/>
+      <c r="D99" s="4" t="n"/>
+      <c r="E99" s="4" t="n"/>
+      <c r="F99" s="4" t="n"/>
+      <c r="G99" s="4" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxEmployeelist.php</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | All branches for viewers in Task Settings (EMPLOYEE W) - was admin or head office.</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="n"/>
+      <c r="D100" s="4" t="n"/>
+      <c r="E100" s="4" t="n"/>
+      <c r="F100" s="4" t="n"/>
+      <c r="G100" s="4" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxGrnList.php</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | All branches for viewers in Task Settings (GRN W) - was admin or head office.</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="n"/>
+      <c r="D101" s="4" t="n"/>
+      <c r="E101" s="4" t="n"/>
+      <c r="F101" s="4" t="n"/>
+      <c r="G101" s="4" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxGrnPaymentList.php</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | All branches for viewers in Task Settings (GRN_PAYMENT W) - was admin or head office.</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="n"/>
+      <c r="D102" s="4" t="n"/>
+      <c r="E102" s="4" t="n"/>
+      <c r="F102" s="4" t="n"/>
+      <c r="G102" s="4" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxInvoiceList.php</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | All branches for viewers in Task Settings (INVOICE W) - was admin or head office.</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="n"/>
+      <c r="D103" s="4" t="n"/>
+      <c r="E103" s="4" t="n"/>
+      <c r="F103" s="4" t="n"/>
+      <c r="G103" s="4" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxItemDetailsList.php</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Edit / price / branch / delete links for creators in Task Settings (ITEM C) - was admin at head office.</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="n"/>
+      <c r="D104" s="4" t="n"/>
+      <c r="E104" s="4" t="n"/>
+      <c r="F104" s="4" t="n"/>
+      <c r="G104" s="4" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxLabourList.php</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | All branches for viewers in Task Settings (EMPLOYEE W) - was admin or head office.</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="n"/>
+      <c r="D105" s="4" t="n"/>
+      <c r="E105" s="4" t="n"/>
+      <c r="F105" s="4" t="n"/>
+      <c r="G105" s="4" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxPoList.php</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Edit links for creators in Task Settings (PURCHASE_ORDER C) - was admin or head office.</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="n"/>
+      <c r="D106" s="4" t="n"/>
+      <c r="E106" s="4" t="n"/>
+      <c r="F106" s="4" t="n"/>
+      <c r="G106" s="4" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxPoPrepareList.php</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | All branches for viewers in Task Settings (PO_PREPARE W) - was admin or head office.</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="n"/>
+      <c r="D107" s="4" t="n"/>
+      <c r="E107" s="4" t="n"/>
+      <c r="F107" s="4" t="n"/>
+      <c r="G107" s="4" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxPurchaseReturnList.php</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | GRN cancel link for approvers in Task Settings (GRN A) - was admin or head office.</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="n"/>
+      <c r="D108" s="4" t="n"/>
+      <c r="E108" s="4" t="n"/>
+      <c r="F108" s="4" t="n"/>
+      <c r="G108" s="4" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxQuotationlist.php</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | All branches for viewers in Task Settings (QUOTATION W) - was admin or head office.</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="n"/>
+      <c r="D109" s="4" t="n"/>
+      <c r="E109" s="4" t="n"/>
+      <c r="F109" s="4" t="n"/>
+      <c r="G109" s="4" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxReceiptlist.php</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | All branches for viewers in Task Settings (SALES_RECEIPT W) - was admin or head office.</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="n"/>
+      <c r="D110" s="4" t="n"/>
+      <c r="E110" s="4" t="n"/>
+      <c r="F110" s="4" t="n"/>
+      <c r="G110" s="4" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxSaleslist.php</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Cancel link for approvers in Task Settings (SALES_ORDER A) - was admin.</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="n"/>
+      <c r="D111" s="4" t="n"/>
+      <c r="E111" s="4" t="n"/>
+      <c r="F111" s="4" t="n"/>
+      <c r="G111" s="4" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxStaffList.php</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | All branches for viewers in Task Settings (EMPLOYEE W) - was admin or head office.</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="n"/>
+      <c r="D112" s="4" t="n"/>
+      <c r="E112" s="4" t="n"/>
+      <c r="F112" s="4" t="n"/>
+      <c r="G112" s="4" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxSupplierList.php</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | All branches for viewers in Task Settings (SUPPLIER W) - was admin or head office.</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="n"/>
+      <c r="D113" s="4" t="n"/>
+      <c r="E113" s="4" t="n"/>
+      <c r="F113" s="4" t="n"/>
+      <c r="G113" s="4" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajax_SiList.php</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | All branches for viewers in Task Settings (STORE_INDENT W) - was admin or head office.</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="n"/>
+      <c r="D114" s="4" t="n"/>
+      <c r="E114" s="4" t="n"/>
+      <c r="F114" s="4" t="n"/>
+      <c r="G114" s="4" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>invoice_list.php</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Branch filter for viewers in Task Settings (INVOICE W) - was head office.</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="n"/>
+      <c r="D115" s="4" t="n"/>
+      <c r="E115" s="4" t="n"/>
+      <c r="F115" s="4" t="n"/>
+      <c r="G115" s="4" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>lst_direct_po.php</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | New PO button for creators and branch filter for viewers in Task Settings - were head office.</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="n"/>
+      <c r="D116" s="4" t="n"/>
+      <c r="E116" s="4" t="n"/>
+      <c r="F116" s="4" t="n"/>
+      <c r="G116" s="4" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>lst_employee.php</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Branch filter for viewers in Task Settings (EMPLOYEE W) - was head office.</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="n"/>
+      <c r="D117" s="4" t="n"/>
+      <c r="E117" s="4" t="n"/>
+      <c r="F117" s="4" t="n"/>
+      <c r="G117" s="4" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>lst_labour.php</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Branch filter for viewers in Task Settings (EMPLOYEE W) - was head office.</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="n"/>
+      <c r="D118" s="4" t="n"/>
+      <c r="E118" s="4" t="n"/>
+      <c r="F118" s="4" t="n"/>
+      <c r="G118" s="4" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>lst_quotation.php</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Branch filter for viewers in Task Settings (QUOTATION W) - was head office.</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="n"/>
+      <c r="D119" s="4" t="n"/>
+      <c r="E119" s="4" t="n"/>
+      <c r="F119" s="4" t="n"/>
+      <c r="G119" s="4" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>lst_sales_order.php</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Branch filter for viewers in Task Settings (SALES_ORDER W) - was head office.</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="n"/>
+      <c r="D120" s="4" t="n"/>
+      <c r="E120" s="4" t="n"/>
+      <c r="F120" s="4" t="n"/>
+      <c r="G120" s="4" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>lst_sales_receipt.php</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Branch filter for viewers in Task Settings (SALES_RECEIPT W) - was head office.</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="n"/>
+      <c r="D121" s="4" t="n"/>
+      <c r="E121" s="4" t="n"/>
+      <c r="F121" s="4" t="n"/>
+      <c r="G121" s="4" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>lst_staff.php</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Branch filter for viewers in Task Settings (EMPLOYEE W) - was head office.</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="n"/>
+      <c r="D122" s="4" t="n"/>
+      <c r="E122" s="4" t="n"/>
+      <c r="F122" s="4" t="n"/>
+      <c r="G122" s="4" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>lst_supplier.php</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Branch filter for viewers in Task Settings (SUPPLIER W) - was head office.</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="n"/>
+      <c r="D123" s="4" t="n"/>
+      <c r="E123" s="4" t="n"/>
+      <c r="F123" s="4" t="n"/>
+      <c r="G123" s="4" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>po_prepare_list.php</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Branch filter for viewers in Task Settings (PO_PREPARE W) - was head office.</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="n"/>
+      <c r="D124" s="4" t="n"/>
+      <c r="E124" s="4" t="n"/>
+      <c r="F124" s="4" t="n"/>
+      <c r="G124" s="4" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>po_print.php</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Approve / reject for approvers in Task Settings (PURCHASE_ORDER A) - was admin.</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="n"/>
+      <c r="D125" s="4" t="n"/>
+      <c r="E125" s="4" t="n"/>
+      <c r="F125" s="4" t="n"/>
+      <c r="G125" s="4" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>print_quotation.php</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Approve / reject for approvers in Task Settings (QUOTATION A) - was admin or the quotation's branch.</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="n"/>
+      <c r="D126" s="4" t="n"/>
+      <c r="E126" s="4" t="n"/>
+      <c r="F126" s="4" t="n"/>
+      <c r="G126" s="4" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>print_sales_order.php</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Approve / reject for approvers in Task Settings (SALES_ORDER A) - was admin.</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="n"/>
+      <c r="D127" s="4" t="n"/>
+      <c r="E127" s="4" t="n"/>
+      <c r="F127" s="4" t="n"/>
+      <c r="G127" s="4" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>purchase_return_list.php</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Branch filter for viewers in Task Settings (PURCHASE_RETURN W) - was head office.</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="n"/>
+      <c r="D128" s="4" t="n"/>
+      <c r="E128" s="4" t="n"/>
+      <c r="F128" s="4" t="n"/>
+      <c r="G128" s="4" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>purchase_return_view.php</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Approve / reject only for approvers in Task Settings (PURCHASE_RETURN A) - was anyone opening the page.</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="n"/>
+      <c r="D129" s="4" t="n"/>
+      <c r="E129" s="4" t="n"/>
+      <c r="F129" s="4" t="n"/>
+      <c r="G129" s="4" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>rpt_so_stock_list_branchwise.php</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Update location for creators in Task Settings (STOCK_LOCATION C) - was users 1 and 9.</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="n"/>
+      <c r="D130" s="4" t="n"/>
+      <c r="E130" s="4" t="n"/>
+      <c r="F130" s="4" t="n"/>
+      <c r="G130" s="4" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>sales_repair_print.php</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Send for approval (SALES_REPAIR V) and approve (SALES_REPAIR A) from Task Settings - were admin.</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="n"/>
+      <c r="D131" s="4" t="n"/>
+      <c r="E131" s="4" t="n"/>
+      <c r="F131" s="4" t="n"/>
+      <c r="G131" s="4" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>store_indent_list.php</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Branch filter for viewers in Task Settings (STORE_INDENT W) - was head office.</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="n"/>
+      <c r="D132" s="4" t="n"/>
+      <c r="E132" s="4" t="n"/>
+      <c r="F132" s="4" t="n"/>
+      <c r="G132" s="4" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>db/post_upload_131026.sql</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | New. Creates mst_task and tbl_task_assign, adds the 18 tasks, starting rows that give everyone exactly the access the code gave, and the Task Settings menu. Safe to run again.</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="n"/>
+      <c r="D133" s="4" t="n"/>
+      <c r="E133" s="4" t="n"/>
+      <c r="F133" s="4" t="n"/>
+      <c r="G133" s="4" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>mst_task.php</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | New. Settings &gt; Task Settings (admin only): add a task, tick the roles it uses, add many users per role with a branch or All, edit or deactivate a task; list shows who holds each role.</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="n"/>
+      <c r="D134" s="4" t="n"/>
+      <c r="E134" s="4" t="n"/>
+      <c r="F134" s="4" t="n"/>
+      <c r="G134" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2161,7 +3104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2249,12 +3192,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>mst_category</t>
+          <t>mst_task</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12 | (rows) | SPAC import adds AIR GUN, FRL, TUBING. Sheet FITTING mapped to the existing FITTINGS.</t>
+          <t>2026-10-13 | (new table) | One row per task: code checked by the screens, name, module, roles used (C V A W), note, status.</t>
         </is>
       </c>
       <c r="C2" s="4" t="n"/>
@@ -2272,12 +3215,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>mst_hsn</t>
+          <t>tbl_task_assign</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12 | (rows) | SPAC import adds 39173290, 39174000, 40169390, 84678910, 84812000, 85045090, 85365090, 85444999 at 18% (9 + 9).</t>
+          <t>2026-10-13 | (new table) | One row per task / role / user / branch (0 = all). Starting rows reproduce the old coded rules: head office users view every branch and create POs, branch users approve their branch's quotations and DCs, accounts confirms payments.</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -2295,12 +3238,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>tbl_item_details / tbl_item_stock</t>
+          <t>mst_sub_menu</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12 | (rows) | SPAC import adds 4,702 items (principal SPAC, Pneumatic, Trading, branches 1,2,3) and one stock row each.</t>
+          <t>2026-10-13 | (row) | Settings &gt; Task Settings (mst_task.php).</t>
         </is>
       </c>
       <c r="C4" s="4" t="n"/>
@@ -2318,12 +3261,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>mst_principal</t>
+          <t>tbl_task_user</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06 | created_by, created_dtm, modify_by, modify_dtm | Added - mst_principal.php writes them on save and update, so both always failed with Unknown column. Existing rows get 0 / NULL.</t>
+          <t>2026-10-13 | (no longer read) | Its user lists are copied into tbl_task_assign by the 13-10-26 script; can be dropped once the new files are live.</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -2341,24 +3284,16 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>tbl_user_rights</t>
+          <t>mst_category</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 | sm_id | Signed TINYINT widened to SMALLINT. It stopped at 127, so the rights rows for the new menus (147, 148) were silently clamped to 127 and the menus never showed.</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05 | mm_id | Signed TINYINT widened to SMALLINT, same reason - it was two main menus away from the same limit.</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05 | (rows) | Six clamped rows deleted (users 2/6/7, sm_id 127 under main menus 3 and 20); sm_id 147 and 148 granted to whoever holds the parent menu.</t>
-        </is>
-      </c>
+          <t>2026-10-12 | (rows) | SPAC import adds AIR GUN, FRL, TUBING. Sheet FITTING mapped to the existing FITTINGS.</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
@@ -2372,19 +3307,15 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>tbl_invoice_details</t>
+          <t>mst_hsn</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 | inv_value, tax_value | 111 rows across 35 invoices rebuilt as net_value / (1 + vat/100); tax_value rebuilt with them. Backup taken as tbl_invoice_details_bkp_051026.</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05 | cgst_per, sgst_per, igst_per, cgst_val, sgst_val, igst_val | Optional tidy on the same 111 rows only.</t>
-        </is>
-      </c>
+          <t>2026-10-12 | (rows) | SPAC import adds 39173290, 39174000, 40169390, 84678910, 84812000, 85045090, 85365090, 85444999 at 18% (9 + 9).</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="n"/>
@@ -2399,106 +3330,42 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>tbl_stock_flow</t>
+          <t>tbl_item_details / tbl_item_stock</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | trans_dir | Added CHAR(1). I = stock in (+), O = stock out (-). Backfilled GRN=I, INV/SALE=O.</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | trans_remarks | Added VARCHAR(255). Reason / narration, mandatory on ADJ rows.</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | stock_field | Added VARCHAR(30). Which tbl_item_stock column was changed. Backfilled from mst_branch.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | before_qty | INT to DECIMAL(12,3). Was truncating decimal stock.</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | trans_qty | INT to DECIMAL(12,3). Always a positive magnitude, direction is in trans_dir.</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | rcvd_qty | INT to DECIMAL(12,3).</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | after_qty | INT to DECIMAL(12,3).</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | reje_qty | INT to DECIMAL(12,3).</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | pend_qty | INT to DECIMAL(12,3).</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | trans_type | VARCHAR(8) to VARCHAR(10). Values GRN, INV, ADJ, OPEN, RET.</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | idx_sf_item_branch_date | Index added on (item_id, branch_id, trans_date) - what the reports filter on.</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | idx_sf_trans | Index added on (trans_type, trans_id).</t>
-        </is>
-      </c>
+          <t>2026-10-12 | (rows) | SPAC import adds 4,702 items (principal SPAC, Pneumatic, Trading, branches 1,2,3) and one stock row each.</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>tbl_stock_adjustment</t>
+          <t>mst_principal</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | (new table) | Header for every manual stock correction. One row per adjustment.</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | adj_id, adj_refno, adj_slno, adj_finyr | Key and reference number ADJ/nnnn/BIE/&lt;branch&gt;/&lt;finyr&gt;.</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | adj_date, branch_id, stock_field, item_id | What was adjusted, where, and which stock column.</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | adj_type, adj_qty, before_qty, after_qty | I = increase, D = decrease. adj_qty is always positive.</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | item_price, adj_reason, adj_status | Reason is mandatory. adj_status 1 = active, 0 = deleted.</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 | created_by, created_dtm | Who made the adjustment and when.</t>
-        </is>
-      </c>
+          <t>2026-10-06 | created_by, created_dtm, modify_by, modify_dtm | Added - mst_principal.php writes them on save and update, so both always failed with Unknown column. Existing rows get 0 / NULL.</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
       <c r="H9" s="4" t="n"/>
       <c r="I9" s="4" t="n"/>
       <c r="J9" s="4" t="n"/>
@@ -2509,20 +3376,24 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>mst_sub_menu</t>
+          <t>tbl_user_rights</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | (row) | sm_id 147, mm_id 20 (Stores) - Stock Adjustment, stock_adjustment.php.</t>
+          <t>2026-10-05 | sm_id | Signed TINYINT widened to SMALLINT. It stopped at 127, so the rights rows for the new menus (147, 148) were silently clamped to 127 and the menus never showed.</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 | (row) | sm_id 148, mm_id 3 (Item Masters) - Item Stock List, lst_item_stock.php.</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n"/>
+          <t>2026-10-05 | mm_id | Signed TINYINT widened to SMALLINT, same reason - it was two main menus away from the same limit.</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05 | (rows) | Six clamped rows deleted (users 2/6/7, sm_id 127 under main menus 3 and 20); sm_id 147 and 148 granted to whoever holds the parent menu.</t>
+        </is>
+      </c>
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
@@ -2536,17 +3407,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>tbl_user_rights</t>
+          <t>tbl_invoice_details</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | (rows) | sm_id 147 granted to every user who already has the Stores menu.</t>
+          <t>2026-10-05 | inv_value, tax_value | 111 rows across 35 invoices rebuilt as net_value / (1 + vat/100); tax_value rebuilt with them. Backup taken as tbl_invoice_details_bkp_051026.</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 | (rows) | sm_id 148 granted to every user who already has the Item Masters menu.</t>
+          <t>2026-10-05 | cgst_per, sgst_per, igst_per, cgst_val, sgst_val, igst_val | Optional tidy on the same 111 rows only.</t>
         </is>
       </c>
       <c r="D11" s="4" t="n"/>
@@ -2563,46 +3434,106 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>tbl_item_stock</t>
+          <t>tbl_stock_flow</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | (no schema change) | Qty columns are now only written through fnApplyStockMovement(), never directly.</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n"/>
+          <t>2026-09-22 | trans_dir | Added CHAR(1). I = stock in (+), O = stock out (-). Backfilled GRN=I, INV/SALE=O.</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | trans_remarks | Added VARCHAR(255). Reason / narration, mandatory on ADJ rows.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | stock_field | Added VARCHAR(30). Which tbl_item_stock column was changed. Backfilled from mst_branch.</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | before_qty | INT to DECIMAL(12,3). Was truncating decimal stock.</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | trans_qty | INT to DECIMAL(12,3). Always a positive magnitude, direction is in trans_dir.</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | rcvd_qty | INT to DECIMAL(12,3).</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | after_qty | INT to DECIMAL(12,3).</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | reje_qty | INT to DECIMAL(12,3).</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | pend_qty | INT to DECIMAL(12,3).</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | trans_type | VARCHAR(8) to VARCHAR(10). Values GRN, INV, ADJ, OPEN, RET.</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | idx_sf_item_branch_date | Index added on (item_id, branch_id, trans_date) - what the reports filter on.</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | idx_sf_trans | Index added on (trans_type, trans_id).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>tbl_cash_details</t>
+          <t>tbl_stock_adjustment</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | cash_status | 2000.00 set to 0 (retired). Not deleted - old receipts hold cash_id 7 and history screens look the name up without checking status.</t>
+          <t>2026-09-22 | (new table) | Header for every manual stock correction. One row per adjustment.</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | (rows) | Added cash_id 8 = 1.00, 9 = 2.00, 10 = 5.00, all active. Used by the Sales Receipt screen.</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
+          <t>2026-09-22 | adj_id, adj_refno, adj_slno, adj_finyr | Key and reference number ADJ/nnnn/BIE/&lt;branch&gt;/&lt;finyr&gt;.</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | adj_date, branch_id, stock_field, item_id | What was adjusted, where, and which stock column.</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | adj_type, adj_qty, before_qty, after_qty | I = increase, D = decrease. adj_qty is always positive.</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | item_price, adj_reason, adj_status | Reason is mandatory. adj_status 1 = active, 0 = deleted.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | created_by, created_dtm | Who made the adjustment and when.</t>
+        </is>
+      </c>
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
       <c r="J13" s="4" t="n"/>
@@ -2613,17 +3544,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>mst_cash_details</t>
+          <t>mst_sub_menu</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | cash_status | 2000.00 set to 0 (retired). Same reasoning as tbl_cash_details.</t>
+          <t>2026-09-22 | (row) | sm_id 147, mm_id 20 (Stores) - Stock Adjustment, stock_adjustment.php.</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 | (rows) | Added cash_id 8 = 1.00, 9 = 2.00, 10 = 5.00, all active. Used by the Invoice and Credit screens.</t>
+          <t>2026-09-23 | (row) | sm_id 148, mm_id 3 (Item Masters) - Item Stock List, lst_item_stock.php.</t>
         </is>
       </c>
       <c r="D14" s="4" t="n"/>
@@ -2640,15 +3571,19 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>mst_customer_branch_temp</t>
+          <t>tbl_user_rights</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | (whole table) | No longer used. Branch rows live in the page and post back as arrays. Drop with db/drop_temp_tables.sql.</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n"/>
+          <t>2026-09-22 | (rows) | sm_id 147 granted to every user who already has the Stores menu.</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23 | (rows) | sm_id 148 granted to every user who already has the Item Masters menu.</t>
+        </is>
+      </c>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n"/>
@@ -2663,12 +3598,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>tbl_item_group_details_temp</t>
+          <t>tbl_item_stock</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | (whole table) | No longer used. Group items live in the page. Drop with db/drop_temp_tables.sql.</t>
+          <t>2026-09-22 | (no schema change) | Qty columns are now only written through fnApplyStockMovement(), never directly.</t>
         </is>
       </c>
       <c r="C16" s="4" t="n"/>
@@ -2686,15 +3621,19 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>tbl_dc_details_temp</t>
+          <t>tbl_cash_details</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | (whole table) | No longer used. DC item rows are built in php and posted back as arrays. Drop with db/drop_temp_tables.sql.</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n"/>
+          <t>2026-09-25 | cash_status | 2000.00 set to 0 (retired). Not deleted - old receipts hold cash_id 7 and history screens look the name up without checking status.</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | (rows) | Added cash_id 8 = 1.00, 9 = 2.00, 10 = 5.00, all active. Used by the Sales Receipt screen.</t>
+        </is>
+      </c>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="n"/>
@@ -2709,15 +3648,19 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>tbl_package_box_details_temp</t>
+          <t>mst_cash_details</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01 | (whole table) | No longer used. Packing rides on the DC item row as csv hidden fields. Drop with db/drop_temp_tables.sql.</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n"/>
+          <t>2026-09-25 | cash_status | 2000.00 set to 0 (retired). Same reasoning as tbl_cash_details.</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25 | (rows) | Added cash_id 8 = 1.00, 9 = 2.00, 10 = 5.00, all active. Used by the Invoice and Credit screens.</t>
+        </is>
+      </c>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
@@ -2732,12 +3675,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>tbl_invoice_details</t>
+          <t>mst_customer_branch_temp</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30 | inv_value | No schema change. Data repair - rows saved from the invoice edit screen had this zeroed by a bad field mapping. Rebuilt as net_value - tax_value where that agrees with qty x unit_price less discount.</t>
+          <t>2026-10-01 | (whole table) | No longer used. Branch rows live in the page and post back as arrays. Drop with db/drop_temp_tables.sql.</t>
         </is>
       </c>
       <c r="C19" s="4" t="n"/>
@@ -2755,12 +3698,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>tbl_proforma_details</t>
+          <t>tbl_item_group_details_temp</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30 | pro_value | No schema change. Same data repair as tbl_invoice_details.</t>
+          <t>2026-10-01 | (whole table) | No longer used. Group items live in the page. Drop with db/drop_temp_tables.sql.</t>
         </is>
       </c>
       <c r="C20" s="4" t="n"/>
@@ -2778,12 +3721,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>tbl_item_details</t>
+          <t>tbl_dc_details_temp</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 | item_curr_stock | No change. Noted as dead - every write to it was already commented out. Branch columns in tbl_item_stock are the live balance.</t>
+          <t>2026-10-01 | (whole table) | No longer used. DC item rows are built in php and posted back as arrays. Drop with db/drop_temp_tables.sql.</t>
         </is>
       </c>
       <c r="C21" s="4" t="n"/>
@@ -2798,6 +3741,98 @@
       <c r="L21" s="4" t="n"/>
       <c r="M21" s="4" t="n"/>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>tbl_package_box_details_temp</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01 | (whole table) | No longer used. Packing rides on the DC item row as csv hidden fields. Drop with db/drop_temp_tables.sql.</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
+      <c r="K22" s="4" t="n"/>
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>tbl_invoice_details</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30 | inv_value | No schema change. Data repair - rows saved from the invoice edit screen had this zeroed by a bad field mapping. Rebuilt as net_value - tax_value where that agrees with qty x unit_price less discount.</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
+      <c r="K23" s="4" t="n"/>
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>tbl_proforma_details</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30 | pro_value | No schema change. Same data repair as tbl_invoice_details.</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>tbl_item_details</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 | item_curr_stock | No change. Noted as dead - every write to it was already commented out. Branch columns in tbl_item_stock are the live balance.</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2407,7 +2407,11 @@
           <t>2026-10-13 | Dashboard tiles shown to all-branch approvers of each task (PO, supplier, quotation, credit sales, new item, GRN payment) - were the tbl_task_user ids.</t>
         </is>
       </c>
-      <c r="C94" s="4" t="n"/>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | GRN Payment Pending tile counts what its page lists (bill and payment both not done) - it counted bill only.</t>
+        </is>
+      </c>
       <c r="D94" s="4" t="n"/>
       <c r="E94" s="4" t="n"/>
       <c r="F94" s="4" t="n"/>
@@ -2900,7 +2904,11 @@
           <t>2026-10-13 | Branch filter for viewers in Task Settings (SUPPLIER W) - was head office.</t>
         </is>
       </c>
-      <c r="C123" s="4" t="n"/>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Opened from the Supplier InApproval tile the branch filter starts at All - it showed head office only, so a pending Kerala supplier was counted but not listed.</t>
+        </is>
+      </c>
       <c r="D123" s="4" t="n"/>
       <c r="E123" s="4" t="n"/>
       <c r="F123" s="4" t="n"/>
@@ -3092,6 +3100,23 @@
       <c r="E134" s="4" t="n"/>
       <c r="F134" s="4" t="n"/>
       <c r="G134" s="4" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>lst_quo_approval.php</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Deleted quotations (quo_status 0) left out, as the dashboard tile does.</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="n"/>
+      <c r="D135" s="4" t="n"/>
+      <c r="E135" s="4" t="n"/>
+      <c r="F135" s="4" t="n"/>
+      <c r="G135" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1027,7 +1027,11 @@
           <t>2026-10-13 | Loads access.php.</t>
         </is>
       </c>
-      <c r="E24" s="4" t="n"/>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Loads task_queues.php.</t>
+        </is>
+      </c>
       <c r="F24" s="4" t="n"/>
       <c r="G24" s="4" t="n"/>
     </row>
@@ -1302,7 +1306,11 @@
           <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
         </is>
       </c>
-      <c r="D36" s="4" t="n"/>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Mark as credit follows Sales Order in Accounts verifier - showed to every user (every user holds it to begin with).</t>
+        </is>
+      </c>
       <c r="E36" s="4" t="n"/>
       <c r="F36" s="4" t="n"/>
       <c r="G36" s="4" t="n"/>
@@ -1724,7 +1732,11 @@
           <t>2026-10-13 | Cancel for approvers in Task Settings (SALES_ORDER A).</t>
         </is>
       </c>
-      <c r="E57" s="4" t="n"/>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Cancel checked against SO_CANCEL.</t>
+        </is>
+      </c>
       <c r="F57" s="4" t="n"/>
       <c r="G57" s="4" t="n"/>
     </row>
@@ -1994,7 +2006,11 @@
           <t>2026-10-13 | fnTaskCan(code, role, branch), fnTaskIsAdmin, fnTaskDefaultUser; rows read once per request. fnUserHasMenu / fnTaskUserListed removed.</t>
         </is>
       </c>
-      <c r="D72" s="4" t="n"/>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | fnTaskBranches - the branches a user holds a role for.</t>
+        </is>
+      </c>
       <c r="E72" s="4" t="n"/>
       <c r="F72" s="4" t="n"/>
       <c r="G72" s="4" t="n"/>
@@ -2412,7 +2428,11 @@
           <t>2026-10-13 | GRN Payment Pending tile counts what its page lists (bill and payment both not done) - it counted bill only.</t>
         </is>
       </c>
-      <c r="D94" s="4" t="n"/>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Tiles built from task_queues.php: every verify / approve job the user holds, any branch; count limited to their branches.</t>
+        </is>
+      </c>
       <c r="E94" s="4" t="n"/>
       <c r="F94" s="4" t="n"/>
       <c r="G94" s="4" t="n"/>
@@ -2700,7 +2720,11 @@
           <t>2026-10-13 | Cancel link for approvers in Task Settings (SALES_ORDER A) - was admin.</t>
         </is>
       </c>
-      <c r="C111" s="4" t="n"/>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Cancel link moved to its own task SO_CANCEL (admin) - approve and cancel are different people.</t>
+        </is>
+      </c>
       <c r="D111" s="4" t="n"/>
       <c r="E111" s="4" t="n"/>
       <c r="F111" s="4" t="n"/>
@@ -2734,7 +2758,11 @@
           <t>2026-10-13 | All branches for viewers in Task Settings (SUPPLIER W) - was admin or head office.</t>
         </is>
       </c>
-      <c r="C113" s="4" t="n"/>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Tile mode: pending suppliers of the user's approver branches; status filter cast to int.</t>
+        </is>
+      </c>
       <c r="D113" s="4" t="n"/>
       <c r="E113" s="4" t="n"/>
       <c r="F113" s="4" t="n"/>
@@ -2909,7 +2937,11 @@
           <t>2026-10-13 | Opened from the Supplier InApproval tile the branch filter starts at All - it showed head office only, so a pending Kerala supplier was counted but not listed.</t>
         </is>
       </c>
-      <c r="D123" s="4" t="n"/>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | From the tile it lists the pending suppliers of the branches the user approves for.</t>
+        </is>
+      </c>
       <c r="E123" s="4" t="n"/>
       <c r="F123" s="4" t="n"/>
       <c r="G123" s="4" t="n"/>
@@ -2976,7 +3008,11 @@
           <t>2026-10-13 | Approve / reject for approvers in Task Settings (SALES_ORDER A) - was admin.</t>
         </is>
       </c>
-      <c r="C127" s="4" t="n"/>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Approve / reject buttons follow Sales Order approver - they showed to every user (every user holds it to begin with).</t>
+        </is>
+      </c>
       <c r="D127" s="4" t="n"/>
       <c r="E127" s="4" t="n"/>
       <c r="F127" s="4" t="n"/>
@@ -3078,7 +3114,11 @@
           <t>2026-10-13 | New. Creates mst_task and tbl_task_assign, adds the 18 tasks, starting rows that give everyone exactly the access the code gave, and the Task Settings menu. Safe to run again.</t>
         </is>
       </c>
-      <c r="C133" s="4" t="n"/>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Second block: SO_CANCEL task; sales order approver and payment verifier for every user (head office all branches, others own) - the buttons had no check. Runs once, also where the first version ran.</t>
+        </is>
+      </c>
       <c r="D133" s="4" t="n"/>
       <c r="E133" s="4" t="n"/>
       <c r="F133" s="4" t="n"/>
@@ -3112,11 +3152,117 @@
           <t>2026-10-13 | Deleted quotations (quo_status 0) left out, as the dashboard tile does.</t>
         </is>
       </c>
-      <c r="C135" s="4" t="n"/>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | List limited to the branches the user approves for, same rule as the tile.</t>
+        </is>
+      </c>
       <c r="D135" s="4" t="n"/>
       <c r="E135" s="4" t="n"/>
       <c r="F135" s="4" t="n"/>
       <c r="G135" s="4" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>inc/common/task_queues.php</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | New. One definition per dashboard tile: task / role, waiting rule, branch column, page it opens; count and page share it.</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="n"/>
+      <c r="D136" s="4" t="n"/>
+      <c r="E136" s="4" t="n"/>
+      <c r="F136" s="4" t="n"/>
+      <c r="G136" s="4" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>lst_pending.php</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | New. Waiting list behind the new tiles (sales order, payment, DC, purchase return, repair) with an Open link; only for holders of the job, their branches.</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="n"/>
+      <c r="D137" s="4" t="n"/>
+      <c r="E137" s="4" t="n"/>
+      <c r="F137" s="4" t="n"/>
+      <c r="G137" s="4" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>lst_direct_po_approval.php</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | List limited to the branches the user approves for, same rule as the tile.</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="n"/>
+      <c r="D138" s="4" t="n"/>
+      <c r="E138" s="4" t="n"/>
+      <c r="F138" s="4" t="n"/>
+      <c r="G138" s="4" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>lst_so_approval.php</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | List limited to the branches the user approves for, same rule as the tile.</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="n"/>
+      <c r="D139" s="4" t="n"/>
+      <c r="E139" s="4" t="n"/>
+      <c r="F139" s="4" t="n"/>
+      <c r="G139" s="4" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>lst_item_approval.php</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | List only for item approvers, same rule as the tile.</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="n"/>
+      <c r="D140" s="4" t="n"/>
+      <c r="E140" s="4" t="n"/>
+      <c r="F140" s="4" t="n"/>
+      <c r="G140" s="4" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>grn_payment_details_pending.php</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | List limited to the branches the user approves for, same rule as the tile.</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="n"/>
+      <c r="D141" s="4" t="n"/>
+      <c r="E141" s="4" t="n"/>
+      <c r="F141" s="4" t="n"/>
+      <c r="G141" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3248,7 +3394,11 @@
           <t>2026-10-13 | (new table) | One row per task / role / user / branch (0 = all). Starting rows reproduce the old coded rules: head office users view every branch and create POs, branch users approve their branch's quotations and DCs, accounts confirms payments.</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | (rows) | Sales order approver and payment verifier: every user (head office all branches, others own branch). New task SO_CANCEL for cancel (admin).</t>
+        </is>
+      </c>
       <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1077,7 +1077,11 @@
           <t>2026-10-13 | Named approver from Task Settings (QUOTATION A, else admin) - was tbl_task_user 1.</t>
         </is>
       </c>
-      <c r="E26" s="4" t="n"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Named approver may be a holder for the quotation's branch.</t>
+        </is>
+      </c>
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
     </row>
@@ -1185,7 +1189,11 @@
           <t>2026-10-13 | Named approver from Task Settings (PURCHASE_ORDER A, else admin) - was tbl_task_user 1.</t>
         </is>
       </c>
-      <c r="E30" s="4" t="n"/>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Named approver may be a holder for the PO's branch.</t>
+        </is>
+      </c>
       <c r="F30" s="4" t="n"/>
       <c r="G30" s="4" t="n"/>
     </row>
@@ -1210,7 +1218,11 @@
           <t>2026-10-13 | Named approver from Task Settings (STORE_INDENT A, else admin) - was tbl_task_user 1.</t>
         </is>
       </c>
-      <c r="E31" s="4" t="n"/>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Named approver may be a holder for the indent's branch.</t>
+        </is>
+      </c>
       <c r="F31" s="4" t="n"/>
       <c r="G31" s="4" t="n"/>
     </row>
@@ -1707,7 +1719,11 @@
           <t>2026-10-13 | Credit approval for approvers in Task Settings (CREDIT_SALES A).</t>
         </is>
       </c>
-      <c r="E56" s="4" t="n"/>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Only a sales order waiting for credit approval.</t>
+        </is>
+      </c>
       <c r="F56" s="4" t="n"/>
       <c r="G56" s="4" t="n"/>
     </row>
@@ -2011,7 +2027,11 @@
           <t>2026-10-13 | fnTaskBranches - the branches a user holds a role for.</t>
         </is>
       </c>
-      <c r="E72" s="4" t="n"/>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Named approver: All-branch holder, then the document's branch, else admin.</t>
+        </is>
+      </c>
       <c r="F72" s="4" t="n"/>
       <c r="G72" s="4" t="n"/>
     </row>
@@ -2031,7 +2051,11 @@
           <t>2026-10-13 | Approver from Task Settings (PURCHASE_ORDER A).</t>
         </is>
       </c>
-      <c r="D73" s="4" t="n"/>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Only a PO in approval can be approved / rejected; otherwise 'not waiting'.</t>
+        </is>
+      </c>
       <c r="E73" s="4" t="n"/>
       <c r="F73" s="4" t="n"/>
       <c r="G73" s="4" t="n"/>
@@ -2052,7 +2076,11 @@
           <t>2026-10-13 | Approver from Task Settings (PURCHASE_RETURN A).</t>
         </is>
       </c>
-      <c r="D74" s="4" t="n"/>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Only a return sent and not decided.</t>
+        </is>
+      </c>
       <c r="E74" s="4" t="n"/>
       <c r="F74" s="4" t="n"/>
       <c r="G74" s="4" t="n"/>
@@ -2073,7 +2101,11 @@
           <t>2026-10-13 | Approver from Task Settings (QUOTATION A, per branch).</t>
         </is>
       </c>
-      <c r="D75" s="4" t="n"/>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Only a quotation sent and not decided.</t>
+        </is>
+      </c>
       <c r="E75" s="4" t="n"/>
       <c r="F75" s="4" t="n"/>
       <c r="G75" s="4" t="n"/>
@@ -2094,7 +2126,11 @@
           <t>2026-10-13 | Approver from Task Settings (SALES_ORDER A).</t>
         </is>
       </c>
-      <c r="D76" s="4" t="n"/>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Only a verified, open sales order.</t>
+        </is>
+      </c>
       <c r="E76" s="4" t="n"/>
       <c r="F76" s="4" t="n"/>
       <c r="G76" s="4" t="n"/>
@@ -2115,7 +2151,11 @@
           <t>2026-10-13 | Approver from Task Settings (DC A, per branch).</t>
         </is>
       </c>
-      <c r="D77" s="4" t="n"/>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Only a DC sent and not decided.</t>
+        </is>
+      </c>
       <c r="E77" s="4" t="n"/>
       <c r="F77" s="4" t="n"/>
       <c r="G77" s="4" t="n"/>
@@ -2136,7 +2176,11 @@
           <t>2026-10-13 | Send for approval / approve from Task Settings (SALES_REPAIR V / A).</t>
         </is>
       </c>
-      <c r="D78" s="4" t="n"/>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Repair's branch (company_id) passed; send / approve only in the right state.</t>
+        </is>
+      </c>
       <c r="E78" s="4" t="n"/>
       <c r="F78" s="4" t="n"/>
       <c r="G78" s="4" t="n"/>
@@ -2253,7 +2297,11 @@
           <t>2026-10-13 | Salary issue button for approvers in Task Settings (SALARY A) - was admin.</t>
         </is>
       </c>
-      <c r="C84" s="4" t="n"/>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Issue button checked against the employee's branch.</t>
+        </is>
+      </c>
       <c r="D84" s="4" t="n"/>
       <c r="E84" s="4" t="n"/>
       <c r="F84" s="4" t="n"/>
@@ -2270,7 +2318,11 @@
           <t>2026-10-13 | Salary issue button for approvers in Task Settings (SALARY A) - was admin.</t>
         </is>
       </c>
-      <c r="C85" s="4" t="n"/>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Issue button checked against the employee's branch.</t>
+        </is>
+      </c>
       <c r="D85" s="4" t="n"/>
       <c r="E85" s="4" t="n"/>
       <c r="F85" s="4" t="n"/>
@@ -2287,7 +2339,11 @@
           <t>2026-10-13 | Salary issue button for approvers in Task Settings (SALARY A) - was admin.</t>
         </is>
       </c>
-      <c r="C86" s="4" t="n"/>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Issue button checked against the employee's branch.</t>
+        </is>
+      </c>
       <c r="D86" s="4" t="n"/>
       <c r="E86" s="4" t="n"/>
       <c r="F86" s="4" t="n"/>
@@ -2516,7 +2572,11 @@
           <t>2026-10-13 | All branches for viewers in Task Settings (EMPLOYEE W) - was admin or head office.</t>
         </is>
       </c>
-      <c r="C99" s="4" t="n"/>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Own branch only without the Employee viewer role - every branch showed.</t>
+        </is>
+      </c>
       <c r="D99" s="4" t="n"/>
       <c r="E99" s="4" t="n"/>
       <c r="F99" s="4" t="n"/>
@@ -2830,7 +2890,11 @@
           <t>2026-10-13 | Branch filter for viewers in Task Settings (EMPLOYEE W) - was head office.</t>
         </is>
       </c>
-      <c r="C117" s="4" t="n"/>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Ajax url matches the file name case - broke on case-sensitive servers.</t>
+        </is>
+      </c>
       <c r="D117" s="4" t="n"/>
       <c r="E117" s="4" t="n"/>
       <c r="F117" s="4" t="n"/>
@@ -3080,7 +3144,11 @@
           <t>2026-10-13 | Send for approval (SALES_REPAIR V) and approve (SALES_REPAIR A) from Task Settings - were admin.</t>
         </is>
       </c>
-      <c r="C131" s="4" t="n"/>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Buttons checked against the repair's branch (company_id).</t>
+        </is>
+      </c>
       <c r="D131" s="4" t="n"/>
       <c r="E131" s="4" t="n"/>
       <c r="F131" s="4" t="n"/>
@@ -3135,7 +3203,11 @@
           <t>2026-10-13 | New. Settings &gt; Task Settings (admin only): add a task, tick the roles it uses, add many users per role with a branch or All, edit or deactivate a task; list shows who holds each role.</t>
         </is>
       </c>
-      <c r="C134" s="4" t="n"/>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Unknown user / branch ids refused; Item and Stock Location rows always All branches.</t>
+        </is>
+      </c>
       <c r="D134" s="4" t="n"/>
       <c r="E134" s="4" t="n"/>
       <c r="F134" s="4" t="n"/>
@@ -3173,7 +3245,11 @@
           <t>2026-10-13 | New. One definition per dashboard tile: task / role, waiting rule, branch column, page it opens; count and page share it.</t>
         </is>
       </c>
-      <c r="C136" s="4" t="n"/>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Sales repair tiles counted by the repair's branch.</t>
+        </is>
+      </c>
       <c r="D136" s="4" t="n"/>
       <c r="E136" s="4" t="n"/>
       <c r="F136" s="4" t="n"/>
@@ -3263,6 +3339,40 @@
       <c r="E141" s="4" t="n"/>
       <c r="F141" s="4" t="n"/>
       <c r="G141" s="4" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>inc/cis_ajax/jquery_delete_records.php</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | CRITICAL: login + csrf, only the 24 table / column pairs the delete links use, status forced to 0, id bound - it took table, column and value from the post with no login.</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="n"/>
+      <c r="D142" s="4" t="n"/>
+      <c r="E142" s="4" t="n"/>
+      <c r="F142" s="4" t="n"/>
+      <c r="G142" s="4" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>issue_salary.php</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 | Csrf + salary approver for the employee's branch on the server - only the button was hidden.</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="n"/>
+      <c r="D143" s="4" t="n"/>
+      <c r="E143" s="4" t="n"/>
+      <c r="F143" s="4" t="n"/>
+      <c r="G143" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3373,6 +3373,23 @@
       <c r="E143" s="4" t="n"/>
       <c r="F143" s="4" t="n"/>
       <c r="G143" s="4" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>invoice_report.php</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14 | Customer branch read from cus_branch_id - it used branch_id (our branch), so every invoice showed customer branch 1 or 2, even for customers without a branch.</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="n"/>
+      <c r="D144" s="4" t="n"/>
+      <c r="E144" s="4" t="n"/>
+      <c r="F144" s="4" t="n"/>
+      <c r="G144" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1809,7 +1809,11 @@
           <t>2026-10-07 | fnRowCount() added - posted row count, 0 for a missing or single value.</t>
         </is>
       </c>
-      <c r="C60" s="4" t="n"/>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14 | fnIsLoggedIn(); isAdmin also needs the user id and branch - a session with only _user=crm_user (another app on the server) opened pages with no user or branch.</t>
+        </is>
+      </c>
       <c r="D60" s="4" t="n"/>
       <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="n"/>
@@ -3390,6 +3394,23 @@
       <c r="E144" s="4" t="n"/>
       <c r="F144" s="4" t="n"/>
       <c r="G144" s="4" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>inc/cis_ajax/modal_items_dets.php</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14 | Login needed - it answered without one (prices / stock) and logged sql errors for an empty branch.</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="n"/>
+      <c r="D145" s="4" t="n"/>
+      <c r="E145" s="4" t="n"/>
+      <c r="F145" s="4" t="n"/>
+      <c r="G145" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1032,7 +1032,11 @@
           <t>2026-10-13 | Loads task_queues.php.</t>
         </is>
       </c>
-      <c r="F24" s="4" t="n"/>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | Loads revoke.php.</t>
+        </is>
+      </c>
       <c r="G24" s="4" t="n"/>
     </row>
     <row r="25">
@@ -1323,7 +1327,11 @@
           <t>2026-10-13 | Mark as credit follows Sales Order in Accounts verifier - showed to every user (every user holds it to begin with).</t>
         </is>
       </c>
-      <c r="E36" s="4" t="n"/>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | Revoke payment confirm / mark as credit (SALES_RECEIPT R) - back to payment pending; revoke credit approval (CREDIT_SALES R) - back to credit requested. Each only before the next step is approved.</t>
+        </is>
+      </c>
       <c r="F36" s="4" t="n"/>
       <c r="G36" s="4" t="n"/>
     </row>
@@ -1396,7 +1404,11 @@
           <t>2026-10-13 | Csrf token attached in $.ajaxPrefilter - pages passing their own beforeSend dropped the ajaxSetup hook, so their posts had no token.</t>
         </is>
       </c>
-      <c r="G39" s="4" t="n"/>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | Loads js/revoke.js.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2247,7 +2259,11 @@
           <t>2026-10-13 | Approver from Task Settings (SUPPLIER A).</t>
         </is>
       </c>
-      <c r="D81" s="4" t="n"/>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | Revoke (SUPPLIER R) on an approved supplier - back to not approved; refused once used in a PO / GRN / return.</t>
+        </is>
+      </c>
       <c r="E81" s="4" t="n"/>
       <c r="F81" s="4" t="n"/>
       <c r="G81" s="4" t="n"/>
@@ -2306,7 +2322,11 @@
           <t>2026-10-13 | Issue button checked against the employee's branch.</t>
         </is>
       </c>
-      <c r="D84" s="4" t="n"/>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | Revoke next to Issued (SALARY R).</t>
+        </is>
+      </c>
       <c r="E84" s="4" t="n"/>
       <c r="F84" s="4" t="n"/>
       <c r="G84" s="4" t="n"/>
@@ -2327,7 +2347,11 @@
           <t>2026-10-13 | Issue button checked against the employee's branch.</t>
         </is>
       </c>
-      <c r="D85" s="4" t="n"/>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | Revoke next to Issued (SALARY R) - salary set to not issued, its accounts entry removed, Issue shows again.</t>
+        </is>
+      </c>
       <c r="E85" s="4" t="n"/>
       <c r="F85" s="4" t="n"/>
       <c r="G85" s="4" t="n"/>
@@ -2348,7 +2372,11 @@
           <t>2026-10-13 | Issue button checked against the employee's branch.</t>
         </is>
       </c>
-      <c r="D86" s="4" t="n"/>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | Revoke next to Issued (SALARY R).</t>
+        </is>
+      </c>
       <c r="E86" s="4" t="n"/>
       <c r="F86" s="4" t="n"/>
       <c r="G86" s="4" t="n"/>
@@ -2381,7 +2409,11 @@
           <t>2026-10-13 | Approve / reject for approvers in Task Settings (DC A) - was admin or the DC's branch.</t>
         </is>
       </c>
-      <c r="C88" s="4" t="n"/>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | Revoke (DC R) on an approved DC - back to draft; refused once invoiced.</t>
+        </is>
+      </c>
       <c r="D88" s="4" t="n"/>
       <c r="E88" s="4" t="n"/>
       <c r="F88" s="4" t="n"/>
@@ -2767,7 +2799,11 @@
           <t>2026-10-13 | All branches for viewers in Task Settings (SALES_RECEIPT W) - was admin or head office.</t>
         </is>
       </c>
-      <c r="C110" s="4" t="n"/>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | Revoke next to a confirmed payment (SALES_RECEIPT R).</t>
+        </is>
+      </c>
       <c r="D110" s="4" t="n"/>
       <c r="E110" s="4" t="n"/>
       <c r="F110" s="4" t="n"/>
@@ -2827,7 +2863,11 @@
           <t>2026-10-13 | Tile mode: pending suppliers of the user's approver branches; status filter cast to int.</t>
         </is>
       </c>
-      <c r="D113" s="4" t="n"/>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | Approve page link also for Revokers on approved suppliers.</t>
+        </is>
+      </c>
       <c r="E113" s="4" t="n"/>
       <c r="F113" s="4" t="n"/>
       <c r="G113" s="4" t="n"/>
@@ -3042,7 +3082,11 @@
           <t>2026-10-13 | Approve / reject for approvers in Task Settings (PURCHASE_ORDER A) - was admin.</t>
         </is>
       </c>
-      <c r="C125" s="4" t="n"/>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | Revoke for Revokers (PURCHASE_ORDER R) on an approved PO - back to draft; refused once a GRN is made. Last revoke shown.</t>
+        </is>
+      </c>
       <c r="D125" s="4" t="n"/>
       <c r="E125" s="4" t="n"/>
       <c r="F125" s="4" t="n"/>
@@ -3059,7 +3103,11 @@
           <t>2026-10-13 | Approve / reject for approvers in Task Settings (QUOTATION A) - was admin or the quotation's branch.</t>
         </is>
       </c>
-      <c r="C126" s="4" t="n"/>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | Revoke (QUOTATION R) on an approved quotation - back to draft; refused once a sales order / invoice / proforma / requote is made.</t>
+        </is>
+      </c>
       <c r="D126" s="4" t="n"/>
       <c r="E126" s="4" t="n"/>
       <c r="F126" s="4" t="n"/>
@@ -3081,7 +3129,11 @@
           <t>2026-10-13 | Approve / reject buttons follow Sales Order approver - they showed to every user (every user holds it to begin with).</t>
         </is>
       </c>
-      <c r="D127" s="4" t="n"/>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | Revoke (SALES_ORDER R) on an approved sales order - back to in approval (credit sales back to credit approved); refused once a DC / invoice is made.</t>
+        </is>
+      </c>
       <c r="E127" s="4" t="n"/>
       <c r="F127" s="4" t="n"/>
       <c r="G127" s="4" t="n"/>
@@ -3114,7 +3166,11 @@
           <t>2026-10-13 | Approve / reject only for approvers in Task Settings (PURCHASE_RETURN A) - was anyone opening the page.</t>
         </is>
       </c>
-      <c r="C129" s="4" t="n"/>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | Revoke (PURCHASE_RETURN R) on an approved return - back to draft (a rejected return cannot be edited).</t>
+        </is>
+      </c>
       <c r="D129" s="4" t="n"/>
       <c r="E129" s="4" t="n"/>
       <c r="F129" s="4" t="n"/>
@@ -3153,7 +3209,11 @@
           <t>2026-10-13 | Buttons checked against the repair's branch (company_id).</t>
         </is>
       </c>
-      <c r="D131" s="4" t="n"/>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | Revoke under send for approval (back to draft) and approve (back to in approval) - SALES_REPAIR R.</t>
+        </is>
+      </c>
       <c r="E131" s="4" t="n"/>
       <c r="F131" s="4" t="n"/>
       <c r="G131" s="4" t="n"/>
@@ -3212,7 +3272,11 @@
           <t>2026-10-13 | Unknown user / branch ids refused; Item and Stock Location rows always All branches.</t>
         </is>
       </c>
-      <c r="D134" s="4" t="n"/>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | Revoker role (R) - role tick, user rows and a Revoker column on the list.</t>
+        </is>
+      </c>
       <c r="E134" s="4" t="n"/>
       <c r="F134" s="4" t="n"/>
       <c r="G134" s="4" t="n"/>
@@ -3411,6 +3475,91 @@
       <c r="E145" s="4" t="n"/>
       <c r="F145" s="4" t="n"/>
       <c r="G145" s="4" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>db/post_upload_151026.sql</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | New. Revoker role (R) on 10 tasks - mst_task.task_roles widened to 10, notes extended; new table tbl_revoke_log. No user rows: admin only until Revokers are given in Task Settings. Run after post_upload_131026.sql. Safe to run again.</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="n"/>
+      <c r="D146" s="4" t="n"/>
+      <c r="E146" s="4" t="n"/>
+      <c r="F146" s="4" t="n"/>
+      <c r="G146" s="4" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>inc/common/revoke.php</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | New. One entry per form: state it must be in, what blocks it (GRN / sales order / DC / invoice / proforma / requote made on top), state it goes back to. Revoke + log in one transaction, button and last-revoke note helpers.</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="n"/>
+      <c r="D147" s="4" t="n"/>
+      <c r="E147" s="4" t="n"/>
+      <c r="F147" s="4" t="n"/>
+      <c r="G147" s="4" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>inc/cis_ajax/jquery_revoke.php</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | New. The revoke call for every form - login, csrf, Revoker for the document's branch, reason needed; 409 with the reason when refused.</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="n"/>
+      <c r="D148" s="4" t="n"/>
+      <c r="E148" s="4" t="n"/>
+      <c r="F148" s="4" t="n"/>
+      <c r="G148" s="4" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>js/revoke.js</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | New. Revoke button: asks the reason, calls the revoke, reloads or shows why it was refused.</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="n"/>
+      <c r="D149" s="4" t="n"/>
+      <c r="E149" s="4" t="n"/>
+      <c r="F149" s="4" t="n"/>
+      <c r="G149" s="4" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>attendance_report_epf_txt.php</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | EPF text file only takes issued salaries - a revoked one stays in the table with status 0.</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="n"/>
+      <c r="D150" s="4" t="n"/>
+      <c r="E150" s="4" t="n"/>
+      <c r="F150" s="4" t="n"/>
+      <c r="G150" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3423,7 +3572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3519,7 +3668,11 @@
           <t>2026-10-13 | (new table) | One row per task: code checked by the screens, name, module, roles used (C V A W), note, status.</t>
         </is>
       </c>
-      <c r="C2" s="4" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | task_roles | VARCHAR(4) widened to VARCHAR(10); R (Revoker) added to PURCHASE_ORDER, SUPPLIER, PURCHASE_RETURN, QUOTATION, SALES_ORDER, CREDIT_SALES, DC, SALES_RECEIPT, SALES_REPAIR, SALARY.</t>
+        </is>
+      </c>
       <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
@@ -3547,7 +3700,11 @@
           <t>2026-10-13 | (rows) | Sales order approver and payment verifier: every user (head office all branches, others own branch). New task SO_CANCEL for cancel (admin).</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | task_role | New value R (Revoker). No rows added - admin only to begin with.</t>
+        </is>
+      </c>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
@@ -4156,6 +4313,75 @@
       <c r="L25" s="4" t="n"/>
       <c r="M25" s="4" t="n"/>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>tbl_revoke_log</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | (new table) | One row per revoke: form, task, document id / ref, branch, old values (json), reason, who, when.</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>tbl_emp_monthly_salary</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | salary_status | Revoke sets 0 (not issued); the reports already count only 1, the EPF text file now too.</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>tbl_accounts</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | (rows) | Revoking a salary deletes its entry (emp_sal_id).</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3530,12 +3530,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>js/revoke.js</t>
+          <t>db/spac_discount_30_151026.sql</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15 | New. Revoke button: asks the reason, calls the revoke, reloads or shows why it was refused.</t>
+          <t>2026-10-15 | New. SPAC items discount 28% -&gt; 30%: cost price and margin per branch and in the item master, item / selling price unchanged, price history row per item per branch. Safe to run again.</t>
         </is>
       </c>
       <c r="C149" s="4" t="n"/>
@@ -3547,12 +3547,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>attendance_report_epf_txt.php</t>
+          <t>js/revoke.js</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15 | EPF text file only takes issued salaries - a revoked one stays in the table with status 0.</t>
+          <t>2026-10-15 | New. Revoke button: asks the reason, calls the revoke, reloads or shows why it was refused.</t>
         </is>
       </c>
       <c r="C150" s="4" t="n"/>
@@ -3560,6 +3560,23 @@
       <c r="E150" s="4" t="n"/>
       <c r="F150" s="4" t="n"/>
       <c r="G150" s="4" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>attendance_report_epf_txt.php</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | EPF text file only takes issued salaries - a revoked one stays in the table with status 0.</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="n"/>
+      <c r="D151" s="4" t="n"/>
+      <c r="E151" s="4" t="n"/>
+      <c r="F151" s="4" t="n"/>
+      <c r="G151" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3572,7 +3589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4316,12 +4333,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>tbl_revoke_log</t>
+          <t>tbl_itemprice_history</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15 | (new table) | One row per revoke: form, task, document id / ref, branch, old values (json), reason, who, when.</t>
+          <t>2026-10-15 | (rows) | One per SPAC item per branch for the 28% -&gt; 30% discount change.</t>
         </is>
       </c>
       <c r="C26" s="4" t="n"/>
@@ -4339,12 +4356,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>tbl_emp_monthly_salary</t>
+          <t>tbl_revoke_log</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15 | salary_status | Revoke sets 0 (not issued); the reports already count only 1, the EPF text file now too.</t>
+          <t>2026-10-15 | (new table) | One row per revoke: form, task, document id / ref, branch, old values (json), reason, who, when.</t>
         </is>
       </c>
       <c r="C27" s="4" t="n"/>
@@ -4362,12 +4379,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>tbl_accounts</t>
+          <t>tbl_item_stock / tbl_item_details (SPAC)</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15 | (rows) | Revoking a salary deletes its entry (emp_sal_id).</t>
+          <t>2026-10-15 | (rows) | SPAC items: discount 30, cost price and margin recalculated; item and selling price unchanged.</t>
         </is>
       </c>
       <c r="C28" s="4" t="n"/>
@@ -4382,6 +4399,52 @@
       <c r="L28" s="4" t="n"/>
       <c r="M28" s="4" t="n"/>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>tbl_emp_monthly_salary</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | salary_status | Revoke sets 0 (not issued); the reports already count only 1, the EPF text file now too.</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" s="4" t="n"/>
+      <c r="L29" s="4" t="n"/>
+      <c r="M29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>tbl_accounts</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 | (rows) | Revoking a salary deletes its entry (emp_sal_id).</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="4" t="n"/>
+      <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:H158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -473,6 +473,7 @@
     <col width="62" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
     <col width="62" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -509,6 +510,11 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Change 6</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Change 7</t>
         </is>
       </c>
     </row>
@@ -528,6 +534,7 @@
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -549,6 +556,7 @@
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -566,6 +574,7 @@
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -587,6 +596,7 @@
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -616,6 +626,7 @@
       </c>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -649,6 +660,7 @@
         </is>
       </c>
       <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -682,6 +694,7 @@
         </is>
       </c>
       <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -715,6 +728,7 @@
         </is>
       </c>
       <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -752,6 +766,11 @@
           <t>2026-10-13 | updated_by from _user_id (was empty).</t>
         </is>
       </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16 | Margin on cost (was on item price), branch and multi-UOM rows; price / discount no longer rewrite the selling price; loaded margin shown on cost.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -784,7 +803,12 @@
           <t>2026-10-13 | Price block check uses Task Settings (ITEM C) - was user 1; both branches show it.</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16 | Price fields use js/price_calc.js - price / discount no longer rewrite the selling price.</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -802,6 +826,7 @@
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -819,6 +844,7 @@
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -840,6 +866,7 @@
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -857,6 +884,7 @@
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n"/>
       <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -874,6 +902,7 @@
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
       <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -899,6 +928,7 @@
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="n"/>
       <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -916,6 +946,7 @@
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -933,6 +964,7 @@
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="n"/>
       <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -950,6 +982,7 @@
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -967,6 +1000,7 @@
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
       <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -984,6 +1018,7 @@
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
       <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1005,6 +1040,7 @@
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="n"/>
       <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1038,6 +1074,7 @@
         </is>
       </c>
       <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1059,6 +1096,7 @@
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1088,6 +1126,7 @@
       </c>
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1113,6 +1152,7 @@
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="n"/>
       <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1146,6 +1186,7 @@
         </is>
       </c>
       <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1171,6 +1212,7 @@
       <c r="E29" s="4" t="n"/>
       <c r="F29" s="4" t="n"/>
       <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1200,6 +1242,7 @@
       </c>
       <c r="F30" s="4" t="n"/>
       <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1229,6 +1272,7 @@
       </c>
       <c r="F31" s="4" t="n"/>
       <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1250,6 +1294,7 @@
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1271,6 +1316,7 @@
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n"/>
       <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1288,6 +1334,7 @@
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1305,6 +1352,7 @@
       <c r="E35" s="4" t="n"/>
       <c r="F35" s="4" t="n"/>
       <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1334,6 +1382,7 @@
       </c>
       <c r="F36" s="4" t="n"/>
       <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1355,6 +1404,7 @@
       <c r="E37" s="4" t="n"/>
       <c r="F37" s="4" t="n"/>
       <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1372,6 +1422,7 @@
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="n"/>
       <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1407,6 +1458,11 @@
       <c r="G39" s="3" t="inlineStr">
         <is>
           <t>2026-10-15 | Loads js/revoke.js.</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16 | Loads js/price_calc.js.</t>
         </is>
       </c>
     </row>
@@ -1426,6 +1482,7 @@
       <c r="E40" s="4" t="n"/>
       <c r="F40" s="4" t="n"/>
       <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1443,6 +1500,7 @@
       <c r="E41" s="4" t="n"/>
       <c r="F41" s="4" t="n"/>
       <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1460,6 +1518,7 @@
       <c r="E42" s="4" t="n"/>
       <c r="F42" s="4" t="n"/>
       <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1481,6 +1540,7 @@
       <c r="E43" s="4" t="n"/>
       <c r="F43" s="4" t="n"/>
       <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1498,6 +1558,7 @@
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="n"/>
       <c r="G44" s="4" t="n"/>
+      <c r="H44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1519,6 +1580,7 @@
       <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="n"/>
       <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1536,6 +1598,7 @@
       <c r="E46" s="4" t="n"/>
       <c r="F46" s="4" t="n"/>
       <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1553,6 +1616,7 @@
       <c r="E47" s="4" t="n"/>
       <c r="F47" s="4" t="n"/>
       <c r="G47" s="4" t="n"/>
+      <c r="H47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1570,6 +1634,7 @@
       <c r="E48" s="4" t="n"/>
       <c r="F48" s="4" t="n"/>
       <c r="G48" s="4" t="n"/>
+      <c r="H48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1591,6 +1656,7 @@
       <c r="E49" s="4" t="n"/>
       <c r="F49" s="4" t="n"/>
       <c r="G49" s="4" t="n"/>
+      <c r="H49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1608,6 +1674,7 @@
       <c r="E50" s="4" t="n"/>
       <c r="F50" s="4" t="n"/>
       <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1629,6 +1696,7 @@
       <c r="E51" s="4" t="n"/>
       <c r="F51" s="4" t="n"/>
       <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1646,6 +1714,7 @@
       <c r="E52" s="4" t="n"/>
       <c r="F52" s="4" t="n"/>
       <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1675,6 +1744,7 @@
       </c>
       <c r="F53" s="4" t="n"/>
       <c r="G53" s="4" t="n"/>
+      <c r="H53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1692,6 +1762,7 @@
       <c r="E54" s="4" t="n"/>
       <c r="F54" s="4" t="n"/>
       <c r="G54" s="4" t="n"/>
+      <c r="H54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1709,6 +1780,7 @@
       <c r="E55" s="4" t="n"/>
       <c r="F55" s="4" t="n"/>
       <c r="G55" s="4" t="n"/>
+      <c r="H55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1738,6 +1810,7 @@
       </c>
       <c r="F56" s="4" t="n"/>
       <c r="G56" s="4" t="n"/>
+      <c r="H56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1767,6 +1840,7 @@
       </c>
       <c r="F57" s="4" t="n"/>
       <c r="G57" s="4" t="n"/>
+      <c r="H57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1792,6 +1866,7 @@
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="n"/>
       <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -1809,6 +1884,7 @@
       <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="n"/>
       <c r="G59" s="4" t="n"/>
+      <c r="H59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1830,6 +1906,7 @@
       <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
+      <c r="H60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -1847,6 +1924,7 @@
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="n"/>
       <c r="G61" s="4" t="n"/>
+      <c r="H61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -1864,6 +1942,7 @@
       <c r="E62" s="4" t="n"/>
       <c r="F62" s="4" t="n"/>
       <c r="G62" s="4" t="n"/>
+      <c r="H62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -1881,6 +1960,7 @@
       <c r="E63" s="4" t="n"/>
       <c r="F63" s="4" t="n"/>
       <c r="G63" s="4" t="n"/>
+      <c r="H63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -1898,6 +1978,7 @@
       <c r="E64" s="4" t="n"/>
       <c r="F64" s="4" t="n"/>
       <c r="G64" s="4" t="n"/>
+      <c r="H64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -1915,6 +1996,7 @@
       <c r="E65" s="4" t="n"/>
       <c r="F65" s="4" t="n"/>
       <c r="G65" s="4" t="n"/>
+      <c r="H65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -1932,6 +2014,7 @@
       <c r="E66" s="4" t="n"/>
       <c r="F66" s="4" t="n"/>
       <c r="G66" s="4" t="n"/>
+      <c r="H66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -1949,6 +2032,7 @@
       <c r="E67" s="4" t="n"/>
       <c r="F67" s="4" t="n"/>
       <c r="G67" s="4" t="n"/>
+      <c r="H67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -1970,6 +2054,7 @@
       <c r="E68" s="4" t="n"/>
       <c r="F68" s="4" t="n"/>
       <c r="G68" s="4" t="n"/>
+      <c r="H68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -1987,6 +2072,7 @@
       <c r="E69" s="4" t="n"/>
       <c r="F69" s="4" t="n"/>
       <c r="G69" s="4" t="n"/>
+      <c r="H69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2004,6 +2090,7 @@
       <c r="E70" s="4" t="n"/>
       <c r="F70" s="4" t="n"/>
       <c r="G70" s="4" t="n"/>
+      <c r="H70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2021,6 +2108,7 @@
       <c r="E71" s="4" t="n"/>
       <c r="F71" s="4" t="n"/>
       <c r="G71" s="4" t="n"/>
+      <c r="H71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2050,6 +2138,7 @@
       </c>
       <c r="F72" s="4" t="n"/>
       <c r="G72" s="4" t="n"/>
+      <c r="H72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2075,6 +2164,7 @@
       <c r="E73" s="4" t="n"/>
       <c r="F73" s="4" t="n"/>
       <c r="G73" s="4" t="n"/>
+      <c r="H73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2100,6 +2190,7 @@
       <c r="E74" s="4" t="n"/>
       <c r="F74" s="4" t="n"/>
       <c r="G74" s="4" t="n"/>
+      <c r="H74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2125,6 +2216,7 @@
       <c r="E75" s="4" t="n"/>
       <c r="F75" s="4" t="n"/>
       <c r="G75" s="4" t="n"/>
+      <c r="H75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2150,6 +2242,7 @@
       <c r="E76" s="4" t="n"/>
       <c r="F76" s="4" t="n"/>
       <c r="G76" s="4" t="n"/>
+      <c r="H76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2175,6 +2268,7 @@
       <c r="E77" s="4" t="n"/>
       <c r="F77" s="4" t="n"/>
       <c r="G77" s="4" t="n"/>
+      <c r="H77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2200,6 +2294,7 @@
       <c r="E78" s="4" t="n"/>
       <c r="F78" s="4" t="n"/>
       <c r="G78" s="4" t="n"/>
+      <c r="H78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2221,6 +2316,7 @@
       <c r="E79" s="4" t="n"/>
       <c r="F79" s="4" t="n"/>
       <c r="G79" s="4" t="n"/>
+      <c r="H79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2242,6 +2338,7 @@
       <c r="E80" s="4" t="n"/>
       <c r="F80" s="4" t="n"/>
       <c r="G80" s="4" t="n"/>
+      <c r="H80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -2267,6 +2364,7 @@
       <c r="E81" s="4" t="n"/>
       <c r="F81" s="4" t="n"/>
       <c r="G81" s="4" t="n"/>
+      <c r="H81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -2288,6 +2386,7 @@
       <c r="E82" s="4" t="n"/>
       <c r="F82" s="4" t="n"/>
       <c r="G82" s="4" t="n"/>
+      <c r="H82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -2305,6 +2404,7 @@
       <c r="E83" s="4" t="n"/>
       <c r="F83" s="4" t="n"/>
       <c r="G83" s="4" t="n"/>
+      <c r="H83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2330,6 +2430,7 @@
       <c r="E84" s="4" t="n"/>
       <c r="F84" s="4" t="n"/>
       <c r="G84" s="4" t="n"/>
+      <c r="H84" s="4" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -2355,6 +2456,7 @@
       <c r="E85" s="4" t="n"/>
       <c r="F85" s="4" t="n"/>
       <c r="G85" s="4" t="n"/>
+      <c r="H85" s="4" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2380,6 +2482,7 @@
       <c r="E86" s="4" t="n"/>
       <c r="F86" s="4" t="n"/>
       <c r="G86" s="4" t="n"/>
+      <c r="H86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -2397,6 +2500,7 @@
       <c r="E87" s="4" t="n"/>
       <c r="F87" s="4" t="n"/>
       <c r="G87" s="4" t="n"/>
+      <c r="H87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2418,6 +2522,7 @@
       <c r="E88" s="4" t="n"/>
       <c r="F88" s="4" t="n"/>
       <c r="G88" s="4" t="n"/>
+      <c r="H88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -2435,6 +2540,7 @@
       <c r="E89" s="4" t="n"/>
       <c r="F89" s="4" t="n"/>
       <c r="G89" s="4" t="n"/>
+      <c r="H89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -2452,6 +2558,7 @@
       <c r="E90" s="4" t="n"/>
       <c r="F90" s="4" t="n"/>
       <c r="G90" s="4" t="n"/>
+      <c r="H90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -2469,6 +2576,7 @@
       <c r="E91" s="4" t="n"/>
       <c r="F91" s="4" t="n"/>
       <c r="G91" s="4" t="n"/>
+      <c r="H91" s="4" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -2486,6 +2594,7 @@
       <c r="E92" s="4" t="n"/>
       <c r="F92" s="4" t="n"/>
       <c r="G92" s="4" t="n"/>
+      <c r="H92" s="4" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -2503,6 +2612,7 @@
       <c r="E93" s="4" t="n"/>
       <c r="F93" s="4" t="n"/>
       <c r="G93" s="4" t="n"/>
+      <c r="H93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -2528,6 +2638,7 @@
       <c r="E94" s="4" t="n"/>
       <c r="F94" s="4" t="n"/>
       <c r="G94" s="4" t="n"/>
+      <c r="H94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -2545,6 +2656,7 @@
       <c r="E95" s="4" t="n"/>
       <c r="F95" s="4" t="n"/>
       <c r="G95" s="4" t="n"/>
+      <c r="H95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -2562,6 +2674,7 @@
       <c r="E96" s="4" t="n"/>
       <c r="F96" s="4" t="n"/>
       <c r="G96" s="4" t="n"/>
+      <c r="H96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -2579,6 +2692,7 @@
       <c r="E97" s="4" t="n"/>
       <c r="F97" s="4" t="n"/>
       <c r="G97" s="4" t="n"/>
+      <c r="H97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -2596,6 +2710,7 @@
       <c r="E98" s="4" t="n"/>
       <c r="F98" s="4" t="n"/>
       <c r="G98" s="4" t="n"/>
+      <c r="H98" s="4" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -2617,6 +2732,7 @@
       <c r="E99" s="4" t="n"/>
       <c r="F99" s="4" t="n"/>
       <c r="G99" s="4" t="n"/>
+      <c r="H99" s="4" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -2634,6 +2750,7 @@
       <c r="E100" s="4" t="n"/>
       <c r="F100" s="4" t="n"/>
       <c r="G100" s="4" t="n"/>
+      <c r="H100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -2651,6 +2768,7 @@
       <c r="E101" s="4" t="n"/>
       <c r="F101" s="4" t="n"/>
       <c r="G101" s="4" t="n"/>
+      <c r="H101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -2668,6 +2786,7 @@
       <c r="E102" s="4" t="n"/>
       <c r="F102" s="4" t="n"/>
       <c r="G102" s="4" t="n"/>
+      <c r="H102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -2685,6 +2804,7 @@
       <c r="E103" s="4" t="n"/>
       <c r="F103" s="4" t="n"/>
       <c r="G103" s="4" t="n"/>
+      <c r="H103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -2702,6 +2822,7 @@
       <c r="E104" s="4" t="n"/>
       <c r="F104" s="4" t="n"/>
       <c r="G104" s="4" t="n"/>
+      <c r="H104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -2719,6 +2840,7 @@
       <c r="E105" s="4" t="n"/>
       <c r="F105" s="4" t="n"/>
       <c r="G105" s="4" t="n"/>
+      <c r="H105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -2736,6 +2858,7 @@
       <c r="E106" s="4" t="n"/>
       <c r="F106" s="4" t="n"/>
       <c r="G106" s="4" t="n"/>
+      <c r="H106" s="4" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -2753,6 +2876,7 @@
       <c r="E107" s="4" t="n"/>
       <c r="F107" s="4" t="n"/>
       <c r="G107" s="4" t="n"/>
+      <c r="H107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -2770,6 +2894,7 @@
       <c r="E108" s="4" t="n"/>
       <c r="F108" s="4" t="n"/>
       <c r="G108" s="4" t="n"/>
+      <c r="H108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -2787,6 +2912,7 @@
       <c r="E109" s="4" t="n"/>
       <c r="F109" s="4" t="n"/>
       <c r="G109" s="4" t="n"/>
+      <c r="H109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -2808,6 +2934,7 @@
       <c r="E110" s="4" t="n"/>
       <c r="F110" s="4" t="n"/>
       <c r="G110" s="4" t="n"/>
+      <c r="H110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -2829,6 +2956,7 @@
       <c r="E111" s="4" t="n"/>
       <c r="F111" s="4" t="n"/>
       <c r="G111" s="4" t="n"/>
+      <c r="H111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -2846,6 +2974,7 @@
       <c r="E112" s="4" t="n"/>
       <c r="F112" s="4" t="n"/>
       <c r="G112" s="4" t="n"/>
+      <c r="H112" s="4" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -2871,6 +3000,7 @@
       <c r="E113" s="4" t="n"/>
       <c r="F113" s="4" t="n"/>
       <c r="G113" s="4" t="n"/>
+      <c r="H113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -2888,6 +3018,7 @@
       <c r="E114" s="4" t="n"/>
       <c r="F114" s="4" t="n"/>
       <c r="G114" s="4" t="n"/>
+      <c r="H114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -2905,6 +3036,7 @@
       <c r="E115" s="4" t="n"/>
       <c r="F115" s="4" t="n"/>
       <c r="G115" s="4" t="n"/>
+      <c r="H115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -2922,6 +3054,7 @@
       <c r="E116" s="4" t="n"/>
       <c r="F116" s="4" t="n"/>
       <c r="G116" s="4" t="n"/>
+      <c r="H116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -2943,6 +3076,7 @@
       <c r="E117" s="4" t="n"/>
       <c r="F117" s="4" t="n"/>
       <c r="G117" s="4" t="n"/>
+      <c r="H117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -2960,6 +3094,7 @@
       <c r="E118" s="4" t="n"/>
       <c r="F118" s="4" t="n"/>
       <c r="G118" s="4" t="n"/>
+      <c r="H118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -2977,6 +3112,7 @@
       <c r="E119" s="4" t="n"/>
       <c r="F119" s="4" t="n"/>
       <c r="G119" s="4" t="n"/>
+      <c r="H119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -2994,6 +3130,7 @@
       <c r="E120" s="4" t="n"/>
       <c r="F120" s="4" t="n"/>
       <c r="G120" s="4" t="n"/>
+      <c r="H120" s="4" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -3011,6 +3148,7 @@
       <c r="E121" s="4" t="n"/>
       <c r="F121" s="4" t="n"/>
       <c r="G121" s="4" t="n"/>
+      <c r="H121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -3028,6 +3166,7 @@
       <c r="E122" s="4" t="n"/>
       <c r="F122" s="4" t="n"/>
       <c r="G122" s="4" t="n"/>
+      <c r="H122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -3053,6 +3192,7 @@
       <c r="E123" s="4" t="n"/>
       <c r="F123" s="4" t="n"/>
       <c r="G123" s="4" t="n"/>
+      <c r="H123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -3070,6 +3210,7 @@
       <c r="E124" s="4" t="n"/>
       <c r="F124" s="4" t="n"/>
       <c r="G124" s="4" t="n"/>
+      <c r="H124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -3091,6 +3232,7 @@
       <c r="E125" s="4" t="n"/>
       <c r="F125" s="4" t="n"/>
       <c r="G125" s="4" t="n"/>
+      <c r="H125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -3112,6 +3254,7 @@
       <c r="E126" s="4" t="n"/>
       <c r="F126" s="4" t="n"/>
       <c r="G126" s="4" t="n"/>
+      <c r="H126" s="4" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -3137,6 +3280,7 @@
       <c r="E127" s="4" t="n"/>
       <c r="F127" s="4" t="n"/>
       <c r="G127" s="4" t="n"/>
+      <c r="H127" s="4" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -3154,6 +3298,7 @@
       <c r="E128" s="4" t="n"/>
       <c r="F128" s="4" t="n"/>
       <c r="G128" s="4" t="n"/>
+      <c r="H128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -3175,6 +3320,7 @@
       <c r="E129" s="4" t="n"/>
       <c r="F129" s="4" t="n"/>
       <c r="G129" s="4" t="n"/>
+      <c r="H129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -3192,6 +3338,7 @@
       <c r="E130" s="4" t="n"/>
       <c r="F130" s="4" t="n"/>
       <c r="G130" s="4" t="n"/>
+      <c r="H130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -3217,6 +3364,7 @@
       <c r="E131" s="4" t="n"/>
       <c r="F131" s="4" t="n"/>
       <c r="G131" s="4" t="n"/>
+      <c r="H131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -3234,6 +3382,7 @@
       <c r="E132" s="4" t="n"/>
       <c r="F132" s="4" t="n"/>
       <c r="G132" s="4" t="n"/>
+      <c r="H132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -3255,6 +3404,7 @@
       <c r="E133" s="4" t="n"/>
       <c r="F133" s="4" t="n"/>
       <c r="G133" s="4" t="n"/>
+      <c r="H133" s="4" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -3280,6 +3430,7 @@
       <c r="E134" s="4" t="n"/>
       <c r="F134" s="4" t="n"/>
       <c r="G134" s="4" t="n"/>
+      <c r="H134" s="4" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -3301,6 +3452,7 @@
       <c r="E135" s="4" t="n"/>
       <c r="F135" s="4" t="n"/>
       <c r="G135" s="4" t="n"/>
+      <c r="H135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -3322,6 +3474,7 @@
       <c r="E136" s="4" t="n"/>
       <c r="F136" s="4" t="n"/>
       <c r="G136" s="4" t="n"/>
+      <c r="H136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -3339,6 +3492,7 @@
       <c r="E137" s="4" t="n"/>
       <c r="F137" s="4" t="n"/>
       <c r="G137" s="4" t="n"/>
+      <c r="H137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -3356,6 +3510,7 @@
       <c r="E138" s="4" t="n"/>
       <c r="F138" s="4" t="n"/>
       <c r="G138" s="4" t="n"/>
+      <c r="H138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -3373,6 +3528,7 @@
       <c r="E139" s="4" t="n"/>
       <c r="F139" s="4" t="n"/>
       <c r="G139" s="4" t="n"/>
+      <c r="H139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -3390,6 +3546,7 @@
       <c r="E140" s="4" t="n"/>
       <c r="F140" s="4" t="n"/>
       <c r="G140" s="4" t="n"/>
+      <c r="H140" s="4" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -3407,6 +3564,7 @@
       <c r="E141" s="4" t="n"/>
       <c r="F141" s="4" t="n"/>
       <c r="G141" s="4" t="n"/>
+      <c r="H141" s="4" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -3424,6 +3582,7 @@
       <c r="E142" s="4" t="n"/>
       <c r="F142" s="4" t="n"/>
       <c r="G142" s="4" t="n"/>
+      <c r="H142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -3441,6 +3600,7 @@
       <c r="E143" s="4" t="n"/>
       <c r="F143" s="4" t="n"/>
       <c r="G143" s="4" t="n"/>
+      <c r="H143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -3458,6 +3618,7 @@
       <c r="E144" s="4" t="n"/>
       <c r="F144" s="4" t="n"/>
       <c r="G144" s="4" t="n"/>
+      <c r="H144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -3475,6 +3636,7 @@
       <c r="E145" s="4" t="n"/>
       <c r="F145" s="4" t="n"/>
       <c r="G145" s="4" t="n"/>
+      <c r="H145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -3492,6 +3654,7 @@
       <c r="E146" s="4" t="n"/>
       <c r="F146" s="4" t="n"/>
       <c r="G146" s="4" t="n"/>
+      <c r="H146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -3509,6 +3672,7 @@
       <c r="E147" s="4" t="n"/>
       <c r="F147" s="4" t="n"/>
       <c r="G147" s="4" t="n"/>
+      <c r="H147" s="4" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -3526,6 +3690,7 @@
       <c r="E148" s="4" t="n"/>
       <c r="F148" s="4" t="n"/>
       <c r="G148" s="4" t="n"/>
+      <c r="H148" s="4" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -3543,6 +3708,7 @@
       <c r="E149" s="4" t="n"/>
       <c r="F149" s="4" t="n"/>
       <c r="G149" s="4" t="n"/>
+      <c r="H149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -3560,6 +3726,7 @@
       <c r="E150" s="4" t="n"/>
       <c r="F150" s="4" t="n"/>
       <c r="G150" s="4" t="n"/>
+      <c r="H150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -3577,6 +3744,133 @@
       <c r="E151" s="4" t="n"/>
       <c r="F151" s="4" t="n"/>
       <c r="G151" s="4" t="n"/>
+      <c r="H151" s="4" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>js/price_calc.js</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16 | New. One price rule for every screen: cost = price less discount, margin % on cost; selling changes only from margin or selling.</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="n"/>
+      <c r="D152" s="4" t="n"/>
+      <c r="E152" s="4" t="n"/>
+      <c r="F152" s="4" t="n"/>
+      <c r="G152" s="4" t="n"/>
+      <c r="H152" s="4" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>item_bulk_discount.php</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16 | New screen Item Masters &gt; Bulk Discount / Margin - one discount or margin % for a filtered item set in chosen branches, one save, history per row.</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="n"/>
+      <c r="D153" s="4" t="n"/>
+      <c r="E153" s="4" t="n"/>
+      <c r="F153" s="4" t="n"/>
+      <c r="G153" s="4" t="n"/>
+      <c r="H153" s="4" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>item_price_list.php</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16 | New screen Item Masters &gt; Item Price Update - filtered list of one branch, price / discount / margin / selling boxes, save per row.</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="n"/>
+      <c r="D154" s="4" t="n"/>
+      <c r="E154" s="4" t="n"/>
+      <c r="F154" s="4" t="n"/>
+      <c r="G154" s="4" t="n"/>
+      <c r="H154" s="4" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>inc/common/item_price_filters.php</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16 | New. Principal / brand / division / item type / search filters shared by the two screens.</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="n"/>
+      <c r="D155" s="4" t="n"/>
+      <c r="E155" s="4" t="n"/>
+      <c r="F155" s="4" t="n"/>
+      <c r="G155" s="4" t="n"/>
+      <c r="H155" s="4" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>inc/common/item_price.php</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16 | New. Price list, one-row save and set-based bulk save per branch; history rows; Head Office copied to the item master.</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="n"/>
+      <c r="D156" s="4" t="n"/>
+      <c r="E156" s="4" t="n"/>
+      <c r="F156" s="4" t="n"/>
+      <c r="G156" s="4" t="n"/>
+      <c r="H156" s="4" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>inc/cis_ajax/jquery_item_price.php</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16 | New. List / save row / bulk calls - login, csrf, ITEM C or admin; cost and margin worked out on the server.</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="n"/>
+      <c r="D157" s="4" t="n"/>
+      <c r="E157" s="4" t="n"/>
+      <c r="F157" s="4" t="n"/>
+      <c r="G157" s="4" t="n"/>
+      <c r="H157" s="4" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>db/post_upload_161026.sql</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16 | New. Two menus + rights for Item creators, index on tbl_item_stock.item_id and tbl_itemprice_history (item_id, branch_id), stored margins recalculated on cost.</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="n"/>
+      <c r="D158" s="4" t="n"/>
+      <c r="E158" s="4" t="n"/>
+      <c r="F158" s="4" t="n"/>
+      <c r="G158" s="4" t="n"/>
+      <c r="H158" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3589,7 +3883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4103,8 +4397,16 @@
           <t>2026-09-22 | (no schema change) | Qty columns are now only written through fnApplyStockMovement(), never directly.</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16 | item_id | Index added - lookups by item scanned the whole table.</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16 | ho / kl / rjpm _item_margin | Recalculated on cost: (selling - cost) / cost x 100, 0 without cost or selling. Prices untouched.</t>
+        </is>
+      </c>
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
       <c r="G16" s="4" t="n"/>
@@ -4318,7 +4620,11 @@
           <t>2026-09-22 | item_curr_stock | No change. Noted as dead - every write to it was already commented out. Branch columns in tbl_item_stock are the live balance.</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16 | margin_percent | Recalculated on cost, same rule. Head Office price changes from the new screens are copied here.</t>
+        </is>
+      </c>
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
@@ -4341,8 +4647,16 @@
           <t>2026-10-15 | (rows) | One per SPAC item per branch for the 28% -&gt; 30% discount change.</t>
         </is>
       </c>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16 | item_branch | Index (item_id, branch_id) added.</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16 | (rows) | One per item per branch for every change from Bulk Discount / Margin and Item Price Update.</t>
+        </is>
+      </c>
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
@@ -4445,6 +4759,29 @@
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>mst_sub_menu / tbl_user_rights</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16 | (rows) | Item Masters &gt; Bulk Discount / Margin and Item Price Update; rights for Item creators (ITEM C).</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H158"/>
+  <dimension ref="A1:H159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2817,7 +2817,11 @@
           <t>2026-10-13 | Edit / price / branch / delete links for creators in Task Settings (ITEM C) - was admin at head office.</t>
         </is>
       </c>
-      <c r="C104" s="4" t="n"/>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16 | Principal filter; brand / principal as numbers and search text quoted - they went into the sql as typed.</t>
+        </is>
+      </c>
       <c r="D104" s="4" t="n"/>
       <c r="E104" s="4" t="n"/>
       <c r="F104" s="4" t="n"/>
@@ -3757,7 +3761,11 @@
           <t>2026-10-16 | New. One price rule for every screen: cost = price less discount, margin % on cost; selling changes only from margin or selling.</t>
         </is>
       </c>
-      <c r="C152" s="4" t="n"/>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16 | fnPrice.busy() - small please-wait loader over the page, calls can overlap.</t>
+        </is>
+      </c>
       <c r="D152" s="4" t="n"/>
       <c r="E152" s="4" t="n"/>
       <c r="F152" s="4" t="n"/>
@@ -3775,7 +3783,11 @@
           <t>2026-10-16 | New screen Item Masters &gt; Bulk Discount / Margin - one discount or margin % for a filtered item set in chosen branches, one save, history per row.</t>
         </is>
       </c>
-      <c r="C153" s="4" t="n"/>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16 | Loader while loading / redrawing / saving; preview redraws 300 ms after typing; branches on their own line.</t>
+        </is>
+      </c>
       <c r="D153" s="4" t="n"/>
       <c r="E153" s="4" t="n"/>
       <c r="F153" s="4" t="n"/>
@@ -3793,7 +3805,11 @@
           <t>2026-10-16 | New screen Item Masters &gt; Item Price Update - filtered list of one branch, price / discount / margin / selling boxes, save per row.</t>
         </is>
       </c>
-      <c r="C154" s="4" t="n"/>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16 | Loader while loading and saving a row.</t>
+        </is>
+      </c>
       <c r="D154" s="4" t="n"/>
       <c r="E154" s="4" t="n"/>
       <c r="F154" s="4" t="n"/>
@@ -3871,6 +3887,24 @@
       <c r="F158" s="4" t="n"/>
       <c r="G158" s="4" t="n"/>
       <c r="H158" s="4" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>lst_item_details.php</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16 | Principal filter (name - code) next to Brand.</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="n"/>
+      <c r="D159" s="4" t="n"/>
+      <c r="E159" s="4" t="n"/>
+      <c r="F159" s="4" t="n"/>
+      <c r="G159" s="4" t="n"/>
+      <c r="H159" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H159"/>
+  <dimension ref="A1:H160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1742,7 +1742,11 @@
           <t>2026-10-13 | Edit paid amount for approvers in Task Settings (GRN_PAYMENT A) - was admin.</t>
         </is>
       </c>
-      <c r="F53" s="4" t="n"/>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 | Bill save: status and balance from payments made (was reset to Pending, old balance kept); bill below paid refused. Payment save: balance worked out on the server. Multiple GRN linked by supplier and branch (was same PO only); payments table balance uses all payments.</t>
+        </is>
+      </c>
       <c r="G53" s="4" t="n"/>
       <c r="H53" s="4" t="n"/>
     </row>
@@ -2607,7 +2611,11 @@
           <t>2026-10-13 | Branch filter for viewers in Task Settings (GRN_PAYMENT W) - was head office.</t>
         </is>
       </c>
-      <c r="C93" s="4" t="n"/>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 | Status filter and page number set before use - PHP 8 warning broke the page script.</t>
+        </is>
+      </c>
       <c r="D93" s="4" t="n"/>
       <c r="E93" s="4" t="n"/>
       <c r="F93" s="4" t="n"/>
@@ -2781,7 +2789,11 @@
           <t>2026-10-13 | All branches for viewers in Task Settings (GRN_PAYMENT W) - was admin or head office.</t>
         </is>
       </c>
-      <c r="C102" s="4" t="n"/>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 | Status from the saved status, paid 0.00 when none; filters / sort as numbers and column names, search quoted.</t>
+        </is>
+      </c>
       <c r="D102" s="4" t="n"/>
       <c r="E102" s="4" t="n"/>
       <c r="F102" s="4" t="n"/>
@@ -3905,6 +3917,24 @@
       <c r="F159" s="4" t="n"/>
       <c r="G159" s="4" t="n"/>
       <c r="H159" s="4" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>db/grn_pay_status_fix_221026.sql</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 | New. Links GRNs of old multiple bills, recalculates GRN payment status and balance, lists GRNs billed twice for review.</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="n"/>
+      <c r="D160" s="4" t="n"/>
+      <c r="E160" s="4" t="n"/>
+      <c r="F160" s="4" t="n"/>
+      <c r="G160" s="4" t="n"/>
+      <c r="H160" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3917,7 +3947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4796,12 +4826,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>mst_sub_menu / tbl_user_rights</t>
+          <t>tbl_grn (GRN payment)</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16 | (rows) | Item Masters &gt; Bulk Discount / Margin and Item Price Update; rights for Item creators (ITEM C).</t>
+          <t>2026-10-22 | grn_pay_finished_status / grn_bal_value | Recalculated from the payments; pay_type / grn_ids set on GRNs covered by another GRN's multiple bill.</t>
         </is>
       </c>
       <c r="C31" s="4" t="n"/>
@@ -4816,6 +4846,29 @@
       <c r="L31" s="4" t="n"/>
       <c r="M31" s="4" t="n"/>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>mst_sub_menu / tbl_user_rights</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16 | (rows) | Item Masters &gt; Bulk Discount / Margin and Item Price Update; rights for Item creators (ITEM C).</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -1747,7 +1747,11 @@
           <t>2026-10-22 | Bill save: status and balance from payments made (was reset to Pending, old balance kept); bill below paid refused. Payment save: balance worked out on the server. Multiple GRN linked by supplier and branch (was same PO only); payments table balance uses all payments.</t>
         </is>
       </c>
-      <c r="G53" s="4" t="n"/>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 | No bill yet checked as amount 0, not the text '0.000' - with a 2-decimal amount the bill amount was locked and Save hidden.</t>
+        </is>
+      </c>
       <c r="H53" s="4" t="n"/>
     </row>
     <row r="54">
@@ -2794,7 +2798,11 @@
           <t>2026-10-22 | Status from the saved status, paid 0.00 when none; filters / sort as numbers and column names, search quoted.</t>
         </is>
       </c>
-      <c r="D102" s="4" t="n"/>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 | Multiple rows: edit icon opens the main GRN's payment page.</t>
+        </is>
+      </c>
       <c r="E102" s="4" t="n"/>
       <c r="F102" s="4" t="n"/>
       <c r="G102" s="4" t="n"/>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H160"/>
+  <dimension ref="A1:H162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3929,12 +3929,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>db/grn_pay_status_fix_221026.sql</t>
+          <t>rpt_sales_order.php</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22 | New. Links GRNs of old multiple bills, recalculates GRN payment status and balance, lists GRNs billed twice for review.</t>
+          <t>2026-10-22 | Partial opens a popup with the SO's items and their stage (linked to a page that does not exist); dispatched qty from dc_dispatch_qty (dc_qty repeats the ordered qty per DC); dead fnValidate() call removed.</t>
         </is>
       </c>
       <c r="C160" s="4" t="n"/>
@@ -3943,6 +3943,42 @@
       <c r="F160" s="4" t="n"/>
       <c r="G160" s="4" t="n"/>
       <c r="H160" s="4" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>inc/cis_ajax/jquery_so_item_status.php</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 | New. SO items with ordered / DC / invoiced / pending qty, stock, stage, DC and invoice numbers - login + csrf.</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="n"/>
+      <c r="D161" s="4" t="n"/>
+      <c r="E161" s="4" t="n"/>
+      <c r="F161" s="4" t="n"/>
+      <c r="G161" s="4" t="n"/>
+      <c r="H161" s="4" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>db/grn_pay_status_fix_221026.sql</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 | New. Links GRNs of old multiple bills, recalculates GRN payment status and balance, lists GRNs billed twice for review.</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="n"/>
+      <c r="D162" s="4" t="n"/>
+      <c r="E162" s="4" t="n"/>
+      <c r="F162" s="4" t="n"/>
+      <c r="G162" s="4" t="n"/>
+      <c r="H162" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H162"/>
+  <dimension ref="A1:H166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3937,7 +3937,11 @@
           <t>2026-10-22 | Partial opens a popup with the SO's items and their stage (linked to a page that does not exist); dispatched qty from dc_dispatch_qty (dc_qty repeats the ordered qty per DC); dead fnValidate() call removed.</t>
         </is>
       </c>
-      <c r="C160" s="4" t="n"/>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 | Items popup now the shared centred one (was a full-width popup at the top).</t>
+        </is>
+      </c>
       <c r="D160" s="4" t="n"/>
       <c r="E160" s="4" t="n"/>
       <c r="F160" s="4" t="n"/>
@@ -3955,7 +3959,11 @@
           <t>2026-10-22 | New. SO items with ordered / DC / invoiced / pending qty, stock, stage, DC and invoice numbers - login + csrf.</t>
         </is>
       </c>
-      <c r="C161" s="4" t="n"/>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 | Rows marked for the shared popup.</t>
+        </is>
+      </c>
       <c r="D161" s="4" t="n"/>
       <c r="E161" s="4" t="n"/>
       <c r="F161" s="4" t="n"/>
@@ -3979,6 +3987,54 @@
       <c r="F162" s="4" t="n"/>
       <c r="G162" s="4" t="n"/>
       <c r="H162" s="4" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>inc/common/doc_items_modal.php</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 | New. Centred popup in the existing modal style (bg-modal header / footer, Show all items in the footer) shared by the sales order and purchase order reports.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>rpt_purchase_order.php</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 | New. Report &gt; Purchase Order Report: approved POs, GRNs, items fully received, status Pending / Partial / Completed from accepted qty on finalised GRNs; status opens the items popup. PO viewers pick any branch, others their own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>inc/cis_ajax/jquery_po_item_status.php</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 | New. PO items with ordered / received / accepted / rejected / returned / to receive, stock, stage, GRN and return numbers - login + csrf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>db/post_upload_221026.sql</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 | New. Report &gt; Purchase Order Report menu (rights as Sales Order Report); indexes on the PO / GRN / SO / DC / invoice link columns.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3991,7 +4047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4901,7 +4957,11 @@
           <t>2026-10-16 | (rows) | Item Masters &gt; Bulk Discount / Margin and Item Price Update; rights for Item creators (ITEM C).</t>
         </is>
       </c>
-      <c r="C32" s="4" t="n"/>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 | (rows) | Report &gt; Purchase Order Report (rpt_purchase_order.php); rights for users who have the Sales Order Report.</t>
+        </is>
+      </c>
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="4" t="n"/>
@@ -4913,6 +4973,30 @@
       <c r="L32" s="4" t="n"/>
       <c r="M32" s="4" t="n"/>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>tbl_grn / tbl_grn_details / tbl_purchase_order_details</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 | po_id, (grn_id, grn_item_id), po_id | Indexes added - the reports and GRN screens scanned whole tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>tbl_dc / tbl_dc_details / tbl_invoice / tbl_invoice_details / tbl_sales_order_details / tbl_grn_pay_receipt</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 | so_id, (dc_id, dc_item_id), so_id, inv_id, so_id, grn_id | Indexes added on the link columns.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H166"/>
+  <dimension ref="A1:I169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -474,6 +474,7 @@
     <col width="62" customWidth="1" min="6" max="6"/>
     <col width="62" customWidth="1" min="7" max="7"/>
     <col width="62" customWidth="1" min="8" max="8"/>
+    <col width="62" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -515,6 +516,11 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Change 7</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Change 8</t>
         </is>
       </c>
     </row>
@@ -1465,6 +1471,11 @@
           <t>2026-10-16 | Loads js/price_calc.js.</t>
         </is>
       </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23 | datatable-col4 setup (4 columns, actions not sortable) for the principal / brand masters.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3601,7 +3612,11 @@
           <t>2026-10-13 | CRITICAL: login + csrf, only the 24 table / column pairs the delete links use, status forced to 0, id bound - it took table, column and value from the post with no login.</t>
         </is>
       </c>
-      <c r="C142" s="4" t="n"/>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23 | A principal or brand still used by items is refused (409 with the item count).</t>
+        </is>
+      </c>
       <c r="D142" s="4" t="n"/>
       <c r="E142" s="4" t="n"/>
       <c r="F142" s="4" t="n"/>
@@ -3847,7 +3862,11 @@
           <t>2026-10-16 | New. Principal / brand / division / item type / search filters shared by the two screens.</t>
         </is>
       </c>
-      <c r="C155" s="4" t="n"/>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23 | Principal dropdown without data-placeholder - the --- All --- option was taken as the placeholder and hidden on Bulk Discount / Margin and Item Price Update.</t>
+        </is>
+      </c>
       <c r="D155" s="4" t="n"/>
       <c r="E155" s="4" t="n"/>
       <c r="F155" s="4" t="n"/>
@@ -4033,6 +4052,42 @@
       <c r="B166" s="3" t="inlineStr">
         <is>
           <t>2026-10-22 | New. Report &gt; Purchase Order Report menu (rights as Sales Order Report); indexes on the PO / GRN / SO / DC / invoice link columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>mst_principal.php</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23 | Items column (active items mapped); delete icon only when no item uses the principal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>mst_brand.php</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23 | Items column (active items mapped); delete icon only when no item uses the brand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>db/principal_brand_sync_231026.sql</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23 | New. Stanley / Taparia / Chicago Pneumatic / Shree Prayag: brand created when missing, items with the principal get the brand and items with the brand get the principal where the other side is empty or Not Applicable; items with a different real principal / brand listed, not changed.</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4789,7 +4844,11 @@
           <t>2026-10-16 | margin_percent | Recalculated on cost, same rule. Head Office price changes from the new screens are copied here.</t>
         </is>
       </c>
-      <c r="D25" s="4" t="n"/>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23 | item_principal / item_brand_make | The four principal-brand pairs filled in where one side was empty or Not Applicable.</t>
+        </is>
+      </c>
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="n"/>
@@ -4997,6 +5056,18 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>mst_brand</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23 | (rows) | SHREE PRAYAG (SPAC) created; CHICAGO PNEUMATIC / STANLEY / TAPARIA only when missing.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I169"/>
+  <dimension ref="A1:I170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4088,6 +4088,23 @@
       <c r="B169" s="3" t="inlineStr">
         <is>
           <t>2026-10-23 | New. Stanley / Taparia / Chicago Pneumatic / Shree Prayag: brand created when missing, items with the principal get the brand and items with the brand get the principal where the other side is empty or Not Applicable; items with a different real principal / brand listed, not changed.</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23 | Second version: principals found by name as well as code (live codes STANELY / TAPARIA were missed, so Stanley and Taparia were skipped); Chicago uses the existing brand CP; the duplicate CHICAGO PNEUMATIC brand removed when unused; a pair not found is shown, not skipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>db/principal_brand_override_231026.sql</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23 | New, optional. Items with a STANLEY / TAPARIA / CP brand but another real principal (Customize, MULTIBRAND, HONDA, YAMAHA - 45 on live) get the brand's company as principal; lists the changes first.</t>
         </is>
       </c>
     </row>
@@ -5067,6 +5084,11 @@
           <t>2026-10-23 | (rows) | SHREE PRAYAG (SPAC) created; CHICAGO PNEUMATIC / STANLEY / TAPARIA only when missing.</t>
         </is>
       </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23 | (rows) | CHICAGO PNEUMATIC (made by the first sync version, unused) set to status 0 - Chicago Pneumatics uses brand CP.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I170"/>
+  <dimension ref="A1:I174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1720,7 +1720,11 @@
           <t>2026-10-06 | Branch columns driven from mst_branch. The header looped the branch table but the rows wrote only ho_stock and kl_stock, so Rajapalayam had a header and no cells. An item with no tbl_item_stock row now reads 0.000 instead of dropping its cells, the item lookup is bound, and the empty-state colspan follows the branch count.</t>
         </is>
       </c>
-      <c r="C52" s="4" t="n"/>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | Units, GST, stock rows and selling price read once for the whole report (14,035 -&gt; 26 queries). Output unchanged.</t>
+        </is>
+      </c>
       <c r="D52" s="4" t="n"/>
       <c r="E52" s="4" t="n"/>
       <c r="F52" s="4" t="n"/>
@@ -3368,7 +3372,11 @@
           <t>2026-10-13 | Update location for creators in Task Settings (STOCK_LOCATION C) - was users 1 and 9.</t>
         </is>
       </c>
-      <c r="C130" s="4" t="n"/>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | Branch stock and open SO qty read once for the whole report (16,845 -&gt; 28 queries, 13.9 s -&gt; 0.4 s on 8,900 items). Output unchanged.</t>
+        </is>
+      </c>
       <c r="D130" s="4" t="n"/>
       <c r="E130" s="4" t="n"/>
       <c r="F130" s="4" t="n"/>
@@ -3961,7 +3969,11 @@
           <t>2026-10-22 | Items popup now the shared centred one (was a full-width popup at the top).</t>
         </is>
       </c>
-      <c r="D160" s="4" t="n"/>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | SO qty, DC / invoice lists and counts, totals, customer names read once for all SOs listed (5,891 -&gt; 39 queries); unused per-DC lookups removed. Output unchanged.</t>
+        </is>
+      </c>
       <c r="E160" s="4" t="n"/>
       <c r="F160" s="4" t="n"/>
       <c r="G160" s="4" t="n"/>
@@ -4105,6 +4117,54 @@
       <c r="B170" s="3" t="inlineStr">
         <is>
           <t>2026-10-23 | New, optional. Items with a STANLEY / TAPARIA / CP brand but another real principal (Customize, MULTIBRAND, HONDA, YAMAHA - 45 on live) get the brand's company as principal; lists the changes first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>rpt_branch_wise_stock.php</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | Units and branch stock read once for the whole report (21,049 -&gt; 27 queries). Output unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>rpt_store_stock_list.php</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | Descriptions and units read once for the whole report (12,623 -&gt; 21 queries). Output unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>rpt_item_details_check.php</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | Units and HSN codes read once for the whole report (12,621 -&gt; 20 queries). Output unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>inc/common/dbhandler.php</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | New GetMap (whole lookup in one query) and MapValue (value per key, same as GetSingleReconrd gives).</t>
         </is>
       </c>
     </row>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -2991,7 +2991,11 @@
           <t>2026-10-13 | Cancel link moved to its own task SO_CANCEL (admin) - approve and cancel are different people.</t>
         </is>
       </c>
-      <c r="D111" s="4" t="n"/>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | Item count, qty, DC, dispatched qty, invoice and quotation lookups read once for the page's SOs (392 -&gt; 33 queries per page). Output unchanged.</t>
+        </is>
+      </c>
       <c r="E111" s="4" t="n"/>
       <c r="F111" s="4" t="n"/>
       <c r="G111" s="4" t="n"/>
@@ -3602,7 +3606,11 @@
           <t>2026-10-13 | List limited to the branches the user approves for, same rule as the tile.</t>
         </is>
       </c>
-      <c r="C141" s="4" t="n"/>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | Supplier name / credit days and paid amount read once for the list, not 3 queries per GRN (1,512 -&gt; 21 queries). Output unchanged.</t>
+        </is>
+      </c>
       <c r="D141" s="4" t="n"/>
       <c r="E141" s="4" t="n"/>
       <c r="F141" s="4" t="n"/>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I174"/>
+  <dimension ref="A1:I176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1725,7 +1725,11 @@
           <t>2026-10-26 | Units, GST, stock rows and selling price read once for the whole report (14,035 -&gt; 26 queries). Output unchanged.</t>
         </is>
       </c>
-      <c r="D52" s="4" t="n"/>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | Rows shown 100 a page with search; photos load only for the rows shown (5.5 s -&gt; 1.4 s). Exports unchanged.</t>
+        </is>
+      </c>
       <c r="E52" s="4" t="n"/>
       <c r="F52" s="4" t="n"/>
       <c r="G52" s="4" t="n"/>
@@ -3381,7 +3385,11 @@
           <t>2026-10-26 | Branch stock and open SO qty read once for the whole report (16,845 -&gt; 28 queries, 13.9 s -&gt; 0.4 s on 8,900 items). Output unchanged.</t>
         </is>
       </c>
-      <c r="D130" s="4" t="n"/>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | Rows shown 100 a page with search (js/report_rows.js); 8.9 s -&gt; 1.0 s to usable page. Exports unchanged.</t>
+        </is>
+      </c>
       <c r="E130" s="4" t="n"/>
       <c r="F130" s="4" t="n"/>
       <c r="G130" s="4" t="n"/>
@@ -4139,6 +4147,11 @@
           <t>2026-10-26 | Units and branch stock read once for the whole report (21,049 -&gt; 27 queries). Output unchanged.</t>
         </is>
       </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | Rows shown 100 a page with search (4.3 s -&gt; 1.0 s). Exports unchanged.</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -4151,6 +4164,11 @@
           <t>2026-10-26 | Descriptions and units read once for the whole report (12,623 -&gt; 21 queries). Output unchanged.</t>
         </is>
       </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | Rows shown 100 a page with search (1.9 s -&gt; 1.0 s). Exports unchanged.</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -4163,6 +4181,11 @@
           <t>2026-10-26 | Units and HSN codes read once for the whole report (12,621 -&gt; 20 queries). Output unchanged.</t>
         </is>
       </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | Rows shown 100 a page with search (2.1 s -&gt; 0.5 s).</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -4173,6 +4196,30 @@
       <c r="B174" s="3" t="inlineStr">
         <is>
           <t>2026-10-26 | New GetMap (whole lookup in one query) and MapValue (value per key, same as GetSingleReconrd gives).</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>js/report_rows.js</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | New. Report rows held in &lt;template id="rpt_rows"&gt; shown 100 a page with search; Excel / PDF / Print get every row for that click.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>rpt_item_discount.php</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | Rows shown 100 a page with search (3.5 s -&gt; 0.7 s). Exports unchanged.</t>
         </is>
       </c>
     </row>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I176"/>
+  <dimension ref="A1:I178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2950,7 +2950,11 @@
           <t>2026-10-13 | All branches for viewers in Task Settings (QUOTATION W) - was admin or head office.</t>
         </is>
       </c>
-      <c r="C109" s="4" t="n"/>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | Proforma per quotation read once for the page (was one query per row).</t>
+        </is>
+      </c>
       <c r="D109" s="4" t="n"/>
       <c r="E109" s="4" t="n"/>
       <c r="F109" s="4" t="n"/>
@@ -4198,6 +4202,11 @@
           <t>2026-10-26 | New GetMap (whole lookup in one query) and MapValue (value per key, same as GetSingleReconrd gives).</t>
         </is>
       </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | One connection shared by all dbhandler objects of a request (was a new connection each); new GetRow (prepared, first row).</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -4220,6 +4229,30 @@
       <c r="B176" s="3" t="inlineStr">
         <is>
           <t>2026-10-26 | Rows shown 100 a page with search (3.5 s -&gt; 0.7 s). Exports unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>inc/common/sidebar.php</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | All visible sub menus in one query grouped per main menu (was 1-2 queries per main menu). Same menus and HTML.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>inc/common/active_menu.php</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | Page's sub menu and main menu in one prepared query (was two).</t>
         </is>
       </c>
     </row>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I178"/>
+  <dimension ref="A1:I179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4256,6 +4256,18 @@
         </is>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>db/post_upload_261026.sql</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | New. 24 indexes on link columns found by EXPLAIN on every menu page; only indexes, safe to run again.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4267,7 +4279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4595,7 +4607,11 @@
           <t>2026-10-05 | cgst_per, sgst_per, igst_per, cgst_val, sgst_val, igst_val | Optional tidy on the same 111 rows only.</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n"/>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | (index) | item_id - lookups by this column were full table scans. db/post_upload_261026.sql</t>
+        </is>
+      </c>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
@@ -5238,6 +5254,258 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>tbl_quotation_details</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | (index) | quo_id, item_id - lookups by these columns were full table scans. db/post_upload_261026.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>tbl_quo_pack_details</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | (index) | quo_id - lookups by this column were full table scans. db/post_upload_261026.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>tbl_invoice_pack_details</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | (index) | inv_id - lookups by this column were full table scans. db/post_upload_261026.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>tbl_sales_order_pack_dts</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | (index) | so_id - lookups by this column were full table scans. db/post_upload_261026.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>tbl_store_indent_details</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | (index) | si_id - lookups by this column were full table scans. db/post_upload_261026.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>tbl_po_prepare_dets</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | (index) | po_prepare_id, si_id - lookups by these columns were full table scans. db/post_upload_261026.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>tbl_po_prepare</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | (index) | si_id - lookups by this column were full table scans. db/post_upload_261026.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>tbl_po_print_details</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | (index) | po_id - lookups by this column were full table scans. db/post_upload_261026.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>tbl_package_box_details</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | (index) | dc_id - lookups by this column were full table scans. db/post_upload_261026.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>tbl_item_group_details</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | (index) | item_group_id - lookups by this column were full table scans. db/post_upload_261026.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>tbl_attendance</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | (index) | emp_id - lookups by this column were full table scans. db/post_upload_261026.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>tbl_quotation</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | (index) | supp_id - lookups by this column were full table scans. db/post_upload_261026.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>tbl_purchase_order</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | (index) | supp_id - lookups by this column were full table scans. db/post_upload_261026.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>tbl_grn</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | (index) | supp_id - lookups by this column were full table scans. db/post_upload_261026.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>tbl_invoice</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | (index) | supp_id - lookups by this column were full table scans. db/post_upload_261026.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>tbl_sales_order</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | (index) | quo_id - lookups by this column were full table scans. db/post_upload_261026.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>tbl_receipt</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | (index) | so_id - lookups by this column were full table scans. db/post_upload_261026.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>tbl_dc</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | (index) | dc_inv_id - lookups by this column were full table scans. db/post_upload_261026.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>tbl_sales_order_details</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | (index) | item_id - lookups by this column were full table scans. db/post_upload_261026.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>tbl_purchase_order_details</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | (index) | item_id - lookups by this column were full table scans. db/post_upload_261026.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>tbl_spare_mapping</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | (index) | item_id - lookups by this column were full table scans. db/post_upload_261026.sql</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I179"/>
+  <dimension ref="A1:I180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2914,7 +2914,11 @@
           <t>2026-10-13 | All branches for viewers in Task Settings (PO_PREPARE W) - was admin or head office.</t>
         </is>
       </c>
-      <c r="C107" s="4" t="n"/>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | PO prepare / indent lookups read once for the page's indents (about 450 -&gt; 22 queries); unused lookups removed. Output unchanged.</t>
+        </is>
+      </c>
       <c r="D107" s="4" t="n"/>
       <c r="E107" s="4" t="n"/>
       <c r="F107" s="4" t="n"/>
@@ -3004,7 +3008,11 @@
           <t>2026-10-26 | Item count, qty, DC, dispatched qty, invoice and quotation lookups read once for the page's SOs (392 -&gt; 33 queries per page). Output unchanged.</t>
         </is>
       </c>
-      <c r="E111" s="4" t="n"/>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | Item count for an SO with no lines is the number 0, as the old count gave.</t>
+        </is>
+      </c>
       <c r="F111" s="4" t="n"/>
       <c r="G111" s="4" t="n"/>
       <c r="H111" s="4" t="n"/>
@@ -3680,7 +3688,11 @@
           <t>2026-10-14 | Customer branch read from cus_branch_id - it used branch_id (our branch), so every invoice showed customer branch 1 or 2, even for customers without a branch.</t>
         </is>
       </c>
-      <c r="C144" s="4" t="n"/>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | Customer names and invoice / pack totals read once for the report (901 -&gt; 19 queries). Output unchanged.</t>
+        </is>
+      </c>
       <c r="D144" s="4" t="n"/>
       <c r="E144" s="4" t="n"/>
       <c r="F144" s="4" t="n"/>
@@ -3994,7 +4006,11 @@
           <t>2026-10-26 | SO qty, DC / invoice lists and counts, totals, customer names read once for all SOs listed (5,891 -&gt; 39 queries); unused per-DC lookups removed. Output unchanged.</t>
         </is>
       </c>
-      <c r="E160" s="4" t="n"/>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | DC / invoice counts for an SO with none are the number 0, as the old count gave.</t>
+        </is>
+      </c>
       <c r="F160" s="4" t="n"/>
       <c r="G160" s="4" t="n"/>
       <c r="H160" s="4" t="n"/>
@@ -4207,6 +4223,11 @@
           <t>2026-10-26 | One connection shared by all dbhandler objects of a request (was a new connection each); new GetRow (prepared, first row).</t>
         </is>
       </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | MapValue note: COUNT default is 0 (number).</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -4265,6 +4286,18 @@
       <c r="B179" s="3" t="inlineStr">
         <is>
           <t>2026-10-26 | New. 24 indexes on link columns found by EXPLAIN on every menu page; only indexes, safe to run again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>quotation_branch_rept.php</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 | Customer names and item counts read once for the report (3,606 -&gt; 17 queries). Output unchanged.</t>
         </is>
       </c>
     </row>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -3631,7 +3631,11 @@
           <t>2026-10-26 | Supplier name / credit days and paid amount read once for the list, not 3 queries per GRN (1,512 -&gt; 21 queries). Output unchanged.</t>
         </is>
       </c>
-      <c r="D141" s="4" t="n"/>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Bill Due Date = party bill date + supplier credit days (was today + credit days - unset variable); badge follows it.</t>
+        </is>
+      </c>
       <c r="E141" s="4" t="n"/>
       <c r="F141" s="4" t="n"/>
       <c r="G141" s="4" t="n"/>
@@ -4250,6 +4254,11 @@
       <c r="B176" s="3" t="inlineStr">
         <is>
           <t>2026-10-26 | Rows shown 100 a page with search (3.5 s -&gt; 0.7 s). Exports unchanged.</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Max Discount shown whenever a max is set (it checked the min, so showed '-' when min was 0).</t>
         </is>
       </c>
     </row>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I180"/>
+  <dimension ref="A1:I206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -965,7 +965,11 @@
           <t>2026-09-23 | New. Rows for the stock list. One stock column per active branch, read from mst_branch.</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="n"/>
@@ -1730,7 +1734,11 @@
           <t>2026-10-26 | Rows shown 100 a page with search; photos load only for the rows shown (5.5 s -&gt; 1.4 s). Exports unchanged.</t>
         </is>
       </c>
-      <c r="E52" s="4" t="n"/>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Missing price / GST count as 0 - PHP 8 type error stopped the report at row 2,001.</t>
+        </is>
+      </c>
       <c r="F52" s="4" t="n"/>
       <c r="G52" s="4" t="n"/>
       <c r="H52" s="4" t="n"/>
@@ -1929,7 +1937,11 @@
           <t>2026-10-14 | fnIsLoggedIn(); isAdmin also needs the user id and branch - a session with only _user=crm_user (another app on the server) opened pages with no user or branch.</t>
         </is>
       </c>
-      <c r="D60" s="4" t="n"/>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | New fnSqlText / fnSqlColumn / fnSqlDir - search and sort input safe in SQL.</t>
+        </is>
+      </c>
       <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
@@ -2682,7 +2694,11 @@
           <t>2026-10-13 | All branches for viewers in Task Settings (DC W) - was admin or head office.</t>
         </is>
       </c>
-      <c r="C95" s="4" t="n"/>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Sales Details popup given the SO id (was DC id); search / sort input safe.</t>
+        </is>
+      </c>
       <c r="D95" s="4" t="n"/>
       <c r="E95" s="4" t="n"/>
       <c r="F95" s="4" t="n"/>
@@ -2700,7 +2716,11 @@
           <t>2026-10-13 | All branches for viewers in Task Settings (EMPLOYEE W) - was admin or head office.</t>
         </is>
       </c>
-      <c r="C96" s="4" t="n"/>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
       <c r="D96" s="4" t="n"/>
       <c r="E96" s="4" t="n"/>
       <c r="F96" s="4" t="n"/>
@@ -2718,7 +2738,11 @@
           <t>2026-10-13 | All branches for viewers in Task Settings (EMPLOYEE W) - was admin or head office.</t>
         </is>
       </c>
-      <c r="C97" s="4" t="n"/>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
       <c r="D97" s="4" t="n"/>
       <c r="E97" s="4" t="n"/>
       <c r="F97" s="4" t="n"/>
@@ -2736,7 +2760,11 @@
           <t>2026-10-13 | All branches for viewers in Task Settings (EMPLOYEE W) - was admin or head office.</t>
         </is>
       </c>
-      <c r="C98" s="4" t="n"/>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
       <c r="D98" s="4" t="n"/>
       <c r="E98" s="4" t="n"/>
       <c r="F98" s="4" t="n"/>
@@ -2759,7 +2787,11 @@
           <t>2026-10-13 | Own branch only without the Employee viewer role - every branch showed.</t>
         </is>
       </c>
-      <c r="D99" s="4" t="n"/>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
       <c r="E99" s="4" t="n"/>
       <c r="F99" s="4" t="n"/>
       <c r="G99" s="4" t="n"/>
@@ -2776,7 +2808,11 @@
           <t>2026-10-13 | All branches for viewers in Task Settings (EMPLOYEE W) - was admin or head office.</t>
         </is>
       </c>
-      <c r="C100" s="4" t="n"/>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
       <c r="D100" s="4" t="n"/>
       <c r="E100" s="4" t="n"/>
       <c r="F100" s="4" t="n"/>
@@ -2794,7 +2830,11 @@
           <t>2026-10-13 | All branches for viewers in Task Settings (GRN W) - was admin or head office.</t>
         </is>
       </c>
-      <c r="C101" s="4" t="n"/>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
       <c r="D101" s="4" t="n"/>
       <c r="E101" s="4" t="n"/>
       <c r="F101" s="4" t="n"/>
@@ -2822,7 +2862,11 @@
           <t>2026-10-22 | Multiple rows: edit icon opens the main GRN's payment page.</t>
         </is>
       </c>
-      <c r="E102" s="4" t="n"/>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Supplier column sorts by supplier name (supp_id ambiguous); sort input checked.</t>
+        </is>
+      </c>
       <c r="F102" s="4" t="n"/>
       <c r="G102" s="4" t="n"/>
       <c r="H102" s="4" t="n"/>
@@ -2838,7 +2882,11 @@
           <t>2026-10-13 | All branches for viewers in Task Settings (INVOICE W) - was admin or head office.</t>
         </is>
       </c>
-      <c r="C103" s="4" t="n"/>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
       <c r="D103" s="4" t="n"/>
       <c r="E103" s="4" t="n"/>
       <c r="F103" s="4" t="n"/>
@@ -2861,7 +2909,11 @@
           <t>2026-10-16 | Principal filter; brand / principal as numbers and search text quoted - they went into the sql as typed.</t>
         </is>
       </c>
-      <c r="D104" s="4" t="n"/>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
       <c r="E104" s="4" t="n"/>
       <c r="F104" s="4" t="n"/>
       <c r="G104" s="4" t="n"/>
@@ -2878,7 +2930,11 @@
           <t>2026-10-13 | All branches for viewers in Task Settings (EMPLOYEE W) - was admin or head office.</t>
         </is>
       </c>
-      <c r="C105" s="4" t="n"/>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
       <c r="D105" s="4" t="n"/>
       <c r="E105" s="4" t="n"/>
       <c r="F105" s="4" t="n"/>
@@ -2896,7 +2952,11 @@
           <t>2026-10-13 | Edit links for creators in Task Settings (PURCHASE_ORDER C) - was admin or head office.</t>
         </is>
       </c>
-      <c r="C106" s="4" t="n"/>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
       <c r="D106" s="4" t="n"/>
       <c r="E106" s="4" t="n"/>
       <c r="F106" s="4" t="n"/>
@@ -2919,7 +2979,11 @@
           <t>2026-10-26 | PO prepare / indent lookups read once for the page's indents (about 450 -&gt; 22 queries); unused lookups removed. Output unchanged.</t>
         </is>
       </c>
-      <c r="D107" s="4" t="n"/>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Status filter on the PO prepare rows; search / sort input safe.</t>
+        </is>
+      </c>
       <c r="E107" s="4" t="n"/>
       <c r="F107" s="4" t="n"/>
       <c r="G107" s="4" t="n"/>
@@ -2936,7 +3000,11 @@
           <t>2026-10-13 | GRN cancel link for approvers in Task Settings (GRN A) - was admin or head office.</t>
         </is>
       </c>
-      <c r="C108" s="4" t="n"/>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
       <c r="D108" s="4" t="n"/>
       <c r="E108" s="4" t="n"/>
       <c r="F108" s="4" t="n"/>
@@ -2959,7 +3027,11 @@
           <t>2026-10-26 | Proforma per quotation read once for the page (was one query per row).</t>
         </is>
       </c>
-      <c r="D109" s="4" t="n"/>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
       <c r="E109" s="4" t="n"/>
       <c r="F109" s="4" t="n"/>
       <c r="G109" s="4" t="n"/>
@@ -2981,7 +3053,11 @@
           <t>2026-10-15 | Revoke next to a confirmed payment (SALES_RECEIPT R).</t>
         </is>
       </c>
-      <c r="D110" s="4" t="n"/>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
       <c r="E110" s="4" t="n"/>
       <c r="F110" s="4" t="n"/>
       <c r="G110" s="4" t="n"/>
@@ -3013,7 +3089,11 @@
           <t>2026-10-26 | Item count for an SO with no lines is the number 0, as the old count gave.</t>
         </is>
       </c>
-      <c r="F111" s="4" t="n"/>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
       <c r="G111" s="4" t="n"/>
       <c r="H111" s="4" t="n"/>
     </row>
@@ -3028,7 +3108,11 @@
           <t>2026-10-13 | All branches for viewers in Task Settings (EMPLOYEE W) - was admin or head office.</t>
         </is>
       </c>
-      <c r="C112" s="4" t="n"/>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
       <c r="D112" s="4" t="n"/>
       <c r="E112" s="4" t="n"/>
       <c r="F112" s="4" t="n"/>
@@ -3056,7 +3140,11 @@
           <t>2026-10-15 | Approve page link also for Revokers on approved suppliers.</t>
         </is>
       </c>
-      <c r="E113" s="4" t="n"/>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
       <c r="F113" s="4" t="n"/>
       <c r="G113" s="4" t="n"/>
       <c r="H113" s="4" t="n"/>
@@ -3072,7 +3160,11 @@
           <t>2026-10-13 | All branches for viewers in Task Settings (STORE_INDENT W) - was admin or head office.</t>
         </is>
       </c>
-      <c r="C114" s="4" t="n"/>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
       <c r="D114" s="4" t="n"/>
       <c r="E114" s="4" t="n"/>
       <c r="F114" s="4" t="n"/>
@@ -3264,7 +3356,11 @@
           <t>2026-10-13 | Branch filter for viewers in Task Settings (PO_PREPARE W) - was head office.</t>
         </is>
       </c>
-      <c r="C124" s="4" t="n"/>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Status not sortable (no column), date sortable.</t>
+        </is>
+      </c>
       <c r="D124" s="4" t="n"/>
       <c r="E124" s="4" t="n"/>
       <c r="F124" s="4" t="n"/>
@@ -3402,7 +3498,11 @@
           <t>2026-10-26 | Rows shown 100 a page with search (js/report_rows.js); 8.9 s -&gt; 1.0 s to usable page. Exports unchanged.</t>
         </is>
       </c>
-      <c r="E130" s="4" t="n"/>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | No stock join (items with 2 stock rows listed twice); no stock row shows 0.000.</t>
+        </is>
+      </c>
       <c r="F130" s="4" t="n"/>
       <c r="G130" s="4" t="n"/>
       <c r="H130" s="4" t="n"/>
@@ -3697,7 +3797,11 @@
           <t>2026-10-26 | Customer names and invoice / pack totals read once for the report (901 -&gt; 19 queries). Output unchanged.</t>
         </is>
       </c>
-      <c r="D144" s="4" t="n"/>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Chosen dates kept; Print / PDF area rpt_division; 5-column spans; search quoted.</t>
+        </is>
+      </c>
       <c r="E144" s="4" t="n"/>
       <c r="F144" s="4" t="n"/>
       <c r="G144" s="4" t="n"/>
@@ -4015,7 +4119,11 @@
           <t>2026-10-26 | DC / invoice counts for an SO with none are the number 0, as the old count gave.</t>
         </is>
       </c>
-      <c r="F160" s="4" t="n"/>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search text quoted, branch as number (a ' broke the report).</t>
+        </is>
+      </c>
       <c r="G160" s="4" t="n"/>
       <c r="H160" s="4" t="n"/>
     </row>
@@ -4118,6 +4226,11 @@
           <t>2026-10-23 | Items column (active items mapped); delete icon only when no item uses the principal.</t>
         </is>
       </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Delete cancel uses return false (return false() threw a script error).</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -4130,6 +4243,11 @@
           <t>2026-10-23 | Items column (active items mapped); delete icon only when no item uses the brand.</t>
         </is>
       </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Delete cancel uses return false (return false() threw a script error).</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -4176,6 +4294,11 @@
           <t>2026-10-26 | Rows shown 100 a page with search (4.3 s -&gt; 1.0 s). Exports unchanged.</t>
         </is>
       </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | No stock join (items with 2 stock rows listed twice, descriptions lost); no stock row shows 0.000.</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -4261,6 +4384,11 @@
           <t>2026-10-27 | Max Discount shown whenever a max is set (it checked the min, so showed '-' when min was 0).</t>
         </is>
       </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Item's first stock row only (items with 2 stock rows listed twice).</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -4285,6 +4413,11 @@
           <t>2026-10-26 | Page's sub menu and main menu in one prepared query (was two).</t>
         </is>
       </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Line breaks in stored menu URLs ignored (those menus never showed active).</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -4307,6 +4440,323 @@
       <c r="B180" s="3" t="inlineStr">
         <is>
           <t>2026-10-26 | Customer names and item counts read once for the report (3,606 -&gt; 17 queries). Output unchanged.</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search text quoted, branch as number (a ' broke the report).</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>inc/cis_ajax/jquery_modal_stock_det.php</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Delete cancel uses return false (return false() threw a script error).</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxCostWorkSheet.php</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxCustomerList.php</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxIndentList.php</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxItemGroupingList.php</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxItemPriceHistoryList.php</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | One joined query: search on existing columns, sort by shown values, no stock row shows blanks (showed previous row).</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxMappingList.php</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Item name opens the item details popup (linked to a missing page); search / sort input safe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxSalaryPackageList.php</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>inc/datatable/ajaxStoreStockList.php</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Search / sort input through fnSqlText / fnSqlColumn / fnSqlDir (a ' in a search box broke the query).</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>lst_customers.php</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | # column not sortable (sorting by it failed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>lst_item_grouping.php</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Delete cancel uses return false (return false() threw a script error).</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>mst_boxtype.php</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Delete cancel uses return false (return false() threw a script error).</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>mst_branch.php</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Delete cancel uses return false (return false() threw a script error).</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>mst_category.php</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Delete cancel uses return false (return false() threw a script error).</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>mst_city.php</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Delete cancel uses return false (return false() threw a script error).</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>mst_color.php</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Delete cancel uses return false (return false() threw a script error).</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>mst_department.php</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Delete cancel uses return false (return false() threw a script error).</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>mst_designation.php</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Delete cancel uses return false (return false() threw a script error).</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>mst_district.php</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Delete cancel uses return false (return false() threw a script error).</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>mst_division.php</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Delete cancel uses return false (return false() threw a script error).</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>mst_hsn.php</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Delete cancel uses return false (return false() threw a script error).</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>mst_labour.php</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Delete cancel uses return false (return false() threw a script error).</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>mst_state.php</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Delete cancel uses return false (return false() threw a script error).</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>mst_uom.php</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Delete cancel uses return false (return false() threw a script error).</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>mst_user.php</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Delete cancel uses return false (return false() threw a script error).</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>spare_mapping_list.php</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 | Item details popup added for the item name link.</t>
         </is>
       </c>
     </row>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I206"/>
+  <dimension ref="A1:I207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4430,6 +4430,11 @@
           <t>2026-10-26 | New. 24 indexes on link columns found by EXPLAIN on every menu page; only indexes, safe to run again.</t>
         </is>
       </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28 | Check query moved out (phpMyAdmin ran the batch against information_schema, #1044).</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -4757,6 +4762,18 @@
       <c r="B206" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 | Item details popup added for the item name link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>db/post_upload_261026_check.sql</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28 | New. Read-only index check for post_upload_261026.sql - run on its own.</t>
         </is>
       </c>
     </row>

--- a/docs/BIE_Change_Log.xlsx
+++ b/docs/BIE_Change_Log.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I207"/>
+  <dimension ref="A1:I211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,11 @@
           <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30 | Quantity takes decimals (above 0, at most 3 decimals); total qty keeps decimals; rows shown with fnQty.</t>
+        </is>
+      </c>
       <c r="H7" s="4" t="n"/>
     </row>
     <row r="8">
@@ -699,7 +703,11 @@
           <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8.</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30 | Invoice qty and total shown with fnQty.</t>
+        </is>
+      </c>
       <c r="H8" s="4" t="n"/>
     </row>
     <row r="9">
@@ -733,7 +741,11 @@
           <t>2026-10-07 | Posted row counts via fnRowCount() - count() on a single value is fatal on PHP 8. Package dropdown renamed pack_pick so it cannot replace the pack_id[] rows.</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30 | Invoice qty and total shown with fnQty.</t>
+        </is>
+      </c>
       <c r="H9" s="4" t="n"/>
     </row>
     <row r="10">
@@ -1942,7 +1954,11 @@
           <t>2026-10-27 | New fnSqlText / fnSqlColumn / fnSqlDir - search and sort input safe in SQL.</t>
         </is>
       </c>
-      <c r="E60" s="4" t="n"/>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30 | New fnQty() - qty shown up to 3 decimals without trailing zeros.</t>
+        </is>
+      </c>
       <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
       <c r="H60" s="4" t="n"/>
@@ -4774,6 +4790,54 @@
       <c r="B207" s="3" t="inlineStr">
         <is>
           <t>2026-10-28 | New. Read-only index check for post_upload_261026.sql - run on its own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>db/post_upload_301026.sql</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30 | New. tbl_invoice_details.inv_qty to DECIMAL(12,3) - items sold in part qty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>inc/cis_ajax/jquery_po_inv_details.php</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30 | Invoice row qty shown with fnQty (part qty).</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>invoice_print.php</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30 | Qty shown with fnQty (0.5 / 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>quo_invoice_print.php</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30 | Qty shown with fnQty (0.5 / 2).</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5185,11 @@
           <t>2026-10-26 | (index) | item_id - lookups by this column were full table scans. db/post_upload_261026.sql</t>
         </is>
       </c>
-      <c r="E11" s="4" t="n"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30 | inv_qty int(11) -&gt; DECIMAL(12,3) NOT NULL (part qty). db/post_upload_301026.sql</t>
+        </is>
+      </c>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="4" t="n"/>
